--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126997331</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127000523</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127003192</v>
       </c>
       <c r="B5" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127002958</v>
       </c>
       <c r="B6" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127000744</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>126996109</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126995985</v>
       </c>
       <c r="B9" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127001329</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>127001472</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127001576</v>
+        <v>127001416</v>
       </c>
       <c r="B12" t="n">
         <v>57657</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595101</v>
+        <v>595109</v>
       </c>
       <c r="R12" t="n">
         <v>6948171</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127001416</v>
+        <v>127001576</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595109</v>
+        <v>595101</v>
       </c>
       <c r="R13" t="n">
         <v>6948171</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127000920</v>
+        <v>127001223</v>
       </c>
       <c r="B14" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1884,34 +1884,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595083</v>
+        <v>595101</v>
       </c>
       <c r="R14" t="n">
-        <v>6948169</v>
+        <v>6948165</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,6 +1949,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1970,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127001223</v>
+        <v>127000920</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,39 +1991,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595101</v>
+        <v>595083</v>
       </c>
       <c r="R15" t="n">
-        <v>6948165</v>
+        <v>6948169</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,11 +2051,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,7 +2182,7 @@
         <v>126999823</v>
       </c>
       <c r="B17" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>127001836</v>
       </c>
       <c r="B18" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>126995868</v>
       </c>
       <c r="B19" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126996841</v>
+        <v>126998950</v>
       </c>
       <c r="B20" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,34 +2481,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594788</v>
+        <v>594798</v>
       </c>
       <c r="R20" t="n">
-        <v>6947674</v>
+        <v>6947746</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,6 +2546,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2567,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126998950</v>
+        <v>127003507</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>91615</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,39 +2588,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594798</v>
+        <v>594996</v>
       </c>
       <c r="R21" t="n">
-        <v>6947746</v>
+        <v>6948027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,11 +2648,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127002250</v>
+        <v>126996841</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>91319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,39 +2685,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595207</v>
+        <v>594788</v>
       </c>
       <c r="R22" t="n">
-        <v>6948320</v>
+        <v>6947674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,11 +2745,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2781,10 +2771,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127003507</v>
+        <v>127002250</v>
       </c>
       <c r="B23" t="n">
-        <v>91541</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2792,34 +2782,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594996</v>
+        <v>595207</v>
       </c>
       <c r="R23" t="n">
-        <v>6948027</v>
+        <v>6948320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,6 +2847,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2988,7 +2988,7 @@
         <v>127001941</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>126995558</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126999630</v>
+        <v>127002933</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>91319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,39 +3190,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594878</v>
+        <v>595226</v>
       </c>
       <c r="R27" t="n">
-        <v>6947857</v>
+        <v>6948345</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,11 +3250,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3289,7 +3279,7 @@
         <v>127003205</v>
       </c>
       <c r="B28" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,10 +3373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127002933</v>
+        <v>126999630</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,34 +3384,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595226</v>
+        <v>594878</v>
       </c>
       <c r="R29" t="n">
-        <v>6948345</v>
+        <v>6947857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3454,6 +3449,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3483,7 +3483,7 @@
         <v>126995659</v>
       </c>
       <c r="B30" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>127001067</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127000961</v>
       </c>
       <c r="B33" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126999279</v>
+        <v>127003667</v>
       </c>
       <c r="B34" t="n">
-        <v>88654</v>
+        <v>91615</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594843</v>
+        <v>594896</v>
       </c>
       <c r="R34" t="n">
-        <v>6947765</v>
+        <v>6947965</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127000459</v>
+        <v>126999279</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>88722</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4102,39 +4102,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595067</v>
+        <v>594843</v>
       </c>
       <c r="R36" t="n">
-        <v>6948158</v>
+        <v>6947765</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4167,11 +4162,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,10 +4188,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127003667</v>
+        <v>127000459</v>
       </c>
       <c r="B37" t="n">
-        <v>91541</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4209,34 +4199,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594896</v>
+        <v>595067</v>
       </c>
       <c r="R37" t="n">
-        <v>6947965</v>
+        <v>6948158</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,6 +4264,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4298,7 +4298,7 @@
         <v>127001802</v>
       </c>
       <c r="B38" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126997331</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127000523</v>
       </c>
       <c r="B3" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127003192</v>
+        <v>127002958</v>
       </c>
       <c r="B5" t="n">
-        <v>91773</v>
+        <v>91621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595066</v>
+        <v>595135</v>
       </c>
       <c r="R5" t="n">
-        <v>6948222</v>
+        <v>6948293</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127002958</v>
+        <v>127003192</v>
       </c>
       <c r="B6" t="n">
-        <v>91615</v>
+        <v>91779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595135</v>
+        <v>595066</v>
       </c>
       <c r="R6" t="n">
-        <v>6948293</v>
+        <v>6948222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
         <v>127000744</v>
       </c>
       <c r="B7" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>126996109</v>
       </c>
       <c r="B8" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126995985</v>
       </c>
       <c r="B9" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127001329</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127001472</v>
+        <v>127001223</v>
       </c>
       <c r="B11" t="n">
-        <v>80114</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,24 +1573,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
@@ -1600,7 +1605,7 @@
         <v>595101</v>
       </c>
       <c r="R11" t="n">
-        <v>6948171</v>
+        <v>6948165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,6 +1638,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,10 +1883,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127001223</v>
+        <v>127002114</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1884,16 +1894,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1913,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595101</v>
+        <v>595155</v>
       </c>
       <c r="R14" t="n">
-        <v>6948165</v>
+        <v>6948272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,11 +1959,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1980,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127000920</v>
+        <v>127001472</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2015,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595083</v>
+        <v>595101</v>
       </c>
       <c r="R15" t="n">
-        <v>6948169</v>
+        <v>6948171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,10 +2082,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127002114</v>
+        <v>127000920</v>
       </c>
       <c r="B16" t="n">
-        <v>57654</v>
+        <v>80117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,39 +2093,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595155</v>
+        <v>595083</v>
       </c>
       <c r="R16" t="n">
-        <v>6948272</v>
+        <v>6948169</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126999823</v>
+        <v>127001836</v>
       </c>
       <c r="B17" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,14 +2210,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594880</v>
+        <v>595099</v>
       </c>
       <c r="R17" t="n">
-        <v>6947896</v>
+        <v>6948188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127001836</v>
+        <v>126999823</v>
       </c>
       <c r="B18" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,14 +2307,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595099</v>
+        <v>594880</v>
       </c>
       <c r="R18" t="n">
-        <v>6948188</v>
+        <v>6947896</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2376,7 +2376,7 @@
         <v>126995868</v>
       </c>
       <c r="B19" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127003507</v>
+        <v>126996841</v>
       </c>
       <c r="B21" t="n">
-        <v>91615</v>
+        <v>91325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2588,34 +2588,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594996</v>
+        <v>594788</v>
       </c>
       <c r="R21" t="n">
-        <v>6948027</v>
+        <v>6947674</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126996841</v>
+        <v>127002250</v>
       </c>
       <c r="B22" t="n">
-        <v>91319</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,34 +2685,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594788</v>
+        <v>595207</v>
       </c>
       <c r="R22" t="n">
-        <v>6947674</v>
+        <v>6948320</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2745,6 +2750,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2771,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127002250</v>
+        <v>127003507</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>91621</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2782,39 +2792,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595207</v>
+        <v>594996</v>
       </c>
       <c r="R23" t="n">
-        <v>6948320</v>
+        <v>6948027</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,11 +2852,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2988,7 +2988,7 @@
         <v>127001941</v>
       </c>
       <c r="B25" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>126995558</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127002933</v>
+        <v>126999630</v>
       </c>
       <c r="B27" t="n">
-        <v>91319</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,34 +3190,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595226</v>
+        <v>594878</v>
       </c>
       <c r="R27" t="n">
-        <v>6948345</v>
+        <v>6947857</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,6 +3255,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3279,7 +3289,7 @@
         <v>127003205</v>
       </c>
       <c r="B28" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,10 +3383,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126999630</v>
+        <v>127002933</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3384,39 +3394,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594878</v>
+        <v>595226</v>
       </c>
       <c r="R29" t="n">
-        <v>6947857</v>
+        <v>6948345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,11 +3454,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,45 +3480,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126995659</v>
+        <v>127001067</v>
       </c>
       <c r="B30" t="n">
-        <v>91284</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594702</v>
+        <v>595082</v>
       </c>
       <c r="R30" t="n">
-        <v>6947579</v>
+        <v>6948159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3577,49 +3581,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127001067</v>
+        <v>126995659</v>
       </c>
       <c r="B31" t="n">
-        <v>98436</v>
+        <v>91290</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595082</v>
+        <v>594702</v>
       </c>
       <c r="R31" t="n">
-        <v>6948159</v>
+        <v>6947579</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127003810</v>
+        <v>127000961</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3689,39 +3689,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>594822</v>
+        <v>595075</v>
       </c>
       <c r="R32" t="n">
-        <v>6947827</v>
+        <v>6948146</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3754,11 +3754,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3785,10 +3780,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127000961</v>
+        <v>127003810</v>
       </c>
       <c r="B33" t="n">
-        <v>80114</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3796,39 +3791,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595075</v>
+        <v>594822</v>
       </c>
       <c r="R33" t="n">
-        <v>6948146</v>
+        <v>6947827</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3861,6 +3856,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3887,10 +3887,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127003667</v>
+        <v>126999279</v>
       </c>
       <c r="B34" t="n">
-        <v>91615</v>
+        <v>88728</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594896</v>
+        <v>594843</v>
       </c>
       <c r="R34" t="n">
-        <v>6947965</v>
+        <v>6947765</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127002325</v>
+        <v>127003667</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>91621</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,39 +3995,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595226</v>
+        <v>594896</v>
       </c>
       <c r="R35" t="n">
-        <v>6948345</v>
+        <v>6947965</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4060,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4091,10 +4081,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126999279</v>
+        <v>127000459</v>
       </c>
       <c r="B36" t="n">
-        <v>88722</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4102,34 +4092,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594843</v>
+        <v>595067</v>
       </c>
       <c r="R36" t="n">
-        <v>6947765</v>
+        <v>6948158</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4162,6 +4157,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4188,7 +4188,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127000459</v>
+        <v>127002325</v>
       </c>
       <c r="B37" t="n">
         <v>57657</v>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595067</v>
+        <v>595226</v>
       </c>
       <c r="R37" t="n">
-        <v>6948158</v>
+        <v>6948345</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
         <v>127001802</v>
       </c>
       <c r="B38" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126997331</v>
+        <v>127000523</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594788</v>
+        <v>595067</v>
       </c>
       <c r="R2" t="n">
-        <v>6947678</v>
+        <v>6948158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127000523</v>
+        <v>127003926</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595067</v>
+        <v>594733</v>
       </c>
       <c r="R3" t="n">
-        <v>6948158</v>
+        <v>6947763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127003926</v>
+        <v>126997331</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594733</v>
+        <v>594788</v>
       </c>
       <c r="R4" t="n">
-        <v>6947763</v>
+        <v>6947678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127002958</v>
+        <v>127000744</v>
       </c>
       <c r="B5" t="n">
-        <v>91621</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595135</v>
+        <v>595082</v>
       </c>
       <c r="R5" t="n">
-        <v>6948293</v>
+        <v>6948159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127000744</v>
+        <v>127002958</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>91621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595082</v>
+        <v>595135</v>
       </c>
       <c r="R7" t="n">
-        <v>6948159</v>
+        <v>6948293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127001223</v>
+        <v>127002114</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595101</v>
+        <v>595155</v>
       </c>
       <c r="R11" t="n">
-        <v>6948165</v>
+        <v>6948272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1638,11 +1638,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127002114</v>
+        <v>127001223</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,16 +1889,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1923,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595155</v>
+        <v>595101</v>
       </c>
       <c r="R14" t="n">
-        <v>6948272</v>
+        <v>6948165</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,6 +1954,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,7 +2179,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127001836</v>
+        <v>126999823</v>
       </c>
       <c r="B17" t="n">
         <v>91325</v>
@@ -2210,14 +2210,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595099</v>
+        <v>594880</v>
       </c>
       <c r="R17" t="n">
-        <v>6948188</v>
+        <v>6947896</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126999823</v>
+        <v>127001836</v>
       </c>
       <c r="B18" t="n">
         <v>91325</v>
@@ -2307,14 +2307,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594880</v>
+        <v>595099</v>
       </c>
       <c r="R18" t="n">
-        <v>6947896</v>
+        <v>6948188</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127002250</v>
+        <v>127003507</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>91621</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,39 +2685,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595207</v>
+        <v>594996</v>
       </c>
       <c r="R22" t="n">
-        <v>6948320</v>
+        <v>6948027</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,11 +2745,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2781,10 +2771,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127003507</v>
+        <v>127002250</v>
       </c>
       <c r="B23" t="n">
-        <v>91621</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2792,34 +2782,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594996</v>
+        <v>595207</v>
       </c>
       <c r="R23" t="n">
-        <v>6948027</v>
+        <v>6948320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,6 +2847,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,10 +3082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126995558</v>
+        <v>126999630</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,34 +3093,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594716</v>
+        <v>594878</v>
       </c>
       <c r="R26" t="n">
-        <v>6947567</v>
+        <v>6947857</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3153,6 +3158,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126999630</v>
+        <v>127003205</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>91621</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,39 +3200,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594878</v>
+        <v>595067</v>
       </c>
       <c r="R27" t="n">
-        <v>6947857</v>
+        <v>6948188</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,11 +3260,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127003205</v>
+        <v>127002933</v>
       </c>
       <c r="B28" t="n">
-        <v>91621</v>
+        <v>91325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595067</v>
+        <v>595226</v>
       </c>
       <c r="R28" t="n">
-        <v>6948188</v>
+        <v>6948345</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,10 +3383,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127002933</v>
+        <v>126995558</v>
       </c>
       <c r="B29" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595226</v>
+        <v>594716</v>
       </c>
       <c r="R29" t="n">
-        <v>6948345</v>
+        <v>6947567</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3480,49 +3480,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127001067</v>
+        <v>126995659</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>91290</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595082</v>
+        <v>594702</v>
       </c>
       <c r="R30" t="n">
-        <v>6948159</v>
+        <v>6947579</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3581,45 +3577,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126995659</v>
+        <v>127001067</v>
       </c>
       <c r="B31" t="n">
-        <v>91290</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594702</v>
+        <v>595082</v>
       </c>
       <c r="R31" t="n">
-        <v>6947579</v>
+        <v>6948159</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127003667</v>
+        <v>127000459</v>
       </c>
       <c r="B35" t="n">
-        <v>91621</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,34 +3995,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594896</v>
+        <v>595067</v>
       </c>
       <c r="R35" t="n">
-        <v>6947965</v>
+        <v>6948158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4060,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4081,7 +4091,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127000459</v>
+        <v>127002325</v>
       </c>
       <c r="B36" t="n">
         <v>57657</v>
@@ -4121,10 +4131,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595067</v>
+        <v>595226</v>
       </c>
       <c r="R36" t="n">
-        <v>6948158</v>
+        <v>6948345</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4188,10 +4198,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127002325</v>
+        <v>127003667</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>91621</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4199,39 +4209,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595226</v>
+        <v>594896</v>
       </c>
       <c r="R37" t="n">
-        <v>6948345</v>
+        <v>6947965</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4264,11 +4269,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127003205</v>
+        <v>126995558</v>
       </c>
       <c r="B27" t="n">
-        <v>91621</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,34 +3200,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595067</v>
+        <v>594716</v>
       </c>
       <c r="R27" t="n">
-        <v>6948188</v>
+        <v>6947567</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127002933</v>
+        <v>127003205</v>
       </c>
       <c r="B28" t="n">
-        <v>91325</v>
+        <v>91621</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595226</v>
+        <v>595067</v>
       </c>
       <c r="R28" t="n">
-        <v>6948345</v>
+        <v>6948188</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,10 +3383,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126995558</v>
+        <v>127002933</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594716</v>
+        <v>595226</v>
       </c>
       <c r="R29" t="n">
-        <v>6947567</v>
+        <v>6948345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127000744</v>
+        <v>127002958</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>91622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595082</v>
+        <v>595135</v>
       </c>
       <c r="R5" t="n">
-        <v>6948159</v>
+        <v>6948293</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
         <v>127003192</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127002958</v>
+        <v>127000744</v>
       </c>
       <c r="B7" t="n">
-        <v>91621</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595135</v>
+        <v>595082</v>
       </c>
       <c r="R7" t="n">
-        <v>6948293</v>
+        <v>6948159</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>126996109</v>
       </c>
       <c r="B8" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126995985</v>
       </c>
       <c r="B9" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127001329</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127002114</v>
+        <v>127001416</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595155</v>
+        <v>595109</v>
       </c>
       <c r="R11" t="n">
-        <v>6948272</v>
+        <v>6948171</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1638,6 +1638,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1664,7 +1669,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127001416</v>
+        <v>127001576</v>
       </c>
       <c r="B12" t="n">
         <v>57657</v>
@@ -1704,7 +1709,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595109</v>
+        <v>595101</v>
       </c>
       <c r="R12" t="n">
         <v>6948171</v>
@@ -1771,7 +1776,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127001576</v>
+        <v>127001223</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1814,7 +1819,7 @@
         <v>595101</v>
       </c>
       <c r="R13" t="n">
-        <v>6948171</v>
+        <v>6948165</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,10 +1883,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127001223</v>
+        <v>127002114</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,16 +1894,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595101</v>
+        <v>595155</v>
       </c>
       <c r="R14" t="n">
-        <v>6948165</v>
+        <v>6948272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,11 +1959,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,7 +2182,7 @@
         <v>126999823</v>
       </c>
       <c r="B17" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>127001836</v>
       </c>
       <c r="B18" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>126995868</v>
       </c>
       <c r="B19" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126998950</v>
+        <v>127002250</v>
       </c>
       <c r="B20" t="n">
         <v>57657</v>
@@ -2501,19 +2501,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594798</v>
+        <v>595207</v>
       </c>
       <c r="R20" t="n">
-        <v>6947746</v>
+        <v>6948320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
         <v>126996841</v>
       </c>
       <c r="B21" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127003507</v>
+        <v>126998950</v>
       </c>
       <c r="B22" t="n">
-        <v>91621</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,34 +2685,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594996</v>
+        <v>594798</v>
       </c>
       <c r="R22" t="n">
-        <v>6948027</v>
+        <v>6947746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2745,6 +2750,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2771,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127002250</v>
+        <v>127003507</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2782,39 +2792,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595207</v>
+        <v>594996</v>
       </c>
       <c r="R23" t="n">
-        <v>6948320</v>
+        <v>6948027</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,11 +2852,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,10 +3082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126999630</v>
+        <v>127003205</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,39 +3093,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594878</v>
+        <v>595067</v>
       </c>
       <c r="R26" t="n">
-        <v>6947857</v>
+        <v>6948188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3158,11 +3153,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3189,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126995558</v>
+        <v>127002933</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,34 +3190,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594716</v>
+        <v>595226</v>
       </c>
       <c r="R27" t="n">
-        <v>6947567</v>
+        <v>6948345</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3286,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127003205</v>
+        <v>126995558</v>
       </c>
       <c r="B28" t="n">
-        <v>91621</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,34 +3287,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595067</v>
+        <v>594716</v>
       </c>
       <c r="R28" t="n">
-        <v>6948188</v>
+        <v>6947567</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,10 +3373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127002933</v>
+        <v>126999630</v>
       </c>
       <c r="B29" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,34 +3384,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595226</v>
+        <v>594878</v>
       </c>
       <c r="R29" t="n">
-        <v>6948345</v>
+        <v>6947857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3454,6 +3449,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3483,7 +3483,7 @@
         <v>126995659</v>
       </c>
       <c r="B30" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>127001067</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>126999279</v>
       </c>
       <c r="B34" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127000459</v>
+        <v>127003667</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,39 +3995,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595067</v>
+        <v>594896</v>
       </c>
       <c r="R35" t="n">
-        <v>6948158</v>
+        <v>6947965</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4060,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4091,7 +4081,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127002325</v>
+        <v>127000459</v>
       </c>
       <c r="B36" t="n">
         <v>57657</v>
@@ -4131,10 +4121,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595226</v>
+        <v>595067</v>
       </c>
       <c r="R36" t="n">
-        <v>6948345</v>
+        <v>6948158</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4198,10 +4188,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127003667</v>
+        <v>127002325</v>
       </c>
       <c r="B37" t="n">
-        <v>91621</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4209,34 +4199,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594896</v>
+        <v>595226</v>
       </c>
       <c r="R37" t="n">
-        <v>6947965</v>
+        <v>6948345</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,6 +4264,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127003926</v>
+        <v>126997331</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594733</v>
+        <v>594788</v>
       </c>
       <c r="R3" t="n">
-        <v>6947763</v>
+        <v>6947678</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126997331</v>
+        <v>127003926</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594788</v>
+        <v>594733</v>
       </c>
       <c r="R4" t="n">
-        <v>6947678</v>
+        <v>6947763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127002250</v>
+        <v>126996841</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,39 +2481,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595207</v>
+        <v>594788</v>
       </c>
       <c r="R20" t="n">
-        <v>6948320</v>
+        <v>6947674</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2546,11 +2541,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2577,10 +2567,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126996841</v>
+        <v>126998950</v>
       </c>
       <c r="B21" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2588,34 +2578,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594788</v>
+        <v>594798</v>
       </c>
       <c r="R21" t="n">
-        <v>6947674</v>
+        <v>6947746</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,6 +2643,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2674,7 +2674,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126998950</v>
+        <v>127002250</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2705,19 +2705,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594798</v>
+        <v>595207</v>
       </c>
       <c r="R22" t="n">
-        <v>6947746</v>
+        <v>6948320</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127000523</v>
+        <v>127003926</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595067</v>
+        <v>594733</v>
       </c>
       <c r="R2" t="n">
-        <v>6948158</v>
+        <v>6947763</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126997331</v>
+        <v>127000523</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594788</v>
+        <v>595067</v>
       </c>
       <c r="R3" t="n">
-        <v>6947678</v>
+        <v>6948158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127003926</v>
+        <v>126997331</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594733</v>
+        <v>594788</v>
       </c>
       <c r="R4" t="n">
-        <v>6947763</v>
+        <v>6947678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127003192</v>
+        <v>127000744</v>
       </c>
       <c r="B6" t="n">
-        <v>91780</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595066</v>
+        <v>595082</v>
       </c>
       <c r="R6" t="n">
-        <v>6948222</v>
+        <v>6948159</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127000744</v>
+        <v>127003192</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>91780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595082</v>
+        <v>595066</v>
       </c>
       <c r="R7" t="n">
-        <v>6948159</v>
+        <v>6948222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127001416</v>
+        <v>127001472</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,36 +1573,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595109</v>
+        <v>595101</v>
       </c>
       <c r="R11" t="n">
         <v>6948171</v>
@@ -1638,11 +1633,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127001576</v>
+        <v>127000920</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,39 +1670,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595101</v>
+        <v>595083</v>
       </c>
       <c r="R12" t="n">
-        <v>6948171</v>
+        <v>6948169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,11 +1730,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1776,10 +1756,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127001223</v>
+        <v>127002114</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,16 +1767,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1816,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595101</v>
+        <v>595155</v>
       </c>
       <c r="R13" t="n">
-        <v>6948165</v>
+        <v>6948272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1883,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127002114</v>
+        <v>127001416</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,16 +1869,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1923,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595155</v>
+        <v>595109</v>
       </c>
       <c r="R14" t="n">
-        <v>6948272</v>
+        <v>6948171</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,6 +1934,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1985,10 +1965,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127001472</v>
+        <v>127001576</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,24 +1976,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
@@ -2056,6 +2041,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2082,10 +2072,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127000920</v>
+        <v>127001223</v>
       </c>
       <c r="B16" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2093,34 +2083,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595083</v>
+        <v>595101</v>
       </c>
       <c r="R16" t="n">
-        <v>6948169</v>
+        <v>6948165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,6 +2148,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2179,7 +2179,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126999823</v>
+        <v>127001836</v>
       </c>
       <c r="B17" t="n">
         <v>91326</v>
@@ -2210,14 +2210,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594880</v>
+        <v>595099</v>
       </c>
       <c r="R17" t="n">
-        <v>6947896</v>
+        <v>6948188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127001836</v>
+        <v>126999823</v>
       </c>
       <c r="B18" t="n">
         <v>91326</v>
@@ -2307,14 +2307,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595099</v>
+        <v>594880</v>
       </c>
       <c r="R18" t="n">
-        <v>6948188</v>
+        <v>6947896</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126996841</v>
+        <v>127002250</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,34 +2481,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594788</v>
+        <v>595207</v>
       </c>
       <c r="R20" t="n">
-        <v>6947674</v>
+        <v>6948320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,6 +2546,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2567,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126998950</v>
+        <v>127003507</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,39 +2588,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594798</v>
+        <v>594996</v>
       </c>
       <c r="R21" t="n">
-        <v>6947746</v>
+        <v>6948027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,11 +2648,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127002250</v>
+        <v>126996841</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,39 +2685,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595207</v>
+        <v>594788</v>
       </c>
       <c r="R22" t="n">
-        <v>6948320</v>
+        <v>6947674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,11 +2745,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2781,10 +2771,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127003507</v>
+        <v>126998950</v>
       </c>
       <c r="B23" t="n">
-        <v>91622</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2792,34 +2782,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594996</v>
+        <v>594798</v>
       </c>
       <c r="R23" t="n">
-        <v>6948027</v>
+        <v>6947746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,6 +2847,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,10 +3082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127003205</v>
+        <v>126999630</v>
       </c>
       <c r="B26" t="n">
-        <v>91622</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,34 +3093,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595067</v>
+        <v>594878</v>
       </c>
       <c r="R26" t="n">
-        <v>6948188</v>
+        <v>6947857</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3153,6 +3158,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3276,10 +3286,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126995558</v>
+        <v>127003205</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>91622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,34 +3297,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594716</v>
+        <v>595067</v>
       </c>
       <c r="R28" t="n">
-        <v>6947567</v>
+        <v>6948188</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3373,10 +3383,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126999630</v>
+        <v>126995558</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3384,39 +3394,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594878</v>
+        <v>594716</v>
       </c>
       <c r="R29" t="n">
-        <v>6947857</v>
+        <v>6947567</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,11 +3454,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3887,10 +3887,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126999279</v>
+        <v>127000459</v>
       </c>
       <c r="B34" t="n">
-        <v>88729</v>
+        <v>57657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3898,34 +3898,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594843</v>
+        <v>595067</v>
       </c>
       <c r="R34" t="n">
-        <v>6947765</v>
+        <v>6948158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3958,6 +3963,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3984,10 +3994,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127003667</v>
+        <v>127002325</v>
       </c>
       <c r="B35" t="n">
-        <v>91622</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,34 +4005,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594896</v>
+        <v>595226</v>
       </c>
       <c r="R35" t="n">
-        <v>6947965</v>
+        <v>6948345</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4070,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4081,10 +4101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127000459</v>
+        <v>127003667</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4092,39 +4112,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595067</v>
+        <v>594896</v>
       </c>
       <c r="R36" t="n">
-        <v>6948158</v>
+        <v>6947965</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4157,11 +4172,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4188,10 +4198,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127002325</v>
+        <v>126999279</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>88729</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4199,39 +4209,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595226</v>
+        <v>594843</v>
       </c>
       <c r="R37" t="n">
-        <v>6948345</v>
+        <v>6947765</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4264,11 +4269,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127003926</v>
+        <v>127000523</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594733</v>
+        <v>595067</v>
       </c>
       <c r="R2" t="n">
-        <v>6947763</v>
+        <v>6948158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127000523</v>
+        <v>126997331</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595067</v>
+        <v>594788</v>
       </c>
       <c r="R3" t="n">
-        <v>6948158</v>
+        <v>6947678</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126997331</v>
+        <v>127003926</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594788</v>
+        <v>594733</v>
       </c>
       <c r="R4" t="n">
-        <v>6947678</v>
+        <v>6947763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1364,45 +1364,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126995985</v>
+        <v>127001329</v>
       </c>
       <c r="B9" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594777</v>
+        <v>595123</v>
       </c>
       <c r="R9" t="n">
-        <v>6947651</v>
+        <v>6948167</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,49 +1465,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127001329</v>
+        <v>126995985</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595123</v>
+        <v>594777</v>
       </c>
       <c r="R10" t="n">
-        <v>6948167</v>
+        <v>6947651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127002250</v>
+        <v>127003507</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,39 +2481,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595207</v>
+        <v>594996</v>
       </c>
       <c r="R20" t="n">
-        <v>6948320</v>
+        <v>6948027</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2546,11 +2541,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2577,10 +2567,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127003507</v>
+        <v>126996841</v>
       </c>
       <c r="B21" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2588,34 +2578,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594996</v>
+        <v>594788</v>
       </c>
       <c r="R21" t="n">
-        <v>6948027</v>
+        <v>6947674</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,10 +2664,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126996841</v>
+        <v>126998950</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,34 +2675,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594788</v>
+        <v>594798</v>
       </c>
       <c r="R22" t="n">
-        <v>6947674</v>
+        <v>6947746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2745,6 +2740,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2771,7 +2771,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126998950</v>
+        <v>127002250</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2802,19 +2802,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594798</v>
+        <v>595207</v>
       </c>
       <c r="R23" t="n">
-        <v>6947746</v>
+        <v>6948320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127003507</v>
+        <v>126996841</v>
       </c>
       <c r="B20" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,34 +2481,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594996</v>
+        <v>594788</v>
       </c>
       <c r="R20" t="n">
-        <v>6948027</v>
+        <v>6947674</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126996841</v>
+        <v>127002250</v>
       </c>
       <c r="B21" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,34 +2578,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594788</v>
+        <v>595207</v>
       </c>
       <c r="R21" t="n">
-        <v>6947674</v>
+        <v>6948320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2638,6 +2643,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2664,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126998950</v>
+        <v>127003507</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,39 +2685,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594798</v>
+        <v>594996</v>
       </c>
       <c r="R22" t="n">
-        <v>6947746</v>
+        <v>6948027</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2740,11 +2745,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2771,7 +2771,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127002250</v>
+        <v>126998950</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2802,19 +2802,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595207</v>
+        <v>594798</v>
       </c>
       <c r="R23" t="n">
-        <v>6948320</v>
+        <v>6947746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127000523</v>
+        <v>126997331</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595067</v>
+        <v>594788</v>
       </c>
       <c r="R2" t="n">
-        <v>6948158</v>
+        <v>6947678</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126997331</v>
+        <v>127000523</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594788</v>
+        <v>595067</v>
       </c>
       <c r="R3" t="n">
-        <v>6947678</v>
+        <v>6948158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127003926</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127002958</v>
+        <v>127000744</v>
       </c>
       <c r="B5" t="n">
-        <v>91622</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595135</v>
+        <v>595082</v>
       </c>
       <c r="R5" t="n">
-        <v>6948293</v>
+        <v>6948159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127000744</v>
+        <v>127003192</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>91784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595082</v>
+        <v>595066</v>
       </c>
       <c r="R6" t="n">
-        <v>6948159</v>
+        <v>6948222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127003192</v>
+        <v>127002958</v>
       </c>
       <c r="B7" t="n">
-        <v>91780</v>
+        <v>91626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595066</v>
+        <v>595135</v>
       </c>
       <c r="R7" t="n">
-        <v>6948222</v>
+        <v>6948293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>126996109</v>
       </c>
       <c r="B8" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127001329</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>126995985</v>
       </c>
       <c r="B10" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127001472</v>
+        <v>127000920</v>
       </c>
       <c r="B11" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595101</v>
+        <v>595083</v>
       </c>
       <c r="R11" t="n">
-        <v>6948171</v>
+        <v>6948169</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127000920</v>
+        <v>127001472</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595083</v>
+        <v>595101</v>
       </c>
       <c r="R12" t="n">
-        <v>6948169</v>
+        <v>6948171</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127002114</v>
+        <v>127001223</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1767,16 +1767,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595155</v>
+        <v>595101</v>
       </c>
       <c r="R13" t="n">
-        <v>6948272</v>
+        <v>6948165</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,6 +1832,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127001416</v>
+        <v>127002114</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1869,16 +1874,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1898,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595109</v>
+        <v>595155</v>
       </c>
       <c r="R14" t="n">
-        <v>6948171</v>
+        <v>6948272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1934,11 +1939,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1965,10 +1965,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127001576</v>
+        <v>127001416</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595101</v>
+        <v>595109</v>
       </c>
       <c r="R15" t="n">
         <v>6948171</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127001223</v>
+        <v>127001576</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>595101</v>
       </c>
       <c r="R16" t="n">
-        <v>6948165</v>
+        <v>6948171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127001836</v>
+        <v>126999823</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,14 +2210,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595099</v>
+        <v>594880</v>
       </c>
       <c r="R17" t="n">
-        <v>6948188</v>
+        <v>6947896</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126999823</v>
+        <v>127001836</v>
       </c>
       <c r="B18" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,14 +2307,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594880</v>
+        <v>595099</v>
       </c>
       <c r="R18" t="n">
-        <v>6947896</v>
+        <v>6948188</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2376,7 +2376,7 @@
         <v>126995868</v>
       </c>
       <c r="B19" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126996841</v>
+        <v>127003507</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>91626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,34 +2481,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594788</v>
+        <v>594996</v>
       </c>
       <c r="R20" t="n">
-        <v>6947674</v>
+        <v>6948027</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127002250</v>
+        <v>126996841</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>91330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,39 +2578,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595207</v>
+        <v>594788</v>
       </c>
       <c r="R21" t="n">
-        <v>6948320</v>
+        <v>6947674</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,11 +2638,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2674,10 +2664,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127003507</v>
+        <v>126998950</v>
       </c>
       <c r="B22" t="n">
-        <v>91622</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,34 +2675,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594996</v>
+        <v>594798</v>
       </c>
       <c r="R22" t="n">
-        <v>6948027</v>
+        <v>6947746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2745,6 +2740,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2771,10 +2771,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126998950</v>
+        <v>127002250</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594798</v>
+        <v>595207</v>
       </c>
       <c r="R23" t="n">
-        <v>6947746</v>
+        <v>6948320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2881,7 +2881,7 @@
         <v>127001501</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>127001941</v>
       </c>
       <c r="B25" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>126999630</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127002933</v>
+        <v>126995558</v>
       </c>
       <c r="B27" t="n">
-        <v>91326</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,34 +3200,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595226</v>
+        <v>594716</v>
       </c>
       <c r="R27" t="n">
-        <v>6948345</v>
+        <v>6947567</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3289,7 +3289,7 @@
         <v>127003205</v>
       </c>
       <c r="B28" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,10 +3383,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126995558</v>
+        <v>127002933</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594716</v>
+        <v>595226</v>
       </c>
       <c r="R29" t="n">
-        <v>6947567</v>
+        <v>6948345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3480,45 +3480,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126995659</v>
+        <v>127001067</v>
       </c>
       <c r="B30" t="n">
-        <v>91291</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594702</v>
+        <v>595082</v>
       </c>
       <c r="R30" t="n">
-        <v>6947579</v>
+        <v>6948159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3577,49 +3581,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127001067</v>
+        <v>126995659</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>91295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595082</v>
+        <v>594702</v>
       </c>
       <c r="R31" t="n">
-        <v>6948159</v>
+        <v>6947579</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3681,7 +3681,7 @@
         <v>127000961</v>
       </c>
       <c r="B32" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>127003810</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127000459</v>
+        <v>126999279</v>
       </c>
       <c r="B34" t="n">
-        <v>57657</v>
+        <v>88733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3898,39 +3898,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595067</v>
+        <v>594843</v>
       </c>
       <c r="R34" t="n">
-        <v>6948158</v>
+        <v>6947765</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3963,11 +3958,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3994,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127002325</v>
+        <v>127003667</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>91626</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4005,39 +3995,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595226</v>
+        <v>594896</v>
       </c>
       <c r="R35" t="n">
-        <v>6948345</v>
+        <v>6947965</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4070,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4101,10 +4081,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127003667</v>
+        <v>127000459</v>
       </c>
       <c r="B36" t="n">
-        <v>91622</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4112,34 +4092,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594896</v>
+        <v>595067</v>
       </c>
       <c r="R36" t="n">
-        <v>6947965</v>
+        <v>6948158</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,6 +4157,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,10 +4188,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126999279</v>
+        <v>127002325</v>
       </c>
       <c r="B37" t="n">
-        <v>88729</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4209,34 +4199,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594843</v>
+        <v>595226</v>
       </c>
       <c r="R37" t="n">
-        <v>6947765</v>
+        <v>6948345</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,6 +4264,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4298,7 +4298,7 @@
         <v>127001802</v>
       </c>
       <c r="B38" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127000744</v>
+        <v>127003192</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>91784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595082</v>
+        <v>595066</v>
       </c>
       <c r="R5" t="n">
-        <v>6948159</v>
+        <v>6948222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127003192</v>
+        <v>127002958</v>
       </c>
       <c r="B6" t="n">
-        <v>91784</v>
+        <v>91626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595066</v>
+        <v>595135</v>
       </c>
       <c r="R6" t="n">
-        <v>6948222</v>
+        <v>6948293</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127002958</v>
+        <v>127000744</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595135</v>
+        <v>595082</v>
       </c>
       <c r="R7" t="n">
-        <v>6948293</v>
+        <v>6948159</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,49 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127001329</v>
+        <v>126995985</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595123</v>
+        <v>594777</v>
       </c>
       <c r="R9" t="n">
-        <v>6948167</v>
+        <v>6947651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,45 +1461,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126995985</v>
+        <v>127001329</v>
       </c>
       <c r="B10" t="n">
-        <v>91626</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594777</v>
+        <v>595123</v>
       </c>
       <c r="R10" t="n">
-        <v>6947651</v>
+        <v>6948167</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127000920</v>
+        <v>127001472</v>
       </c>
       <c r="B11" t="n">
         <v>80121</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595083</v>
+        <v>595101</v>
       </c>
       <c r="R11" t="n">
-        <v>6948169</v>
+        <v>6948171</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127001472</v>
+        <v>127000920</v>
       </c>
       <c r="B12" t="n">
         <v>80121</v>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595101</v>
+        <v>595083</v>
       </c>
       <c r="R12" t="n">
-        <v>6948171</v>
+        <v>6948169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127001223</v>
+        <v>127002114</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1767,16 +1767,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595101</v>
+        <v>595155</v>
       </c>
       <c r="R13" t="n">
-        <v>6948165</v>
+        <v>6948272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1863,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127002114</v>
+        <v>127001416</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,16 +1869,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1903,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595155</v>
+        <v>595109</v>
       </c>
       <c r="R14" t="n">
-        <v>6948272</v>
+        <v>6948171</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,6 +1934,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1965,7 +1965,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127001416</v>
+        <v>127001576</v>
       </c>
       <c r="B15" t="n">
         <v>57661</v>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595109</v>
+        <v>595101</v>
       </c>
       <c r="R15" t="n">
         <v>6948171</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127001576</v>
+        <v>127001223</v>
       </c>
       <c r="B16" t="n">
         <v>57661</v>
@@ -2115,7 +2115,7 @@
         <v>595101</v>
       </c>
       <c r="R16" t="n">
-        <v>6948171</v>
+        <v>6948165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127003507</v>
+        <v>126996841</v>
       </c>
       <c r="B20" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,34 +2481,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594996</v>
+        <v>594788</v>
       </c>
       <c r="R20" t="n">
-        <v>6948027</v>
+        <v>6947674</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126996841</v>
+        <v>126998950</v>
       </c>
       <c r="B21" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,34 +2578,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594788</v>
+        <v>594798</v>
       </c>
       <c r="R21" t="n">
-        <v>6947674</v>
+        <v>6947746</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2638,6 +2643,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2664,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126998950</v>
+        <v>127003507</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,39 +2685,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594798</v>
+        <v>594996</v>
       </c>
       <c r="R22" t="n">
-        <v>6947746</v>
+        <v>6948027</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2740,11 +2745,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,10 +3082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126999630</v>
+        <v>126995558</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,39 +3093,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594878</v>
+        <v>594716</v>
       </c>
       <c r="R26" t="n">
-        <v>6947857</v>
+        <v>6947567</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3158,11 +3153,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3189,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126995558</v>
+        <v>126999630</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,34 +3190,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594716</v>
+        <v>594878</v>
       </c>
       <c r="R27" t="n">
-        <v>6947567</v>
+        <v>6947857</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3260,6 +3255,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127003205</v>
+        <v>127002933</v>
       </c>
       <c r="B28" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595067</v>
+        <v>595226</v>
       </c>
       <c r="R28" t="n">
-        <v>6948188</v>
+        <v>6948345</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,10 +3383,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127002933</v>
+        <v>127003205</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,21 +3394,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3418,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595226</v>
+        <v>595067</v>
       </c>
       <c r="R29" t="n">
-        <v>6948345</v>
+        <v>6948188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127003667</v>
+        <v>127000459</v>
       </c>
       <c r="B35" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,34 +3995,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594896</v>
+        <v>595067</v>
       </c>
       <c r="R35" t="n">
-        <v>6947965</v>
+        <v>6948158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4060,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4081,7 +4091,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127000459</v>
+        <v>127002325</v>
       </c>
       <c r="B36" t="n">
         <v>57661</v>
@@ -4121,10 +4131,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595067</v>
+        <v>595226</v>
       </c>
       <c r="R36" t="n">
-        <v>6948158</v>
+        <v>6948345</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4188,10 +4198,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127002325</v>
+        <v>127003667</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4199,39 +4209,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595226</v>
+        <v>594896</v>
       </c>
       <c r="R37" t="n">
-        <v>6948345</v>
+        <v>6947965</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4264,11 +4269,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126997331</v>
+        <v>127000523</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594788</v>
+        <v>595067</v>
       </c>
       <c r="R2" t="n">
-        <v>6947678</v>
+        <v>6948158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127000523</v>
+        <v>126997331</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595067</v>
+        <v>594788</v>
       </c>
       <c r="R3" t="n">
-        <v>6948158</v>
+        <v>6947678</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127002958</v>
+        <v>127000744</v>
       </c>
       <c r="B6" t="n">
-        <v>91626</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595135</v>
+        <v>595082</v>
       </c>
       <c r="R6" t="n">
-        <v>6948293</v>
+        <v>6948159</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127000744</v>
+        <v>127002958</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>91626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595082</v>
+        <v>595135</v>
       </c>
       <c r="R7" t="n">
-        <v>6948159</v>
+        <v>6948293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,45 +1364,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126995985</v>
+        <v>127001329</v>
       </c>
       <c r="B9" t="n">
-        <v>91626</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594777</v>
+        <v>595123</v>
       </c>
       <c r="R9" t="n">
-        <v>6947651</v>
+        <v>6948167</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,49 +1465,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127001329</v>
+        <v>126995985</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595123</v>
+        <v>594777</v>
       </c>
       <c r="R10" t="n">
-        <v>6948167</v>
+        <v>6947651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127002933</v>
+        <v>127003205</v>
       </c>
       <c r="B28" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595226</v>
+        <v>595067</v>
       </c>
       <c r="R28" t="n">
-        <v>6948345</v>
+        <v>6948188</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,10 +3383,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127003205</v>
+        <v>127002933</v>
       </c>
       <c r="B29" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,21 +3394,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3418,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595067</v>
+        <v>595226</v>
       </c>
       <c r="R29" t="n">
-        <v>6948188</v>
+        <v>6948345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127000459</v>
+        <v>127003667</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,39 +3995,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595067</v>
+        <v>594896</v>
       </c>
       <c r="R35" t="n">
-        <v>6948158</v>
+        <v>6947965</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4060,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4091,7 +4081,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127002325</v>
+        <v>127000459</v>
       </c>
       <c r="B36" t="n">
         <v>57661</v>
@@ -4131,10 +4121,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595226</v>
+        <v>595067</v>
       </c>
       <c r="R36" t="n">
-        <v>6948345</v>
+        <v>6948158</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4198,10 +4188,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127003667</v>
+        <v>127002325</v>
       </c>
       <c r="B37" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4209,34 +4199,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594896</v>
+        <v>595226</v>
       </c>
       <c r="R37" t="n">
-        <v>6947965</v>
+        <v>6948345</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,6 +4264,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127000523</v>
+        <v>127003926</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595067</v>
+        <v>594733</v>
       </c>
       <c r="R2" t="n">
-        <v>6948158</v>
+        <v>6947763</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126997331</v>
+        <v>127000523</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594788</v>
+        <v>595067</v>
       </c>
       <c r="R3" t="n">
-        <v>6947678</v>
+        <v>6948158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127003926</v>
+        <v>126997331</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594733</v>
+        <v>594788</v>
       </c>
       <c r="R4" t="n">
-        <v>6947763</v>
+        <v>6947678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127003192</v>
+        <v>127000744</v>
       </c>
       <c r="B5" t="n">
-        <v>91784</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595066</v>
+        <v>595082</v>
       </c>
       <c r="R5" t="n">
-        <v>6948222</v>
+        <v>6948159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127000744</v>
+        <v>127003192</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>91784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595082</v>
+        <v>595066</v>
       </c>
       <c r="R6" t="n">
-        <v>6948159</v>
+        <v>6948222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1364,49 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127001329</v>
+        <v>126995985</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595123</v>
+        <v>594777</v>
       </c>
       <c r="R9" t="n">
-        <v>6948167</v>
+        <v>6947651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,45 +1461,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126995985</v>
+        <v>127001329</v>
       </c>
       <c r="B10" t="n">
-        <v>91626</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594777</v>
+        <v>595123</v>
       </c>
       <c r="R10" t="n">
-        <v>6947651</v>
+        <v>6948167</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126999823</v>
+        <v>127001836</v>
       </c>
       <c r="B17" t="n">
         <v>91330</v>
@@ -2210,14 +2210,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594880</v>
+        <v>595099</v>
       </c>
       <c r="R17" t="n">
-        <v>6947896</v>
+        <v>6948188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127001836</v>
+        <v>126999823</v>
       </c>
       <c r="B18" t="n">
         <v>91330</v>
@@ -2307,14 +2307,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595099</v>
+        <v>594880</v>
       </c>
       <c r="R18" t="n">
-        <v>6948188</v>
+        <v>6947896</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126996841</v>
+        <v>127002250</v>
       </c>
       <c r="B20" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,34 +2481,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594788</v>
+        <v>595207</v>
       </c>
       <c r="R20" t="n">
-        <v>6947674</v>
+        <v>6948320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,6 +2546,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2771,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127002250</v>
+        <v>126996841</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2782,39 +2792,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595207</v>
+        <v>594788</v>
       </c>
       <c r="R23" t="n">
-        <v>6948320</v>
+        <v>6947674</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,11 +2852,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,10 +3082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126995558</v>
+        <v>127003205</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>91626</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,34 +3093,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594716</v>
+        <v>595067</v>
       </c>
       <c r="R26" t="n">
-        <v>6947567</v>
+        <v>6948188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126999630</v>
+        <v>127002933</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,39 +3190,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594878</v>
+        <v>595226</v>
       </c>
       <c r="R27" t="n">
-        <v>6947857</v>
+        <v>6948345</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,11 +3250,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3286,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127003205</v>
+        <v>126995558</v>
       </c>
       <c r="B28" t="n">
-        <v>91626</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,34 +3287,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595067</v>
+        <v>594716</v>
       </c>
       <c r="R28" t="n">
-        <v>6948188</v>
+        <v>6947567</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,10 +3373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127002933</v>
+        <v>126999630</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,34 +3384,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595226</v>
+        <v>594878</v>
       </c>
       <c r="R29" t="n">
-        <v>6948345</v>
+        <v>6947857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3454,6 +3449,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,49 +3480,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127001067</v>
+        <v>126995659</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>91295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595082</v>
+        <v>594702</v>
       </c>
       <c r="R30" t="n">
-        <v>6948159</v>
+        <v>6947579</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3581,45 +3577,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126995659</v>
+        <v>127001067</v>
       </c>
       <c r="B31" t="n">
-        <v>91295</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594702</v>
+        <v>595082</v>
       </c>
       <c r="R31" t="n">
-        <v>6947579</v>
+        <v>6948159</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126999279</v>
+        <v>127000459</v>
       </c>
       <c r="B34" t="n">
-        <v>88733</v>
+        <v>57661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3898,34 +3898,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594843</v>
+        <v>595067</v>
       </c>
       <c r="R34" t="n">
-        <v>6947765</v>
+        <v>6948158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3958,6 +3963,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3984,10 +3994,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127003667</v>
+        <v>127002325</v>
       </c>
       <c r="B35" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,34 +4005,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594896</v>
+        <v>595226</v>
       </c>
       <c r="R35" t="n">
-        <v>6947965</v>
+        <v>6948345</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4070,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4081,10 +4101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127000459</v>
+        <v>127003667</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4092,39 +4112,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595067</v>
+        <v>594896</v>
       </c>
       <c r="R36" t="n">
-        <v>6948158</v>
+        <v>6947965</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4157,11 +4172,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4188,10 +4198,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127002325</v>
+        <v>126999279</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>88733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4199,39 +4209,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595226</v>
+        <v>594843</v>
       </c>
       <c r="R37" t="n">
-        <v>6948345</v>
+        <v>6947765</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4264,11 +4269,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127003926</v>
+        <v>127000523</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594733</v>
+        <v>595067</v>
       </c>
       <c r="R2" t="n">
-        <v>6947763</v>
+        <v>6948158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127000523</v>
+        <v>126997331</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595067</v>
+        <v>594788</v>
       </c>
       <c r="R3" t="n">
-        <v>6948158</v>
+        <v>6947678</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126997331</v>
+        <v>127003926</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594788</v>
+        <v>594733</v>
       </c>
       <c r="R4" t="n">
-        <v>6947678</v>
+        <v>6947763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2179,7 +2179,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127001836</v>
+        <v>126999823</v>
       </c>
       <c r="B17" t="n">
         <v>91330</v>
@@ -2210,14 +2210,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595099</v>
+        <v>594880</v>
       </c>
       <c r="R17" t="n">
-        <v>6948188</v>
+        <v>6947896</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126999823</v>
+        <v>127001836</v>
       </c>
       <c r="B18" t="n">
         <v>91330</v>
@@ -2307,14 +2307,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594880</v>
+        <v>595099</v>
       </c>
       <c r="R18" t="n">
-        <v>6947896</v>
+        <v>6948188</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126998950</v>
+        <v>127003507</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2588,39 +2588,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594798</v>
+        <v>594996</v>
       </c>
       <c r="R21" t="n">
-        <v>6947746</v>
+        <v>6948027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,11 +2648,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2684,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127003507</v>
+        <v>126996841</v>
       </c>
       <c r="B22" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2695,34 +2685,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594996</v>
+        <v>594788</v>
       </c>
       <c r="R22" t="n">
-        <v>6948027</v>
+        <v>6947674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2781,10 +2771,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126996841</v>
+        <v>126998950</v>
       </c>
       <c r="B23" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2792,34 +2782,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594788</v>
+        <v>594798</v>
       </c>
       <c r="R23" t="n">
-        <v>6947674</v>
+        <v>6947746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,6 +2847,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127000523</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126997331</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127003926</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127000744</v>
+        <v>127003192</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>91786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595082</v>
+        <v>595066</v>
       </c>
       <c r="R5" t="n">
-        <v>6948159</v>
+        <v>6948222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127003192</v>
+        <v>127002958</v>
       </c>
       <c r="B6" t="n">
-        <v>91784</v>
+        <v>91628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595066</v>
+        <v>595135</v>
       </c>
       <c r="R6" t="n">
-        <v>6948222</v>
+        <v>6948293</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127002958</v>
+        <v>127000744</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595135</v>
+        <v>595082</v>
       </c>
       <c r="R7" t="n">
-        <v>6948293</v>
+        <v>6948159</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>126996109</v>
       </c>
       <c r="B8" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,45 +1364,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126995985</v>
+        <v>127001329</v>
       </c>
       <c r="B9" t="n">
-        <v>91626</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594777</v>
+        <v>595123</v>
       </c>
       <c r="R9" t="n">
-        <v>6947651</v>
+        <v>6948167</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,49 +1465,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127001329</v>
+        <v>126995985</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>91628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595123</v>
+        <v>594777</v>
       </c>
       <c r="R10" t="n">
-        <v>6948167</v>
+        <v>6947651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127001472</v>
+        <v>127001416</v>
       </c>
       <c r="B11" t="n">
-        <v>80121</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,31 +1573,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595101</v>
+        <v>595109</v>
       </c>
       <c r="R11" t="n">
         <v>6948171</v>
@@ -1633,6 +1638,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1659,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127000920</v>
+        <v>127001576</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,34 +1680,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595083</v>
+        <v>595101</v>
       </c>
       <c r="R12" t="n">
-        <v>6948169</v>
+        <v>6948171</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,6 +1745,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1756,10 +1776,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127002114</v>
+        <v>127001223</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1767,16 +1787,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1796,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595155</v>
+        <v>595101</v>
       </c>
       <c r="R13" t="n">
-        <v>6948272</v>
+        <v>6948165</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,6 +1852,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,10 +1883,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127001416</v>
+        <v>127001472</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>80123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1869,36 +1894,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595109</v>
+        <v>595101</v>
       </c>
       <c r="R14" t="n">
         <v>6948171</v>
@@ -1934,11 +1954,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1965,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127001576</v>
+        <v>127000920</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,39 +1991,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595101</v>
+        <v>595083</v>
       </c>
       <c r="R15" t="n">
-        <v>6948171</v>
+        <v>6948169</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,11 +2051,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2072,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127001223</v>
+        <v>127002114</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,16 +2088,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2112,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595101</v>
+        <v>595155</v>
       </c>
       <c r="R16" t="n">
-        <v>6948165</v>
+        <v>6948272</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,11 +2153,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
         <v>126999823</v>
       </c>
       <c r="B17" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>127001836</v>
       </c>
       <c r="B18" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>126995868</v>
       </c>
       <c r="B19" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127002250</v>
+        <v>126998950</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2501,19 +2501,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595207</v>
+        <v>594798</v>
       </c>
       <c r="R20" t="n">
-        <v>6948320</v>
+        <v>6947746</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127003507</v>
+        <v>126996841</v>
       </c>
       <c r="B21" t="n">
-        <v>91626</v>
+        <v>91332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2588,34 +2588,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594996</v>
+        <v>594788</v>
       </c>
       <c r="R21" t="n">
-        <v>6948027</v>
+        <v>6947674</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126996841</v>
+        <v>127003507</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>91628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,34 +2685,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594788</v>
+        <v>594996</v>
       </c>
       <c r="R22" t="n">
-        <v>6947674</v>
+        <v>6948027</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2771,10 +2771,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126998950</v>
+        <v>127002250</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594798</v>
+        <v>595207</v>
       </c>
       <c r="R23" t="n">
-        <v>6947746</v>
+        <v>6948320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2881,7 +2881,7 @@
         <v>127001501</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>127001941</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127003205</v>
+        <v>127002933</v>
       </c>
       <c r="B26" t="n">
-        <v>91626</v>
+        <v>91332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595067</v>
+        <v>595226</v>
       </c>
       <c r="R26" t="n">
-        <v>6948188</v>
+        <v>6948345</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127002933</v>
+        <v>126995558</v>
       </c>
       <c r="B27" t="n">
-        <v>91330</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,34 +3190,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595226</v>
+        <v>594716</v>
       </c>
       <c r="R27" t="n">
-        <v>6948345</v>
+        <v>6947567</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126995558</v>
+        <v>126999630</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,34 +3287,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594716</v>
+        <v>594878</v>
       </c>
       <c r="R28" t="n">
-        <v>6947567</v>
+        <v>6947857</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,6 +3352,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3373,10 +3383,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126999630</v>
+        <v>127003205</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>91628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3384,39 +3394,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594878</v>
+        <v>595067</v>
       </c>
       <c r="R29" t="n">
-        <v>6947857</v>
+        <v>6948188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,11 +3454,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,45 +3480,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126995659</v>
+        <v>127001067</v>
       </c>
       <c r="B30" t="n">
-        <v>91295</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594702</v>
+        <v>595082</v>
       </c>
       <c r="R30" t="n">
-        <v>6947579</v>
+        <v>6948159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3577,49 +3581,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127001067</v>
+        <v>126995659</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>91297</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595082</v>
+        <v>594702</v>
       </c>
       <c r="R31" t="n">
-        <v>6948159</v>
+        <v>6947579</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127000961</v>
+        <v>127003810</v>
       </c>
       <c r="B32" t="n">
-        <v>80121</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3689,39 +3689,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595075</v>
+        <v>594822</v>
       </c>
       <c r="R32" t="n">
-        <v>6948146</v>
+        <v>6947827</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3754,6 +3754,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3780,10 +3785,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127003810</v>
+        <v>127000961</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>80123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3791,39 +3796,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>594822</v>
+        <v>595075</v>
       </c>
       <c r="R33" t="n">
-        <v>6947827</v>
+        <v>6948146</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3856,11 +3861,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3887,10 +3887,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127000459</v>
+        <v>126999279</v>
       </c>
       <c r="B34" t="n">
-        <v>57661</v>
+        <v>88735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3898,39 +3898,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595067</v>
+        <v>594843</v>
       </c>
       <c r="R34" t="n">
-        <v>6948158</v>
+        <v>6947765</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3963,11 +3958,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3994,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127002325</v>
+        <v>127003667</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>91628</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4005,39 +3995,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595226</v>
+        <v>594896</v>
       </c>
       <c r="R35" t="n">
-        <v>6948345</v>
+        <v>6947965</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4070,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4101,10 +4081,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127003667</v>
+        <v>127000459</v>
       </c>
       <c r="B36" t="n">
-        <v>91626</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4112,34 +4092,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594896</v>
+        <v>595067</v>
       </c>
       <c r="R36" t="n">
-        <v>6947965</v>
+        <v>6948158</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,6 +4157,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,10 +4188,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126999279</v>
+        <v>127002325</v>
       </c>
       <c r="B37" t="n">
-        <v>88733</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4209,34 +4199,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594843</v>
+        <v>595226</v>
       </c>
       <c r="R37" t="n">
-        <v>6947765</v>
+        <v>6948345</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,6 +4264,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4298,7 +4298,7 @@
         <v>127001802</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127000523</v>
+        <v>126997331</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595067</v>
+        <v>594788</v>
       </c>
       <c r="R2" t="n">
-        <v>6948158</v>
+        <v>6947678</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126997331</v>
+        <v>127000523</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594788</v>
+        <v>595067</v>
       </c>
       <c r="R3" t="n">
-        <v>6947678</v>
+        <v>6948158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127003192</v>
+        <v>127002958</v>
       </c>
       <c r="B5" t="n">
-        <v>91786</v>
+        <v>91628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595066</v>
+        <v>595135</v>
       </c>
       <c r="R5" t="n">
-        <v>6948222</v>
+        <v>6948293</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127002958</v>
+        <v>127003192</v>
       </c>
       <c r="B6" t="n">
-        <v>91628</v>
+        <v>91786</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595135</v>
+        <v>595066</v>
       </c>
       <c r="R6" t="n">
-        <v>6948293</v>
+        <v>6948222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127001416</v>
+        <v>127001472</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,36 +1573,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595109</v>
+        <v>595101</v>
       </c>
       <c r="R11" t="n">
         <v>6948171</v>
@@ -1638,11 +1633,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127001576</v>
+        <v>127000920</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,39 +1670,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595101</v>
+        <v>595083</v>
       </c>
       <c r="R12" t="n">
-        <v>6948171</v>
+        <v>6948169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,11 +1730,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1776,10 +1756,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127001223</v>
+        <v>127002114</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,16 +1767,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1816,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595101</v>
+        <v>595155</v>
       </c>
       <c r="R13" t="n">
-        <v>6948165</v>
+        <v>6948272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1883,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127001472</v>
+        <v>127001416</v>
       </c>
       <c r="B14" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,31 +1869,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595101</v>
+        <v>595109</v>
       </c>
       <c r="R14" t="n">
         <v>6948171</v>
@@ -1954,6 +1934,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1980,10 +1965,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127000920</v>
+        <v>127001576</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,34 +1976,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595083</v>
+        <v>595101</v>
       </c>
       <c r="R15" t="n">
-        <v>6948169</v>
+        <v>6948171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,6 +2041,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2077,10 +2072,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127002114</v>
+        <v>127001223</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,16 +2083,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2117,10 +2112,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595155</v>
+        <v>595101</v>
       </c>
       <c r="R16" t="n">
-        <v>6948272</v>
+        <v>6948165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,6 +2148,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2179,7 +2179,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126999823</v>
+        <v>127001836</v>
       </c>
       <c r="B17" t="n">
         <v>91332</v>
@@ -2210,14 +2210,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594880</v>
+        <v>595099</v>
       </c>
       <c r="R17" t="n">
-        <v>6947896</v>
+        <v>6948188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127001836</v>
+        <v>126999823</v>
       </c>
       <c r="B18" t="n">
         <v>91332</v>
@@ -2307,14 +2307,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595099</v>
+        <v>594880</v>
       </c>
       <c r="R18" t="n">
-        <v>6948188</v>
+        <v>6947896</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127002933</v>
+        <v>127003205</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595226</v>
+        <v>595067</v>
       </c>
       <c r="R26" t="n">
-        <v>6948345</v>
+        <v>6948188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126995558</v>
+        <v>127002933</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,34 +3190,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594716</v>
+        <v>595226</v>
       </c>
       <c r="R27" t="n">
-        <v>6947567</v>
+        <v>6948345</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126999630</v>
+        <v>126995558</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,39 +3287,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594878</v>
+        <v>594716</v>
       </c>
       <c r="R28" t="n">
-        <v>6947857</v>
+        <v>6947567</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3352,11 +3347,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3383,10 +3373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127003205</v>
+        <v>126999630</v>
       </c>
       <c r="B29" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,34 +3384,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595067</v>
+        <v>594878</v>
       </c>
       <c r="R29" t="n">
-        <v>6948188</v>
+        <v>6947857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3454,6 +3449,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,49 +3480,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127001067</v>
+        <v>126995659</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>91297</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595082</v>
+        <v>594702</v>
       </c>
       <c r="R30" t="n">
-        <v>6948159</v>
+        <v>6947579</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3581,45 +3577,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126995659</v>
+        <v>127001067</v>
       </c>
       <c r="B31" t="n">
-        <v>91297</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594702</v>
+        <v>595082</v>
       </c>
       <c r="R31" t="n">
-        <v>6947579</v>
+        <v>6948159</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127003810</v>
+        <v>127000961</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3689,39 +3689,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>594822</v>
+        <v>595075</v>
       </c>
       <c r="R32" t="n">
-        <v>6947827</v>
+        <v>6948146</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3754,11 +3754,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3785,10 +3780,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127000961</v>
+        <v>127003810</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3796,39 +3791,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595075</v>
+        <v>594822</v>
       </c>
       <c r="R33" t="n">
-        <v>6948146</v>
+        <v>6947827</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3861,6 +3856,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126997331</v>
+        <v>127000523</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594788</v>
+        <v>595067</v>
       </c>
       <c r="R2" t="n">
-        <v>6947678</v>
+        <v>6948158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127000523</v>
+        <v>127003926</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595067</v>
+        <v>594733</v>
       </c>
       <c r="R3" t="n">
-        <v>6948158</v>
+        <v>6947763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127003926</v>
+        <v>126997331</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594733</v>
+        <v>594788</v>
       </c>
       <c r="R4" t="n">
-        <v>6947763</v>
+        <v>6947678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2179,7 +2179,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127001836</v>
+        <v>126999823</v>
       </c>
       <c r="B17" t="n">
         <v>91332</v>
@@ -2210,14 +2210,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595099</v>
+        <v>594880</v>
       </c>
       <c r="R17" t="n">
-        <v>6948188</v>
+        <v>6947896</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126999823</v>
+        <v>127001836</v>
       </c>
       <c r="B18" t="n">
         <v>91332</v>
@@ -2307,14 +2307,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594880</v>
+        <v>595099</v>
       </c>
       <c r="R18" t="n">
-        <v>6947896</v>
+        <v>6948188</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126998950</v>
+        <v>127003507</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,39 +2481,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594798</v>
+        <v>594996</v>
       </c>
       <c r="R20" t="n">
-        <v>6947746</v>
+        <v>6948027</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2546,11 +2541,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,10 +2664,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127003507</v>
+        <v>126998950</v>
       </c>
       <c r="B22" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,34 +2675,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594996</v>
+        <v>594798</v>
       </c>
       <c r="R22" t="n">
-        <v>6948027</v>
+        <v>6947746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2745,6 +2740,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,10 +3082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127003205</v>
+        <v>126995558</v>
       </c>
       <c r="B26" t="n">
-        <v>91628</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,34 +3093,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595067</v>
+        <v>594716</v>
       </c>
       <c r="R26" t="n">
-        <v>6948188</v>
+        <v>6947567</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127002933</v>
+        <v>126999630</v>
       </c>
       <c r="B27" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,34 +3190,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595226</v>
+        <v>594878</v>
       </c>
       <c r="R27" t="n">
-        <v>6948345</v>
+        <v>6947857</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,6 +3255,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3276,10 +3286,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126995558</v>
+        <v>127002933</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,34 +3297,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594716</v>
+        <v>595226</v>
       </c>
       <c r="R28" t="n">
-        <v>6947567</v>
+        <v>6948345</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3373,10 +3383,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126999630</v>
+        <v>127003205</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3384,39 +3394,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594878</v>
+        <v>595067</v>
       </c>
       <c r="R29" t="n">
-        <v>6947857</v>
+        <v>6948188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,11 +3454,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127000523</v>
+        <v>126997331</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595067</v>
+        <v>594788</v>
       </c>
       <c r="R2" t="n">
-        <v>6948158</v>
+        <v>6947678</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126997331</v>
+        <v>127000523</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594788</v>
+        <v>595067</v>
       </c>
       <c r="R4" t="n">
-        <v>6947678</v>
+        <v>6948158</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127002958</v>
+        <v>127003192</v>
       </c>
       <c r="B5" t="n">
-        <v>91628</v>
+        <v>91786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595135</v>
+        <v>595066</v>
       </c>
       <c r="R5" t="n">
-        <v>6948293</v>
+        <v>6948222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127003192</v>
+        <v>127000744</v>
       </c>
       <c r="B6" t="n">
-        <v>91786</v>
+        <v>80123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595066</v>
+        <v>595082</v>
       </c>
       <c r="R6" t="n">
-        <v>6948222</v>
+        <v>6948159</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127000744</v>
+        <v>127002958</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>91628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595082</v>
+        <v>595135</v>
       </c>
       <c r="R7" t="n">
-        <v>6948159</v>
+        <v>6948293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,49 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127001329</v>
+        <v>126995985</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>91628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595123</v>
+        <v>594777</v>
       </c>
       <c r="R9" t="n">
-        <v>6948167</v>
+        <v>6947651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,45 +1461,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126995985</v>
+        <v>127001329</v>
       </c>
       <c r="B10" t="n">
-        <v>91628</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594777</v>
+        <v>595123</v>
       </c>
       <c r="R10" t="n">
-        <v>6947651</v>
+        <v>6948167</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127003507</v>
+        <v>126996841</v>
       </c>
       <c r="B20" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,34 +2481,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594996</v>
+        <v>594788</v>
       </c>
       <c r="R20" t="n">
-        <v>6948027</v>
+        <v>6947674</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126996841</v>
+        <v>127002250</v>
       </c>
       <c r="B21" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,34 +2578,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594788</v>
+        <v>595207</v>
       </c>
       <c r="R21" t="n">
-        <v>6947674</v>
+        <v>6948320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2638,6 +2643,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127002250</v>
+        <v>127003507</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2782,39 +2792,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595207</v>
+        <v>594996</v>
       </c>
       <c r="R23" t="n">
-        <v>6948320</v>
+        <v>6948027</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,11 +2852,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,10 +3082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126995558</v>
+        <v>127002933</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,34 +3093,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594716</v>
+        <v>595226</v>
       </c>
       <c r="R26" t="n">
-        <v>6947567</v>
+        <v>6948345</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126999630</v>
+        <v>126995558</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,39 +3190,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594878</v>
+        <v>594716</v>
       </c>
       <c r="R27" t="n">
-        <v>6947857</v>
+        <v>6947567</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,11 +3250,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3286,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127002933</v>
+        <v>126999630</v>
       </c>
       <c r="B28" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,34 +3287,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595226</v>
+        <v>594878</v>
       </c>
       <c r="R28" t="n">
-        <v>6948345</v>
+        <v>6947857</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,6 +3352,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4390,6 +4390,1373 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128612086</v>
+      </c>
+      <c r="B39" t="n">
+        <v>88853</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>510</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>594670</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6947624</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128612029</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>594681</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6947627</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128612379</v>
+      </c>
+      <c r="B41" t="n">
+        <v>88853</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>510</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>594681</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6947644</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128612483</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>594681</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6947627</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128612129</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>658</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>594661</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6947648</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128611231</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>594639</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6947602</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128611210</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>658</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>594639</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6947602</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128610821</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>594615</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6947581</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128612505</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80224</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>594698</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6947653</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128612333</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>594708</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6947647</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128611894</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>594661</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6947648</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128612019</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>594697</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6947614</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>( ca ) och 10 ex har blommat i år.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128611602</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>594641</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6947610</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128612495</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>594698</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6947653</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2677,7 +2677,7 @@
         <v>126998950</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2703,11 +2703,14 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
@@ -2754,7 +2757,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4392,45 +4395,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128612086</v>
+        <v>128615942</v>
       </c>
       <c r="B39" t="n">
-        <v>88853</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>594670</v>
+        <v>594837</v>
       </c>
       <c r="R39" t="n">
-        <v>6947624</v>
+        <v>6947847</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4489,10 +4496,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128612029</v>
+        <v>128613112</v>
       </c>
       <c r="B40" t="n">
-        <v>91452</v>
+        <v>57682</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4500,34 +4507,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594681</v>
+        <v>594740</v>
       </c>
       <c r="R40" t="n">
-        <v>6947627</v>
+        <v>6947720</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4586,10 +4598,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128612379</v>
+        <v>128616686</v>
       </c>
       <c r="B41" t="n">
-        <v>88853</v>
+        <v>57685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4597,34 +4609,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594681</v>
+        <v>594871</v>
       </c>
       <c r="R41" t="n">
-        <v>6947644</v>
+        <v>6947980</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4657,6 +4674,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4683,45 +4705,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128612483</v>
+        <v>128616916</v>
       </c>
       <c r="B42" t="n">
-        <v>80148</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594681</v>
+        <v>594926</v>
       </c>
       <c r="R42" t="n">
-        <v>6947627</v>
+        <v>6947997</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4754,6 +4781,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4780,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128612129</v>
+        <v>128612086</v>
       </c>
       <c r="B43" t="n">
-        <v>91748</v>
+        <v>88853</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4791,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4847,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594661</v>
+        <v>594670</v>
       </c>
       <c r="R43" t="n">
-        <v>6947648</v>
+        <v>6947624</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4877,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128611231</v>
+        <v>128617309</v>
       </c>
       <c r="B44" t="n">
-        <v>91452</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4888,34 +4920,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594639</v>
+        <v>594988</v>
       </c>
       <c r="R44" t="n">
-        <v>6947602</v>
+        <v>6948097</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4948,6 +4985,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4974,45 +5016,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128611210</v>
+        <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>91748</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594639</v>
+        <v>595032</v>
       </c>
       <c r="R45" t="n">
-        <v>6947602</v>
+        <v>6948158</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5071,32 +5117,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128610821</v>
+        <v>128620169</v>
       </c>
       <c r="B46" t="n">
-        <v>92776</v>
+        <v>91748</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5106,10 +5152,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594615</v>
+        <v>594728</v>
       </c>
       <c r="R46" t="n">
-        <v>6947581</v>
+        <v>6947608</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5168,45 +5214,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128612505</v>
+        <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>80224</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594698</v>
+        <v>595003</v>
       </c>
       <c r="R47" t="n">
-        <v>6947653</v>
+        <v>6948130</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5265,10 +5315,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128612333</v>
+        <v>128617216</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,34 +5326,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>594708</v>
+        <v>594974</v>
       </c>
       <c r="R48" t="n">
-        <v>6947647</v>
+        <v>6948058</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5362,7 +5412,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128611894</v>
+        <v>128618485</v>
       </c>
       <c r="B49" t="n">
         <v>91452</v>
@@ -5393,14 +5443,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>594661</v>
+        <v>595155</v>
       </c>
       <c r="R49" t="n">
-        <v>6947648</v>
+        <v>6948251</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,10 +5509,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128612019</v>
+        <v>128618390</v>
       </c>
       <c r="B50" t="n">
-        <v>98571</v>
+        <v>91906</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,38 +5520,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>594697</v>
+        <v>595147</v>
       </c>
       <c r="R50" t="n">
-        <v>6947614</v>
+        <v>6948380</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,11 +5580,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>( ca ) och 10 ex har blommat i år.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5565,32 +5606,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128611602</v>
+        <v>128613043</v>
       </c>
       <c r="B51" t="n">
-        <v>91906</v>
+        <v>91748</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5600,10 +5641,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594641</v>
+        <v>594755</v>
       </c>
       <c r="R51" t="n">
-        <v>6947610</v>
+        <v>6947707</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,45 +5703,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128612495</v>
+        <v>128620066</v>
       </c>
       <c r="B52" t="n">
-        <v>80217</v>
+        <v>57685</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>594698</v>
+        <v>594721</v>
       </c>
       <c r="R52" t="n">
-        <v>6947653</v>
+        <v>6947616</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5735,6 +5784,11 @@
           <t>2025-09-22</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Misstänkt äldre bohål av tretåig hackspett. 4.5 cm i diameter vilket mättes genom att klättra upp i trädet. Översta bohålet är påbörjat men inte avslutat. Det undre hålet är ett färdigt bohål. Omkring 4-5 meter ovan mark.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5756,6 +5810,6473 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128619697</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>594766</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6947633</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128618260</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>595076</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6948261</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128619086</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>594897</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6947850</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128618933</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>594920</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6947885</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128619048</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>594914</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6947844</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128616608</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>594858</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6947916</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128617173</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>594965</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6948042</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ca antal exemplar</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128613042</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>594744</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6947701</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128619552</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>594832</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6947719</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>3 Talltitor sågs och hördes</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128619204</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>594867</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6947807</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128612029</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>594681</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6947627</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128618722</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>594934</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6947911</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128612379</v>
+      </c>
+      <c r="B65" t="n">
+        <v>88853</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>510</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>594681</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6947644</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128618622</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>594967</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6947974</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128612483</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>594681</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6947627</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128618981</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>594960</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6947948</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128617726</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>595067</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6948188</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128617053</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>594946</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6948047</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128612129</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>658</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>594661</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6947648</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128616060</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>594831</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6947874</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>( ca) 120 stycken ( kan vara fler) flera antal ex blommar.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128618571</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>594982</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6947991</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128617807</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>658</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>595066</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6948222</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128617038</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>658</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>594946</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6948047</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128616855</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>594913</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6947961</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Uthackat hål ( enormt stort ) på basen av fallet träd ( gran).</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128617413</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>658</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>594983</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6948130</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128619165</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>658</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>594867</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6947807</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128616633</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>594867</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6947992</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Både färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128611210</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>658</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>594639</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6947602</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128611231</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>594639</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6947602</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128610821</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>594615</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6947581</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128619243</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>594844</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6947806</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128618550</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>595174</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6948235</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128612333</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>594708</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6947647</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128611894</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>594661</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6947648</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128617332</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>594994</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6948085</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( finns tre träd med ringhack) på platts</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128617472</v>
+      </c>
+      <c r="B88" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>594990</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6948134</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128614877</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>594799</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6947817</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128612505</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80224</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>594698</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6947653</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128619333</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>594831</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6947762</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128612019</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>594697</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6947614</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>( ca ) och 10 ex har blommat i år.</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128615259</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>594830</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6947836</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128618582</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>658</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>595147</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6948207</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128619805</v>
+      </c>
+      <c r="B95" t="n">
+        <v>88853</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>510</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>594750</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6947631</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128616883</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>594913</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6947961</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128616241</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>594837</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6947894</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ca 60 exemplar kan finnas mer.</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128614531</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>594823</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6947863</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Finns fortfarande lite sav/kåda kvar varför jag räknar dem som färska</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128615896</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>594831</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6947849</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128619481</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>594832</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6947719</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( många äldre) exemplar</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128611602</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>594641</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6947610</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128613015</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>594744</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6947701</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett ( långt ner ) på gran. Visar på lång användning av området.</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128613034</v>
+      </c>
+      <c r="B103" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>594755</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6947707</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128613693</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>594803</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6947861</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128618083</v>
+      </c>
+      <c r="B105" t="n">
+        <v>91463</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>595055</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6948245</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128612495</v>
+      </c>
+      <c r="B106" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>594698</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6947653</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128613121</v>
+      </c>
+      <c r="B107" t="n">
+        <v>56260</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>594762</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6947710</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128620477</v>
+      </c>
+      <c r="B108" t="n">
+        <v>80216</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>594716</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6947567</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128613734</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>594772</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6947803</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128615878</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>594831</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6947849</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128617160</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>594968</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6948063</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128613050</v>
+      </c>
+      <c r="B112" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>594755</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6947707</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128618964</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>594960</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6947948</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128616521</v>
+      </c>
+      <c r="B114" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>594845</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6947933</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128616565</v>
+      </c>
+      <c r="B115" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>594861</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6947929</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128617668</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Polacksbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>595032</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6948158</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -4395,49 +4395,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128615942</v>
+        <v>128612086</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>88853</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>594837</v>
+        <v>594670</v>
       </c>
       <c r="R39" t="n">
-        <v>6947847</v>
+        <v>6947624</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4496,50 +4492,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128613112</v>
+        <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594740</v>
+        <v>594837</v>
       </c>
       <c r="R40" t="n">
-        <v>6947720</v>
+        <v>6947847</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4598,10 +4593,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128616686</v>
+        <v>128613112</v>
       </c>
       <c r="B41" t="n">
-        <v>57685</v>
+        <v>57682</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4609,16 +4604,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4629,19 +4624,19 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594871</v>
+        <v>594740</v>
       </c>
       <c r="R41" t="n">
-        <v>6947980</v>
+        <v>6947720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4674,11 +4669,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4705,7 +4695,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128616916</v>
+        <v>128616686</v>
       </c>
       <c r="B42" t="n">
         <v>57685</v>
@@ -4745,10 +4735,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594926</v>
+        <v>594871</v>
       </c>
       <c r="R42" t="n">
-        <v>6947997</v>
+        <v>6947980</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,10 +4802,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128612086</v>
+        <v>128616916</v>
       </c>
       <c r="B43" t="n">
-        <v>88853</v>
+        <v>57685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,34 +4813,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594670</v>
+        <v>594926</v>
       </c>
       <c r="R43" t="n">
-        <v>6947624</v>
+        <v>6947997</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4883,6 +4878,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -8147,10 +8147,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128616855</v>
+        <v>128617413</v>
       </c>
       <c r="B76" t="n">
-        <v>57682</v>
+        <v>91748</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8158,39 +8158,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>594913</v>
+        <v>594983</v>
       </c>
       <c r="R76" t="n">
-        <v>6947961</v>
+        <v>6948130</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8223,11 +8218,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Uthackat hål ( enormt stort ) på basen av fallet träd ( gran).</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8254,7 +8244,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128617413</v>
+        <v>128619165</v>
       </c>
       <c r="B77" t="n">
         <v>91748</v>
@@ -8289,10 +8279,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>594983</v>
+        <v>594867</v>
       </c>
       <c r="R77" t="n">
-        <v>6948130</v>
+        <v>6947807</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8351,10 +8341,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128619165</v>
+        <v>128616855</v>
       </c>
       <c r="B78" t="n">
-        <v>91748</v>
+        <v>57682</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8362,34 +8352,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>594867</v>
+        <v>594913</v>
       </c>
       <c r="R78" t="n">
-        <v>6947807</v>
+        <v>6947961</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8422,6 +8417,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Uthackat hål ( enormt stort ) på basen av fallet träd ( gran).</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8953,10 +8953,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128618550</v>
+        <v>128614877</v>
       </c>
       <c r="B84" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8964,39 +8964,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>595174</v>
+        <v>594799</v>
       </c>
       <c r="R84" t="n">
-        <v>6948235</v>
+        <v>6947817</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9033,7 +9028,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9060,10 +9055,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128612333</v>
+        <v>128618550</v>
       </c>
       <c r="B85" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9071,34 +9066,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>594708</v>
+        <v>595174</v>
       </c>
       <c r="R85" t="n">
-        <v>6947647</v>
+        <v>6948235</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9131,6 +9131,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9157,32 +9162,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128611894</v>
+        <v>128612505</v>
       </c>
       <c r="B86" t="n">
-        <v>91452</v>
+        <v>80224</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9192,10 +9197,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>594661</v>
+        <v>594698</v>
       </c>
       <c r="R86" t="n">
-        <v>6947648</v>
+        <v>6947653</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9254,7 +9259,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128617332</v>
+        <v>128619333</v>
       </c>
       <c r="B87" t="n">
         <v>57685</v>
@@ -9294,10 +9299,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>594994</v>
+        <v>594831</v>
       </c>
       <c r="R87" t="n">
-        <v>6948085</v>
+        <v>6947762</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9334,7 +9339,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran ( finns tre träd med ringhack) på platts</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9361,45 +9366,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128617472</v>
+        <v>128612333</v>
       </c>
       <c r="B88" t="n">
-        <v>80148</v>
+        <v>79083</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>594990</v>
+        <v>594708</v>
       </c>
       <c r="R88" t="n">
-        <v>6948134</v>
+        <v>6947647</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9458,10 +9463,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128614877</v>
+        <v>128611894</v>
       </c>
       <c r="B89" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9469,21 +9474,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9493,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>594799</v>
+        <v>594661</v>
       </c>
       <c r="R89" t="n">
-        <v>6947817</v>
+        <v>6947648</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9529,11 +9534,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9560,45 +9560,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128612505</v>
+        <v>128617332</v>
       </c>
       <c r="B90" t="n">
-        <v>80224</v>
+        <v>57685</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>594698</v>
+        <v>594994</v>
       </c>
       <c r="R90" t="n">
-        <v>6947653</v>
+        <v>6948085</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9631,6 +9636,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( finns tre träd med ringhack) på platts</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9657,50 +9667,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128619333</v>
+        <v>128617472</v>
       </c>
       <c r="B91" t="n">
-        <v>57685</v>
+        <v>80148</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>594831</v>
+        <v>594990</v>
       </c>
       <c r="R91" t="n">
-        <v>6947762</v>
+        <v>6948134</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9733,11 +9738,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10258,7 +10258,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128616241</v>
+        <v>128615896</v>
       </c>
       <c r="B97" t="n">
         <v>98571</v>
@@ -10288,19 +10288,19 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>594837</v>
+        <v>594831</v>
       </c>
       <c r="R97" t="n">
-        <v>6947894</v>
+        <v>6947849</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10333,11 +10333,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ca 60 exemplar kan finnas mer.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10364,7 +10359,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128614531</v>
+        <v>128613015</v>
       </c>
       <c r="B98" t="n">
         <v>57685</v>
@@ -10395,7 +10390,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -10404,10 +10399,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>594823</v>
+        <v>594744</v>
       </c>
       <c r="R98" t="n">
-        <v>6947863</v>
+        <v>6947701</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10444,7 +10439,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack på gran. Finns fortfarande lite sav/kåda kvar varför jag räknar dem som färska</t>
+          <t>Äldre ringhack av tretåig hackspett ( långt ner ) på gran. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10471,10 +10466,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128615896</v>
+        <v>128613034</v>
       </c>
       <c r="B99" t="n">
-        <v>98571</v>
+        <v>91906</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10482,38 +10477,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>594831</v>
+        <v>594755</v>
       </c>
       <c r="R99" t="n">
-        <v>6947849</v>
+        <v>6947707</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10776,50 +10767,49 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128613015</v>
+        <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>594744</v>
+        <v>594837</v>
       </c>
       <c r="R102" t="n">
-        <v>6947701</v>
+        <v>6947894</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10856,7 +10846,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett ( långt ner ) på gran. Visar på lång användning av området.</t>
+          <t>Ca 60 exemplar kan finnas mer.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10883,45 +10873,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128613034</v>
+        <v>128614531</v>
       </c>
       <c r="B103" t="n">
-        <v>91906</v>
+        <v>57685</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>594755</v>
+        <v>594823</v>
       </c>
       <c r="R103" t="n">
-        <v>6947707</v>
+        <v>6947863</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10954,6 +10949,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Finns fortfarande lite sav/kåda kvar varför jag räknar dem som färska</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -2677,7 +2677,7 @@
         <v>126998950</v>
       </c>
       <c r="B22" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>128612086</v>
       </c>
       <c r="B39" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>128613112</v>
       </c>
       <c r="B41" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>128616686</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>128616916</v>
       </c>
       <c r="B43" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>128617309</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>128620169</v>
       </c>
       <c r="B46" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>128617216</v>
       </c>
       <c r="B48" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>128618485</v>
       </c>
       <c r="B49" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>128618390</v>
       </c>
       <c r="B50" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128613043</v>
       </c>
       <c r="B51" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128620066</v>
       </c>
       <c r="B52" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Misstänkt äldre bohål av tretåig hackspett. 4.5 cm i diameter vilket mättes genom att klättra upp i trädet. Översta bohålet är påbörjat men inte avslutat. Det undre hålet är ett färdigt bohål. Omkring 4-5 meter ovan mark.</t>
+          <t>Sannolikt äldre bohål av tretåig hackspett. 4.5 cm i diameter vilket mättes genom att klättra upp i trädet. Översta bohålet är påbörjat men inte avslutat. Det undre hålet är ett färdigt bohål. Omkring 4-5 meter ovan mark.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5816,7 +5816,7 @@
         <v>128619697</v>
       </c>
       <c r="B53" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>128618260</v>
       </c>
       <c r="B54" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>128619086</v>
       </c>
       <c r="B55" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>128618933</v>
       </c>
       <c r="B56" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>128619048</v>
       </c>
       <c r="B57" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128616608</v>
       </c>
       <c r="B58" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128617173</v>
       </c>
       <c r="B59" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>128613042</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>128619552</v>
       </c>
       <c r="B61" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>128619204</v>
       </c>
       <c r="B62" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>128612029</v>
       </c>
       <c r="B63" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128618722</v>
       </c>
       <c r="B64" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>128612379</v>
       </c>
       <c r="B65" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>128618622</v>
       </c>
       <c r="B66" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>128612483</v>
       </c>
       <c r="B67" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128618981</v>
       </c>
       <c r="B68" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>128617726</v>
       </c>
       <c r="B69" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>128617053</v>
       </c>
       <c r="B70" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>128612129</v>
       </c>
       <c r="B71" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128616060</v>
       </c>
       <c r="B72" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128618571</v>
       </c>
       <c r="B73" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>128617807</v>
       </c>
       <c r="B74" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>128617038</v>
       </c>
       <c r="B75" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>128617413</v>
       </c>
       <c r="B76" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>128619165</v>
       </c>
       <c r="B77" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>128616855</v>
       </c>
       <c r="B78" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>128616633</v>
       </c>
       <c r="B79" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>128611210</v>
       </c>
       <c r="B80" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>128611231</v>
       </c>
       <c r="B81" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128610821</v>
       </c>
       <c r="B82" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>128619243</v>
       </c>
       <c r="B83" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>128614877</v>
       </c>
       <c r="B84" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>128618550</v>
       </c>
       <c r="B85" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>128612505</v>
       </c>
       <c r="B86" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>128619333</v>
       </c>
       <c r="B87" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>128612333</v>
       </c>
       <c r="B88" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>128611894</v>
       </c>
       <c r="B89" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>128617332</v>
       </c>
       <c r="B90" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>128617472</v>
       </c>
       <c r="B91" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>128612019</v>
       </c>
       <c r="B92" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128615259</v>
       </c>
       <c r="B93" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128618582</v>
       </c>
       <c r="B94" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>128619805</v>
       </c>
       <c r="B95" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128616883</v>
       </c>
       <c r="B96" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>128615896</v>
       </c>
       <c r="B97" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>128613015</v>
       </c>
       <c r="B98" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>128613034</v>
       </c>
       <c r="B99" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>128619481</v>
       </c>
       <c r="B100" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>128611602</v>
       </c>
       <c r="B101" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>128614531</v>
       </c>
       <c r="B103" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>128613693</v>
       </c>
       <c r="B104" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>128618083</v>
       </c>
       <c r="B105" t="n">
-        <v>91463</v>
+        <v>91469</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>128612495</v>
       </c>
       <c r="B106" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>128613121</v>
       </c>
       <c r="B107" t="n">
-        <v>56260</v>
+        <v>56264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>128620477</v>
       </c>
       <c r="B108" t="n">
-        <v>80216</v>
+        <v>80220</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>128613734</v>
       </c>
       <c r="B109" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>128615878</v>
       </c>
       <c r="B110" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>128617160</v>
       </c>
       <c r="B111" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>128613050</v>
       </c>
       <c r="B112" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>128618964</v>
       </c>
       <c r="B113" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>128616521</v>
       </c>
       <c r="B114" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>128616565</v>
       </c>
       <c r="B115" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>128617668</v>
       </c>
       <c r="B116" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -4398,7 +4398,7 @@
         <v>128612086</v>
       </c>
       <c r="B39" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>128620169</v>
       </c>
       <c r="B46" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>128617216</v>
       </c>
       <c r="B48" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>128618485</v>
       </c>
       <c r="B49" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>128618390</v>
       </c>
       <c r="B50" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128613043</v>
       </c>
       <c r="B51" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>128619697</v>
       </c>
       <c r="B53" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>128618933</v>
       </c>
       <c r="B56" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128616608</v>
       </c>
       <c r="B58" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128617173</v>
       </c>
       <c r="B59" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>128612029</v>
       </c>
       <c r="B63" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>128612379</v>
       </c>
       <c r="B65" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128618981</v>
       </c>
       <c r="B68" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>128617053</v>
       </c>
       <c r="B70" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>128612129</v>
       </c>
       <c r="B71" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128616060</v>
       </c>
       <c r="B72" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128618571</v>
       </c>
       <c r="B73" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>128617807</v>
       </c>
       <c r="B74" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>128617038</v>
       </c>
       <c r="B75" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>128617413</v>
       </c>
       <c r="B76" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>128619165</v>
       </c>
       <c r="B77" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>128611210</v>
       </c>
       <c r="B80" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>128611231</v>
       </c>
       <c r="B81" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128610821</v>
       </c>
       <c r="B82" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>128611894</v>
       </c>
       <c r="B89" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>128612019</v>
       </c>
       <c r="B92" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128615259</v>
       </c>
       <c r="B93" t="n">
-        <v>91231</v>
+        <v>91237</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128618582</v>
       </c>
       <c r="B94" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>128619805</v>
       </c>
       <c r="B95" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>128615896</v>
       </c>
       <c r="B97" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>128613034</v>
       </c>
       <c r="B99" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>128611602</v>
       </c>
       <c r="B101" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>128613693</v>
       </c>
       <c r="B104" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>128618083</v>
       </c>
       <c r="B105" t="n">
-        <v>91469</v>
+        <v>91475</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>128613050</v>
       </c>
       <c r="B112" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>128616565</v>
       </c>
       <c r="B115" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>128617668</v>
       </c>
       <c r="B116" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4398,7 +4398,7 @@
         <v>128612086</v>
       </c>
       <c r="B39" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>128620169</v>
       </c>
       <c r="B46" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>128617216</v>
       </c>
       <c r="B48" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>128618485</v>
       </c>
       <c r="B49" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>128618390</v>
       </c>
       <c r="B50" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128613043</v>
       </c>
       <c r="B51" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>128619697</v>
       </c>
       <c r="B53" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>128618933</v>
       </c>
       <c r="B56" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128616608</v>
       </c>
       <c r="B58" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128617173</v>
       </c>
       <c r="B59" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>128613042</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>128612029</v>
       </c>
       <c r="B63" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128618722</v>
       </c>
       <c r="B64" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>128612379</v>
       </c>
       <c r="B65" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>128618622</v>
       </c>
       <c r="B66" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>128612483</v>
       </c>
       <c r="B67" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128618981</v>
       </c>
       <c r="B68" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>128617726</v>
       </c>
       <c r="B69" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>128617053</v>
       </c>
       <c r="B70" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>128612129</v>
       </c>
       <c r="B71" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128616060</v>
       </c>
       <c r="B72" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128618571</v>
       </c>
       <c r="B73" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>128617807</v>
       </c>
       <c r="B74" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>128617038</v>
       </c>
       <c r="B75" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>128617413</v>
       </c>
       <c r="B76" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>128619165</v>
       </c>
       <c r="B77" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>128611210</v>
       </c>
       <c r="B80" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>128611231</v>
       </c>
       <c r="B81" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128610821</v>
       </c>
       <c r="B82" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>128614877</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>128612505</v>
       </c>
       <c r="B86" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>128612333</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>128611894</v>
       </c>
       <c r="B89" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>128617472</v>
       </c>
       <c r="B91" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>128612019</v>
       </c>
       <c r="B92" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128615259</v>
       </c>
       <c r="B93" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128618582</v>
       </c>
       <c r="B94" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>128619805</v>
       </c>
       <c r="B95" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128616883</v>
       </c>
       <c r="B96" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>128615896</v>
       </c>
       <c r="B97" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>128613034</v>
       </c>
       <c r="B99" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>128611602</v>
       </c>
       <c r="B101" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>128613693</v>
       </c>
       <c r="B104" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>128618083</v>
       </c>
       <c r="B105" t="n">
-        <v>91475</v>
+        <v>91477</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>128612495</v>
       </c>
       <c r="B106" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>128620477</v>
       </c>
       <c r="B108" t="n">
-        <v>80220</v>
+        <v>80222</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>128613734</v>
       </c>
       <c r="B109" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>128613050</v>
       </c>
       <c r="B112" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>128616521</v>
       </c>
       <c r="B114" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>128616565</v>
       </c>
       <c r="B115" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>128617668</v>
       </c>
       <c r="B116" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12277,6 +12277,113 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128612205</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Sundsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>594709</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6947638</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -4495,7 +4495,7 @@
         <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>128619697</v>
       </c>
       <c r="B53" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128617173</v>
       </c>
       <c r="B59" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128618981</v>
       </c>
       <c r="B68" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128616060</v>
       </c>
       <c r="B72" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128618571</v>
       </c>
       <c r="B73" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>128612019</v>
       </c>
       <c r="B92" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>128615896</v>
       </c>
       <c r="B97" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>128616565</v>
       </c>
       <c r="B115" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -4495,7 +4495,7 @@
         <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>128620169</v>
       </c>
       <c r="B46" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>128617216</v>
       </c>
       <c r="B48" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>128618485</v>
       </c>
       <c r="B49" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>128618390</v>
       </c>
       <c r="B50" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128613043</v>
       </c>
       <c r="B51" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>128619697</v>
       </c>
       <c r="B53" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>128618933</v>
       </c>
       <c r="B56" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128616608</v>
       </c>
       <c r="B58" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128617173</v>
       </c>
       <c r="B59" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>128612029</v>
       </c>
       <c r="B63" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128618981</v>
       </c>
       <c r="B68" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>128617053</v>
       </c>
       <c r="B70" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>128612129</v>
       </c>
       <c r="B71" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128616060</v>
       </c>
       <c r="B72" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128618571</v>
       </c>
       <c r="B73" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>128617807</v>
       </c>
       <c r="B74" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>128617038</v>
       </c>
       <c r="B75" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>128617413</v>
       </c>
       <c r="B76" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>128619165</v>
       </c>
       <c r="B77" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>128611210</v>
       </c>
       <c r="B80" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>128611231</v>
       </c>
       <c r="B81" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128610821</v>
       </c>
       <c r="B82" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>128611894</v>
       </c>
       <c r="B89" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>128612019</v>
       </c>
       <c r="B92" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128615259</v>
       </c>
       <c r="B93" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128618582</v>
       </c>
       <c r="B94" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>128615896</v>
       </c>
       <c r="B97" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>128613034</v>
       </c>
       <c r="B99" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>128611602</v>
       </c>
       <c r="B101" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>128613693</v>
       </c>
       <c r="B104" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>128618083</v>
       </c>
       <c r="B105" t="n">
-        <v>91477</v>
+        <v>91478</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>128613050</v>
       </c>
       <c r="B112" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>128616565</v>
       </c>
       <c r="B115" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>128617668</v>
       </c>
       <c r="B116" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -2677,7 +2677,7 @@
         <v>126998950</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>128612086</v>
       </c>
       <c r="B39" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>128613112</v>
       </c>
       <c r="B41" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>128616686</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>128616916</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>128617309</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>128620169</v>
       </c>
       <c r="B46" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>128617216</v>
       </c>
       <c r="B48" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>128618485</v>
       </c>
       <c r="B49" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>128618390</v>
       </c>
       <c r="B50" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128613043</v>
       </c>
       <c r="B51" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128620066</v>
       </c>
       <c r="B52" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>128619697</v>
       </c>
       <c r="B53" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>128618260</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>128619086</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>128618933</v>
       </c>
       <c r="B56" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>128619048</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128616608</v>
       </c>
       <c r="B58" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128617173</v>
       </c>
       <c r="B59" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>128613042</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>128619552</v>
       </c>
       <c r="B61" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>128619204</v>
       </c>
       <c r="B62" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>128612029</v>
       </c>
       <c r="B63" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128618722</v>
       </c>
       <c r="B64" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>128612379</v>
       </c>
       <c r="B65" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>128618622</v>
       </c>
       <c r="B66" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>128612483</v>
       </c>
       <c r="B67" t="n">
-        <v>80154</v>
+        <v>80181</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128618981</v>
       </c>
       <c r="B68" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>128617726</v>
       </c>
       <c r="B69" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>128617053</v>
       </c>
       <c r="B70" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>128612129</v>
       </c>
       <c r="B71" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128616060</v>
       </c>
       <c r="B72" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128618571</v>
       </c>
       <c r="B73" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>128617807</v>
       </c>
       <c r="B74" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>128617038</v>
       </c>
       <c r="B75" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>128617413</v>
       </c>
       <c r="B76" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>128619165</v>
       </c>
       <c r="B77" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>128616855</v>
       </c>
       <c r="B78" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>128616633</v>
       </c>
       <c r="B79" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>128611210</v>
       </c>
       <c r="B80" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>128611231</v>
       </c>
       <c r="B81" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128610821</v>
       </c>
       <c r="B82" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>128619243</v>
       </c>
       <c r="B83" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>128614877</v>
       </c>
       <c r="B84" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>128618550</v>
       </c>
       <c r="B85" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>128612505</v>
       </c>
       <c r="B86" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>128619333</v>
       </c>
       <c r="B87" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>128612333</v>
       </c>
       <c r="B88" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>128611894</v>
       </c>
       <c r="B89" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>128617332</v>
       </c>
       <c r="B90" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>128617472</v>
       </c>
       <c r="B91" t="n">
-        <v>80154</v>
+        <v>80181</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>128612019</v>
       </c>
       <c r="B92" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128615259</v>
       </c>
       <c r="B93" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128618582</v>
       </c>
       <c r="B94" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>128619805</v>
       </c>
       <c r="B95" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128616883</v>
       </c>
       <c r="B96" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>128615896</v>
       </c>
       <c r="B97" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>128613015</v>
       </c>
       <c r="B98" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>128613034</v>
       </c>
       <c r="B99" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>128619481</v>
       </c>
       <c r="B100" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>128611602</v>
       </c>
       <c r="B101" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>128614531</v>
       </c>
       <c r="B103" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>128613693</v>
       </c>
       <c r="B104" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>128618083</v>
       </c>
       <c r="B105" t="n">
-        <v>91478</v>
+        <v>91505</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>128612495</v>
       </c>
       <c r="B106" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>128613121</v>
       </c>
       <c r="B107" t="n">
-        <v>56264</v>
+        <v>56291</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>128620477</v>
       </c>
       <c r="B108" t="n">
-        <v>80222</v>
+        <v>80249</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>128613734</v>
       </c>
       <c r="B109" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>128615878</v>
       </c>
       <c r="B110" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>128617160</v>
       </c>
       <c r="B111" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>128613050</v>
       </c>
       <c r="B112" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>128618964</v>
       </c>
       <c r="B113" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>128616521</v>
       </c>
       <c r="B114" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>128616565</v>
       </c>
       <c r="B115" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>128617668</v>
       </c>
       <c r="B116" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>128612205</v>
       </c>
       <c r="B117" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -4398,7 +4398,7 @@
         <v>128612086</v>
       </c>
       <c r="B39" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>128620169</v>
       </c>
       <c r="B46" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>128617216</v>
       </c>
       <c r="B48" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>128618485</v>
       </c>
       <c r="B49" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>128618390</v>
       </c>
       <c r="B50" t="n">
-        <v>91948</v>
+        <v>91953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128613043</v>
       </c>
       <c r="B51" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>128619697</v>
       </c>
       <c r="B53" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>128618933</v>
       </c>
       <c r="B56" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128616608</v>
       </c>
       <c r="B58" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128617173</v>
       </c>
       <c r="B59" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>128613042</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>128612029</v>
       </c>
       <c r="B63" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128618722</v>
       </c>
       <c r="B64" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>128612379</v>
       </c>
       <c r="B65" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>128618622</v>
       </c>
       <c r="B66" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>128612483</v>
       </c>
       <c r="B67" t="n">
-        <v>80181</v>
+        <v>80185</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128618981</v>
       </c>
       <c r="B68" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>128617726</v>
       </c>
       <c r="B69" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>128617053</v>
       </c>
       <c r="B70" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>128612129</v>
       </c>
       <c r="B71" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128616060</v>
       </c>
       <c r="B72" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128618571</v>
       </c>
       <c r="B73" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>128617807</v>
       </c>
       <c r="B74" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>128617038</v>
       </c>
       <c r="B75" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>128617413</v>
       </c>
       <c r="B76" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>128619165</v>
       </c>
       <c r="B77" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>128611210</v>
       </c>
       <c r="B80" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>128611231</v>
       </c>
       <c r="B81" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128610821</v>
       </c>
       <c r="B82" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>128614877</v>
       </c>
       <c r="B84" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>128612505</v>
       </c>
       <c r="B86" t="n">
-        <v>80257</v>
+        <v>80261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>128612333</v>
       </c>
       <c r="B88" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>128611894</v>
       </c>
       <c r="B89" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>128617472</v>
       </c>
       <c r="B91" t="n">
-        <v>80181</v>
+        <v>80185</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>128612019</v>
       </c>
       <c r="B92" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128615259</v>
       </c>
       <c r="B93" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128618582</v>
       </c>
       <c r="B94" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>128619805</v>
       </c>
       <c r="B95" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128616883</v>
       </c>
       <c r="B96" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>128615896</v>
       </c>
       <c r="B97" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>128613034</v>
       </c>
       <c r="B99" t="n">
-        <v>91948</v>
+        <v>91953</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>128611602</v>
       </c>
       <c r="B101" t="n">
-        <v>91948</v>
+        <v>91953</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>128613693</v>
       </c>
       <c r="B104" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>128618083</v>
       </c>
       <c r="B105" t="n">
-        <v>91505</v>
+        <v>91510</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>128612495</v>
       </c>
       <c r="B106" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>128620477</v>
       </c>
       <c r="B108" t="n">
-        <v>80249</v>
+        <v>80253</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>128613734</v>
       </c>
       <c r="B109" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>128613050</v>
       </c>
       <c r="B112" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>128616521</v>
       </c>
       <c r="B114" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>128616565</v>
       </c>
       <c r="B115" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>128617668</v>
       </c>
       <c r="B116" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -4398,7 +4398,7 @@
         <v>128612086</v>
       </c>
       <c r="B39" t="n">
-        <v>88915</v>
+        <v>88920</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>128620169</v>
       </c>
       <c r="B46" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>128617216</v>
       </c>
       <c r="B48" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>128618485</v>
       </c>
       <c r="B49" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>128618390</v>
       </c>
       <c r="B50" t="n">
-        <v>91970</v>
+        <v>91975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128613043</v>
       </c>
       <c r="B51" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>128619697</v>
       </c>
       <c r="B53" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>128618933</v>
       </c>
       <c r="B56" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128616608</v>
       </c>
       <c r="B58" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128617173</v>
       </c>
       <c r="B59" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>128613042</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>128612029</v>
       </c>
       <c r="B63" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128618722</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>128612379</v>
       </c>
       <c r="B65" t="n">
-        <v>88915</v>
+        <v>88920</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>128618622</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>128612483</v>
       </c>
       <c r="B67" t="n">
-        <v>80094</v>
+        <v>80099</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128618981</v>
       </c>
       <c r="B68" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>128617726</v>
       </c>
       <c r="B69" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>128617053</v>
       </c>
       <c r="B70" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>128612129</v>
       </c>
       <c r="B71" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128616060</v>
       </c>
       <c r="B72" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128618571</v>
       </c>
       <c r="B73" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>128617807</v>
       </c>
       <c r="B74" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>128617038</v>
       </c>
       <c r="B75" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>128617413</v>
       </c>
       <c r="B76" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>128619165</v>
       </c>
       <c r="B77" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>128611210</v>
       </c>
       <c r="B80" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>128611231</v>
       </c>
       <c r="B81" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128610821</v>
       </c>
       <c r="B82" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>128614877</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>128612505</v>
       </c>
       <c r="B86" t="n">
-        <v>80170</v>
+        <v>80175</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>128612333</v>
       </c>
       <c r="B88" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>128611894</v>
       </c>
       <c r="B89" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>128617472</v>
       </c>
       <c r="B91" t="n">
-        <v>80094</v>
+        <v>80099</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>128612019</v>
       </c>
       <c r="B92" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128615259</v>
       </c>
       <c r="B93" t="n">
-        <v>91288</v>
+        <v>91293</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128618582</v>
       </c>
       <c r="B94" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>128619805</v>
       </c>
       <c r="B95" t="n">
-        <v>88915</v>
+        <v>88920</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128616883</v>
       </c>
       <c r="B96" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>128615896</v>
       </c>
       <c r="B97" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>128613034</v>
       </c>
       <c r="B99" t="n">
-        <v>91970</v>
+        <v>91975</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>128611602</v>
       </c>
       <c r="B101" t="n">
-        <v>91970</v>
+        <v>91975</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>128613693</v>
       </c>
       <c r="B104" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>128618083</v>
       </c>
       <c r="B105" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>128612495</v>
       </c>
       <c r="B106" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>128620477</v>
       </c>
       <c r="B108" t="n">
-        <v>80162</v>
+        <v>80167</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>128613734</v>
       </c>
       <c r="B109" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>128613050</v>
       </c>
       <c r="B112" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>128616521</v>
       </c>
       <c r="B114" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>128616565</v>
       </c>
       <c r="B115" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>128617668</v>
       </c>
       <c r="B116" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -4398,7 +4398,7 @@
         <v>128612086</v>
       </c>
       <c r="B39" t="n">
-        <v>88920</v>
+        <v>88926</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>128615942</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>128617664</v>
       </c>
       <c r="B45" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>128620169</v>
       </c>
       <c r="B46" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128617592</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>128617216</v>
       </c>
       <c r="B48" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>128618485</v>
       </c>
       <c r="B49" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>128618390</v>
       </c>
       <c r="B50" t="n">
-        <v>91975</v>
+        <v>91981</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128613043</v>
       </c>
       <c r="B51" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>128619697</v>
       </c>
       <c r="B53" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>128618933</v>
       </c>
       <c r="B56" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128616608</v>
       </c>
       <c r="B58" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128617173</v>
       </c>
       <c r="B59" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>128613042</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>128612029</v>
       </c>
       <c r="B63" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128618722</v>
       </c>
       <c r="B64" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>128612379</v>
       </c>
       <c r="B65" t="n">
-        <v>88920</v>
+        <v>88926</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>128618622</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>128612483</v>
       </c>
       <c r="B67" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128618981</v>
       </c>
       <c r="B68" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>128617726</v>
       </c>
       <c r="B69" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>128617053</v>
       </c>
       <c r="B70" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>128612129</v>
       </c>
       <c r="B71" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128616060</v>
       </c>
       <c r="B72" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128618571</v>
       </c>
       <c r="B73" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>128617807</v>
       </c>
       <c r="B74" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>128617038</v>
       </c>
       <c r="B75" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>128617413</v>
       </c>
       <c r="B76" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>128619165</v>
       </c>
       <c r="B77" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>128611210</v>
       </c>
       <c r="B80" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>128611231</v>
       </c>
       <c r="B81" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>128610821</v>
       </c>
       <c r="B82" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>128614877</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>128612505</v>
       </c>
       <c r="B86" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>128612333</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>128611894</v>
       </c>
       <c r="B89" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>128617472</v>
       </c>
       <c r="B91" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>128612019</v>
       </c>
       <c r="B92" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128615259</v>
       </c>
       <c r="B93" t="n">
-        <v>91293</v>
+        <v>91299</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128618582</v>
       </c>
       <c r="B94" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>128619805</v>
       </c>
       <c r="B95" t="n">
-        <v>88920</v>
+        <v>88926</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>128616883</v>
       </c>
       <c r="B96" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>128615896</v>
       </c>
       <c r="B97" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>128613034</v>
       </c>
       <c r="B99" t="n">
-        <v>91975</v>
+        <v>91981</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>128611602</v>
       </c>
       <c r="B101" t="n">
-        <v>91975</v>
+        <v>91981</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>128616241</v>
       </c>
       <c r="B102" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>128613693</v>
       </c>
       <c r="B104" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>128618083</v>
       </c>
       <c r="B105" t="n">
-        <v>91531</v>
+        <v>91537</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>128612495</v>
       </c>
       <c r="B106" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>128620477</v>
       </c>
       <c r="B108" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>128613734</v>
       </c>
       <c r="B109" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>128613050</v>
       </c>
       <c r="B112" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>128616521</v>
       </c>
       <c r="B114" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>128616565</v>
       </c>
       <c r="B115" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>128617668</v>
       </c>
       <c r="B116" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -5706,7 +5706,7 @@
         <v>128620066</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>128612205</v>
       </c>
       <c r="B117" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12283,7 +12283,7 @@
         <v>128612205</v>
       </c>
       <c r="B117" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127003926</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>127001416</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>127001576</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127001223</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>127002250</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>126998950</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>127001501</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>126999630</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>127003810</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>127000459</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>127002325</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>128616686</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>128616916</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>128617309</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128620066</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>128618260</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>128619086</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>128619048</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>128619204</v>
       </c>
       <c r="B62" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>128616633</v>
       </c>
       <c r="B79" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>128619243</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>128618550</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>128619333</v>
       </c>
       <c r="B87" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>128617332</v>
       </c>
       <c r="B90" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>128613015</v>
       </c>
       <c r="B98" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>128619481</v>
       </c>
       <c r="B100" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>128614531</v>
       </c>
       <c r="B103" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>128615878</v>
       </c>
       <c r="B110" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>128617160</v>
       </c>
       <c r="B111" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>128618964</v>
       </c>
       <c r="B113" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>128612205</v>
       </c>
       <c r="B117" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127003926</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>127001416</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>127001576</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127001223</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>127002250</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>126998950</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>127001501</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>126999630</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>127003810</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>127000459</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>127002325</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>128616686</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>128616916</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>128617309</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128620066</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>128618260</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>128619086</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>128619048</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>128619204</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>128616633</v>
       </c>
       <c r="B79" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>128619243</v>
       </c>
       <c r="B83" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>128618550</v>
       </c>
       <c r="B85" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>128619333</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>128617332</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>128613015</v>
       </c>
       <c r="B98" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>128619481</v>
       </c>
       <c r="B100" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>128614531</v>
       </c>
       <c r="B103" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>128615878</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>128617160</v>
       </c>
       <c r="B111" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>128618964</v>
       </c>
       <c r="B113" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>128612205</v>
       </c>
       <c r="B117" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126997331</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127003926</v>
+        <v>127000523</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>80114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594733</v>
+        <v>595067</v>
       </c>
       <c r="R3" t="n">
-        <v>6947763</v>
+        <v>6948158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127000523</v>
+        <v>127003926</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>57741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595067</v>
+        <v>594733</v>
       </c>
       <c r="R4" t="n">
-        <v>6948158</v>
+        <v>6947763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>127003192</v>
       </c>
       <c r="B5" t="n">
-        <v>91786</v>
+        <v>91773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127000744</v>
+        <v>127002958</v>
       </c>
       <c r="B6" t="n">
-        <v>80123</v>
+        <v>91615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595082</v>
+        <v>595135</v>
       </c>
       <c r="R6" t="n">
-        <v>6948159</v>
+        <v>6948293</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127002958</v>
+        <v>127000744</v>
       </c>
       <c r="B7" t="n">
-        <v>91628</v>
+        <v>80114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595135</v>
+        <v>595082</v>
       </c>
       <c r="R7" t="n">
-        <v>6948293</v>
+        <v>6948159</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>126996109</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
+        <v>91615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126995985</v>
       </c>
       <c r="B9" t="n">
-        <v>91628</v>
+        <v>91615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127001329</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>127001472</v>
       </c>
       <c r="B11" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127000920</v>
+        <v>127001416</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>57741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,34 +1670,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595083</v>
+        <v>595109</v>
       </c>
       <c r="R12" t="n">
-        <v>6948169</v>
+        <v>6948171</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,6 +1735,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1756,10 +1766,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127002114</v>
+        <v>127001576</v>
       </c>
       <c r="B13" t="n">
-        <v>57660</v>
+        <v>57741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1767,16 +1777,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1796,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595155</v>
+        <v>595101</v>
       </c>
       <c r="R13" t="n">
-        <v>6948272</v>
+        <v>6948171</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,6 +1842,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,7 +1873,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127001416</v>
+        <v>127001223</v>
       </c>
       <c r="B14" t="n">
         <v>57741</v>
@@ -1898,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595109</v>
+        <v>595101</v>
       </c>
       <c r="R14" t="n">
-        <v>6948171</v>
+        <v>6948165</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127001576</v>
+        <v>127000920</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,39 +1991,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595101</v>
+        <v>595083</v>
       </c>
       <c r="R15" t="n">
-        <v>6948171</v>
+        <v>6948169</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,11 +2051,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2072,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127001223</v>
+        <v>127002114</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,16 +2088,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2112,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595101</v>
+        <v>595155</v>
       </c>
       <c r="R16" t="n">
-        <v>6948165</v>
+        <v>6948272</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,11 +2153,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
         <v>126999823</v>
       </c>
       <c r="B17" t="n">
-        <v>91332</v>
+        <v>91319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>127001836</v>
       </c>
       <c r="B18" t="n">
-        <v>91332</v>
+        <v>91319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>126995868</v>
       </c>
       <c r="B19" t="n">
-        <v>97327</v>
+        <v>97314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126996841</v>
+        <v>126998950</v>
       </c>
       <c r="B20" t="n">
-        <v>91332</v>
+        <v>57741</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,34 +2481,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594788</v>
+        <v>594798</v>
       </c>
       <c r="R20" t="n">
-        <v>6947674</v>
+        <v>6947746</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,6 +2549,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2567,10 +2580,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127002250</v>
+        <v>127003507</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>91615</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,39 +2591,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595207</v>
+        <v>594996</v>
       </c>
       <c r="R21" t="n">
-        <v>6948320</v>
+        <v>6948027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,11 +2651,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2674,10 +2677,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126998950</v>
+        <v>126996841</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>91319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,42 +2688,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594798</v>
+        <v>594788</v>
       </c>
       <c r="R22" t="n">
-        <v>6947746</v>
+        <v>6947674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,11 +2748,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2784,10 +2774,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127003507</v>
+        <v>127002250</v>
       </c>
       <c r="B23" t="n">
-        <v>91628</v>
+        <v>57741</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,34 +2785,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594996</v>
+        <v>595207</v>
       </c>
       <c r="R23" t="n">
-        <v>6948027</v>
+        <v>6948320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2855,6 +2850,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2991,7 +2991,7 @@
         <v>127001941</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3085,10 +3085,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127002933</v>
+        <v>126995558</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3096,34 +3096,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595226</v>
+        <v>594716</v>
       </c>
       <c r="R26" t="n">
-        <v>6948345</v>
+        <v>6947567</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126995558</v>
+        <v>127002933</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>91319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3193,34 +3193,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594716</v>
+        <v>595226</v>
       </c>
       <c r="R27" t="n">
-        <v>6947567</v>
+        <v>6948345</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126999630</v>
+        <v>127003205</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>91615</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3290,39 +3290,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594878</v>
+        <v>595067</v>
       </c>
       <c r="R28" t="n">
-        <v>6947857</v>
+        <v>6948188</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,11 +3350,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3386,10 +3376,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127003205</v>
+        <v>126999630</v>
       </c>
       <c r="B29" t="n">
-        <v>91628</v>
+        <v>57741</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,34 +3387,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595067</v>
+        <v>594878</v>
       </c>
       <c r="R29" t="n">
-        <v>6948188</v>
+        <v>6947857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3457,6 +3452,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3486,7 +3486,7 @@
         <v>126995659</v>
       </c>
       <c r="B30" t="n">
-        <v>91297</v>
+        <v>91284</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>127001067</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127000961</v>
+        <v>127003810</v>
       </c>
       <c r="B32" t="n">
-        <v>80123</v>
+        <v>57741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3692,39 +3692,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595075</v>
+        <v>594822</v>
       </c>
       <c r="R32" t="n">
-        <v>6948146</v>
+        <v>6947827</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3757,6 +3757,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3783,10 +3788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127003810</v>
+        <v>127000961</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,39 +3799,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>594822</v>
+        <v>595075</v>
       </c>
       <c r="R33" t="n">
-        <v>6947827</v>
+        <v>6948146</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,11 +3864,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3890,10 +3890,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126999279</v>
+        <v>127003667</v>
       </c>
       <c r="B34" t="n">
-        <v>88735</v>
+        <v>91615</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3901,34 +3901,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundsjöåsen, Mpd</t>
+          <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594843</v>
+        <v>594896</v>
       </c>
       <c r="R34" t="n">
-        <v>6947765</v>
+        <v>6947965</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127003667</v>
+        <v>127002325</v>
       </c>
       <c r="B35" t="n">
-        <v>91628</v>
+        <v>57741</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3998,34 +3998,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Polacksbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594896</v>
+        <v>595226</v>
       </c>
       <c r="R35" t="n">
-        <v>6947965</v>
+        <v>6948345</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4058,6 +4063,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4084,10 +4094,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127000459</v>
+        <v>126999279</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>88722</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4095,39 +4105,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Polacksbäcken, Mpd</t>
+          <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595067</v>
+        <v>594843</v>
       </c>
       <c r="R36" t="n">
-        <v>6948158</v>
+        <v>6947765</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4160,11 +4165,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4191,7 +4191,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127002325</v>
+        <v>127000459</v>
       </c>
       <c r="B37" t="n">
         <v>57741</v>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595226</v>
+        <v>595067</v>
       </c>
       <c r="R37" t="n">
-        <v>6948345</v>
+        <v>6948158</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
         <v>127001802</v>
       </c>
       <c r="B38" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12494,10 +12494,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133312232</v>
+        <v>133312291</v>
       </c>
       <c r="B119" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>594755</v>
+        <v>594753</v>
       </c>
       <c r="R119" t="n">
-        <v>6947677</v>
+        <v>6947749</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12601,10 +12601,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133312291</v>
+        <v>133312232</v>
       </c>
       <c r="B120" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12612,21 +12612,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>594753</v>
+        <v>594755</v>
       </c>
       <c r="R120" t="n">
-        <v>6947749</v>
+        <v>6947677</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12708,32 +12708,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312200</v>
+        <v>133312293</v>
       </c>
       <c r="B121" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594692</v>
+        <v>594745</v>
       </c>
       <c r="R121" t="n">
-        <v>6947605</v>
+        <v>6947738</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,32 +12815,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312241</v>
+        <v>133312200</v>
       </c>
       <c r="B122" t="n">
-        <v>79952</v>
+        <v>75433</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594784</v>
+        <v>594692</v>
       </c>
       <c r="R122" t="n">
-        <v>6947732</v>
+        <v>6947605</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,32 +12922,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312205</v>
+        <v>133312241</v>
       </c>
       <c r="B123" t="n">
-        <v>75433</v>
+        <v>79952</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594702</v>
+        <v>594784</v>
       </c>
       <c r="R123" t="n">
-        <v>6947615</v>
+        <v>6947732</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,32 +13029,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312229</v>
+        <v>133312205</v>
       </c>
       <c r="B124" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594755</v>
+        <v>594702</v>
       </c>
       <c r="R124" t="n">
-        <v>6947668</v>
+        <v>6947615</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,10 +13136,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312293</v>
+        <v>133312229</v>
       </c>
       <c r="B125" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13147,21 +13147,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,13 +13171,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594745</v>
+        <v>594755</v>
       </c>
       <c r="R125" t="n">
-        <v>6947738</v>
+        <v>6947668</v>
       </c>
       <c r="S125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13457,32 +13457,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312184</v>
+        <v>133312257</v>
       </c>
       <c r="B128" t="n">
-        <v>75433</v>
+        <v>79365</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,10 +13492,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594713</v>
+        <v>594820</v>
       </c>
       <c r="R128" t="n">
-        <v>6947589</v>
+        <v>6947705</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13564,10 +13564,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312246</v>
+        <v>133312263</v>
       </c>
       <c r="B129" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13575,21 +13575,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,13 +13599,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594810</v>
+        <v>594826</v>
       </c>
       <c r="R129" t="n">
-        <v>6947725</v>
+        <v>6947773</v>
       </c>
       <c r="S129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,7 +13644,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13671,32 +13676,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312263</v>
+        <v>133312184</v>
       </c>
       <c r="B130" t="n">
-        <v>57955</v>
+        <v>75433</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13706,10 +13711,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594826</v>
+        <v>594713</v>
       </c>
       <c r="R130" t="n">
-        <v>6947773</v>
+        <v>6947589</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13741,7 +13746,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13751,12 +13756,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13783,10 +13783,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312257</v>
+        <v>133312246</v>
       </c>
       <c r="B131" t="n">
-        <v>79365</v>
+        <v>79952</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13794,21 +13794,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13818,13 +13818,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594820</v>
+        <v>594810</v>
       </c>
       <c r="R131" t="n">
-        <v>6947705</v>
+        <v>6947725</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13890,10 +13890,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312305</v>
+        <v>133312247</v>
       </c>
       <c r="B132" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13901,21 +13901,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,13 +13925,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594707</v>
+        <v>594801</v>
       </c>
       <c r="R132" t="n">
-        <v>6947692</v>
+        <v>6947716</v>
       </c>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312247</v>
+        <v>133312244</v>
       </c>
       <c r="B133" t="n">
-        <v>92217</v>
+        <v>57145</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594801</v>
+        <v>594797</v>
       </c>
       <c r="R133" t="n">
-        <v>6947716</v>
+        <v>6947735</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,7 +14077,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14104,32 +14109,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312244</v>
+        <v>133312305</v>
       </c>
       <c r="B134" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14139,13 +14144,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594797</v>
+        <v>594707</v>
       </c>
       <c r="R134" t="n">
-        <v>6947735</v>
+        <v>6947692</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14174,7 +14179,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14184,12 +14189,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312320</v>
+        <v>133312226</v>
       </c>
       <c r="B140" t="n">
-        <v>79365</v>
+        <v>5199</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,10 +14799,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594653</v>
+        <v>594755</v>
       </c>
       <c r="R140" t="n">
-        <v>6947566</v>
+        <v>6947670</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312297</v>
+        <v>133312320</v>
       </c>
       <c r="B141" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594737</v>
+        <v>594653</v>
       </c>
       <c r="R141" t="n">
-        <v>6947721</v>
+        <v>6947566</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14978,32 +14978,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133312226</v>
+        <v>133312272</v>
       </c>
       <c r="B142" t="n">
-        <v>5199</v>
+        <v>83315</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>594755</v>
+        <v>594856</v>
       </c>
       <c r="R142" t="n">
-        <v>6947670</v>
+        <v>6947779</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15085,10 +15085,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312272</v>
+        <v>133312297</v>
       </c>
       <c r="B143" t="n">
-        <v>83315</v>
+        <v>91918</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15096,21 +15096,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,13 +15120,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594856</v>
+        <v>594737</v>
       </c>
       <c r="R143" t="n">
-        <v>6947779</v>
+        <v>6947721</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15406,7 +15406,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133312252</v>
+        <v>133312181</v>
       </c>
       <c r="B146" t="n">
         <v>91918</v>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>594811</v>
+        <v>594723</v>
       </c>
       <c r="R146" t="n">
-        <v>6947698</v>
+        <v>6947583</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15513,10 +15513,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133312181</v>
+        <v>133312250</v>
       </c>
       <c r="B147" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15524,21 +15524,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15548,10 +15548,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>594723</v>
+        <v>594805</v>
       </c>
       <c r="R147" t="n">
-        <v>6947583</v>
+        <v>6947701</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15620,7 +15620,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133312250</v>
+        <v>133312304</v>
       </c>
       <c r="B148" t="n">
         <v>92217</v>
@@ -15655,7 +15655,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>594805</v>
+        <v>594716</v>
       </c>
       <c r="R148" t="n">
         <v>6947701</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15727,10 +15727,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133312304</v>
+        <v>133312288</v>
       </c>
       <c r="B149" t="n">
-        <v>92217</v>
+        <v>79952</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15738,21 +15738,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>594716</v>
+        <v>594771</v>
       </c>
       <c r="R149" t="n">
-        <v>6947701</v>
+        <v>6947766</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15834,10 +15834,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133312288</v>
+        <v>133312252</v>
       </c>
       <c r="B150" t="n">
-        <v>79952</v>
+        <v>91918</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15845,21 +15845,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>594771</v>
+        <v>594811</v>
       </c>
       <c r="R150" t="n">
-        <v>6947766</v>
+        <v>6947698</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15941,10 +15941,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133312186</v>
+        <v>133312303</v>
       </c>
       <c r="B151" t="n">
-        <v>75433</v>
+        <v>80466</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15952,21 +15952,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6426</v>
+        <v>6461</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15976,13 +15976,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>594705</v>
+        <v>594701</v>
       </c>
       <c r="R151" t="n">
-        <v>6947589</v>
+        <v>6947707</v>
       </c>
       <c r="S151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16048,10 +16048,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312271</v>
+        <v>133312218</v>
       </c>
       <c r="B152" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16059,21 +16059,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16083,10 +16083,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594798</v>
+        <v>594717</v>
       </c>
       <c r="R152" t="n">
-        <v>6947776</v>
+        <v>6947668</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16128,7 +16128,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16155,32 +16160,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312218</v>
+        <v>133312186</v>
       </c>
       <c r="B153" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16190,13 +16195,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594717</v>
+        <v>594705</v>
       </c>
       <c r="R153" t="n">
-        <v>6947668</v>
+        <v>6947589</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16225,7 +16230,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16235,12 +16240,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16267,10 +16267,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133312189</v>
+        <v>133312271</v>
       </c>
       <c r="B154" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16278,21 +16278,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16302,13 +16302,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>594688</v>
+        <v>594798</v>
       </c>
       <c r="R154" t="n">
-        <v>6947584</v>
+        <v>6947776</v>
       </c>
       <c r="S154" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16374,32 +16374,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133312303</v>
+        <v>133312189</v>
       </c>
       <c r="B155" t="n">
-        <v>80466</v>
+        <v>83181</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16409,13 +16409,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>594701</v>
+        <v>594688</v>
       </c>
       <c r="R155" t="n">
-        <v>6947707</v>
+        <v>6947584</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16909,10 +16909,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133312306</v>
+        <v>133312198</v>
       </c>
       <c r="B160" t="n">
-        <v>80342</v>
+        <v>75433</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16920,21 +16920,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16944,13 +16944,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>594711</v>
+        <v>594683</v>
       </c>
       <c r="R160" t="n">
-        <v>6947680</v>
+        <v>6947603</v>
       </c>
       <c r="S160" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17016,10 +17016,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133312198</v>
+        <v>133312306</v>
       </c>
       <c r="B161" t="n">
-        <v>75433</v>
+        <v>80342</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17027,21 +17027,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17051,13 +17051,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>594683</v>
+        <v>594711</v>
       </c>
       <c r="R161" t="n">
-        <v>6947603</v>
+        <v>6947680</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17337,10 +17337,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>133312279</v>
+        <v>133312203</v>
       </c>
       <c r="B164" t="n">
-        <v>92217</v>
+        <v>83181</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17348,21 +17348,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17372,10 +17372,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>594835</v>
+        <v>594694</v>
       </c>
       <c r="R164" t="n">
-        <v>6947822</v>
+        <v>6947611</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133312203</v>
+        <v>133312279</v>
       </c>
       <c r="B165" t="n">
-        <v>83181</v>
+        <v>92217</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17455,21 +17455,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>594694</v>
+        <v>594835</v>
       </c>
       <c r="R165" t="n">
-        <v>6947611</v>
+        <v>6947822</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17765,10 +17765,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312216</v>
+        <v>133312313</v>
       </c>
       <c r="B168" t="n">
-        <v>92641</v>
+        <v>80474</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17776,21 +17776,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594730</v>
+        <v>594697</v>
       </c>
       <c r="R168" t="n">
-        <v>6947646</v>
+        <v>6947661</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312313</v>
+        <v>133312259</v>
       </c>
       <c r="B169" t="n">
-        <v>80474</v>
+        <v>79952</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594697</v>
+        <v>594814</v>
       </c>
       <c r="R169" t="n">
-        <v>6947661</v>
+        <v>6947723</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,32 +17979,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312259</v>
+        <v>133312216</v>
       </c>
       <c r="B170" t="n">
-        <v>79952</v>
+        <v>92641</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>3298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594814</v>
+        <v>594730</v>
       </c>
       <c r="R170" t="n">
-        <v>6947723</v>
+        <v>6947646</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18193,32 +18193,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312312</v>
+        <v>133312319</v>
       </c>
       <c r="B172" t="n">
-        <v>80398</v>
+        <v>91918</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,13 +18228,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594697</v>
+        <v>594662</v>
       </c>
       <c r="R172" t="n">
-        <v>6947661</v>
+        <v>6947577</v>
       </c>
       <c r="S172" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18300,32 +18300,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312319</v>
+        <v>133312312</v>
       </c>
       <c r="B173" t="n">
-        <v>91918</v>
+        <v>80398</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>594662</v>
+        <v>594697</v>
       </c>
       <c r="R173" t="n">
-        <v>6947577</v>
+        <v>6947661</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18407,32 +18407,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133312308</v>
+        <v>133312243</v>
       </c>
       <c r="B174" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>594707</v>
+        <v>594794</v>
       </c>
       <c r="R174" t="n">
-        <v>6947669</v>
+        <v>6947729</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18514,10 +18514,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312212</v>
+        <v>133312268</v>
       </c>
       <c r="B175" t="n">
-        <v>91932</v>
+        <v>57955</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594721</v>
+        <v>594805</v>
       </c>
       <c r="R175" t="n">
-        <v>6947646</v>
+        <v>6947762</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,7 +18594,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18621,10 +18626,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312243</v>
+        <v>133312212</v>
       </c>
       <c r="B176" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18632,21 +18637,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18656,10 +18661,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594794</v>
+        <v>594721</v>
       </c>
       <c r="R176" t="n">
-        <v>6947729</v>
+        <v>6947646</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18691,7 +18696,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18701,7 +18706,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18728,32 +18733,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312268</v>
+        <v>133312308</v>
       </c>
       <c r="B177" t="n">
-        <v>57955</v>
+        <v>75433</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18763,10 +18768,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594805</v>
+        <v>594707</v>
       </c>
       <c r="R177" t="n">
-        <v>6947762</v>
+        <v>6947669</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18798,7 +18803,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18808,12 +18813,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20124,32 +20124,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312197</v>
+        <v>133312266</v>
       </c>
       <c r="B190" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20159,10 +20159,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594687</v>
+        <v>594820</v>
       </c>
       <c r="R190" t="n">
-        <v>6947597</v>
+        <v>6947773</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,32 +20231,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312318</v>
+        <v>133312197</v>
       </c>
       <c r="B191" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20266,7 +20266,7 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594678</v>
+        <v>594687</v>
       </c>
       <c r="R191" t="n">
         <v>6947597</v>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,32 +20338,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312317</v>
+        <v>133312318</v>
       </c>
       <c r="B192" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,13 +20373,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594682</v>
+        <v>594678</v>
       </c>
       <c r="R192" t="n">
-        <v>6947610</v>
+        <v>6947597</v>
       </c>
       <c r="S192" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312289</v>
+        <v>133312317</v>
       </c>
       <c r="B193" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,13 +20480,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594777</v>
+        <v>594682</v>
       </c>
       <c r="R193" t="n">
-        <v>6947757</v>
+        <v>6947610</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20552,7 +20552,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133312266</v>
+        <v>133312225</v>
       </c>
       <c r="B194" t="n">
         <v>91918</v>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>594820</v>
+        <v>594757</v>
       </c>
       <c r="R194" t="n">
-        <v>6947773</v>
+        <v>6947666</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20659,10 +20659,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133312225</v>
+        <v>133312289</v>
       </c>
       <c r="B195" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20670,21 +20670,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20694,10 +20694,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>594757</v>
+        <v>594777</v>
       </c>
       <c r="R195" t="n">
-        <v>6947666</v>
+        <v>6947757</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312219</v>
+        <v>133312215</v>
       </c>
       <c r="B196" t="n">
-        <v>91932</v>
+        <v>92217</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594728</v>
+        <v>594730</v>
       </c>
       <c r="R196" t="n">
-        <v>6947667</v>
+        <v>6947645</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,7 +20873,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312215</v>
+        <v>133312224</v>
       </c>
       <c r="B197" t="n">
         <v>92217</v>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594730</v>
+        <v>594755</v>
       </c>
       <c r="R197" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,10 +20980,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312224</v>
+        <v>133312219</v>
       </c>
       <c r="B198" t="n">
-        <v>92217</v>
+        <v>91932</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20991,21 +20991,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21015,7 +21015,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594755</v>
+        <v>594728</v>
       </c>
       <c r="R198" t="n">
         <v>6947667</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD198" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12387,10 +12387,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133312282</v>
+        <v>133312232</v>
       </c>
       <c r="B118" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>594775</v>
+        <v>594755</v>
       </c>
       <c r="R118" t="n">
-        <v>6947806</v>
+        <v>6947677</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12494,7 +12494,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133312291</v>
+        <v>133312282</v>
       </c>
       <c r="B119" t="n">
         <v>79365</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>594753</v>
+        <v>594775</v>
       </c>
       <c r="R119" t="n">
-        <v>6947749</v>
+        <v>6947806</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12601,10 +12601,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133312232</v>
+        <v>133312291</v>
       </c>
       <c r="B120" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12612,21 +12612,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>594755</v>
+        <v>594753</v>
       </c>
       <c r="R120" t="n">
-        <v>6947677</v>
+        <v>6947749</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12708,10 +12708,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312293</v>
+        <v>133312229</v>
       </c>
       <c r="B121" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12719,21 +12719,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594745</v>
+        <v>594755</v>
       </c>
       <c r="R121" t="n">
-        <v>6947738</v>
+        <v>6947668</v>
       </c>
       <c r="S121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,32 +12815,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312200</v>
+        <v>133312284</v>
       </c>
       <c r="B122" t="n">
-        <v>75433</v>
+        <v>91868</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6426</v>
+        <v>112</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594692</v>
+        <v>594757</v>
       </c>
       <c r="R122" t="n">
-        <v>6947605</v>
+        <v>6947805</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,10 +12922,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312241</v>
+        <v>133312293</v>
       </c>
       <c r="B123" t="n">
-        <v>79952</v>
+        <v>91918</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12933,21 +12933,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,13 +12957,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594784</v>
+        <v>594745</v>
       </c>
       <c r="R123" t="n">
-        <v>6947732</v>
+        <v>6947738</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,32 +13029,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312205</v>
+        <v>133312274</v>
       </c>
       <c r="B124" t="n">
-        <v>75433</v>
+        <v>92217</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594702</v>
+        <v>594857</v>
       </c>
       <c r="R124" t="n">
-        <v>6947615</v>
+        <v>6947775</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312229</v>
+        <v>133312200</v>
       </c>
       <c r="B125" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594755</v>
+        <v>594692</v>
       </c>
       <c r="R125" t="n">
-        <v>6947668</v>
+        <v>6947605</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,10 +13243,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312274</v>
+        <v>133312241</v>
       </c>
       <c r="B126" t="n">
-        <v>92217</v>
+        <v>79952</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,21 +13254,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594857</v>
+        <v>594784</v>
       </c>
       <c r="R126" t="n">
-        <v>6947775</v>
+        <v>6947732</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,32 +13350,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312284</v>
+        <v>133312205</v>
       </c>
       <c r="B127" t="n">
-        <v>91868</v>
+        <v>75433</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>112</v>
+        <v>6426</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594757</v>
+        <v>594702</v>
       </c>
       <c r="R127" t="n">
-        <v>6947805</v>
+        <v>6947615</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13457,10 +13457,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312257</v>
+        <v>133312263</v>
       </c>
       <c r="B128" t="n">
-        <v>79365</v>
+        <v>57955</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13468,21 +13468,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,10 +13492,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594820</v>
+        <v>594826</v>
       </c>
       <c r="R128" t="n">
-        <v>6947705</v>
+        <v>6947773</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,7 +13537,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13564,10 +13569,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312263</v>
+        <v>133312257</v>
       </c>
       <c r="B129" t="n">
-        <v>57955</v>
+        <v>79365</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13575,21 +13580,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,10 +13604,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594826</v>
+        <v>594820</v>
       </c>
       <c r="R129" t="n">
-        <v>6947773</v>
+        <v>6947705</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13634,7 +13639,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,12 +13649,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312244</v>
+        <v>133312305</v>
       </c>
       <c r="B133" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,13 +14032,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594797</v>
+        <v>594707</v>
       </c>
       <c r="R133" t="n">
-        <v>6947735</v>
+        <v>6947692</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,12 +14077,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14109,32 +14104,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312305</v>
+        <v>133312244</v>
       </c>
       <c r="B134" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14144,13 +14139,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594707</v>
+        <v>594797</v>
       </c>
       <c r="R134" t="n">
-        <v>6947692</v>
+        <v>6947735</v>
       </c>
       <c r="S134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14179,7 +14174,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14189,7 +14184,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14323,10 +14323,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312299</v>
+        <v>133312262</v>
       </c>
       <c r="B136" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14334,21 +14334,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594747</v>
+        <v>594845</v>
       </c>
       <c r="R136" t="n">
-        <v>6947714</v>
+        <v>6947767</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14430,10 +14430,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312262</v>
+        <v>133312294</v>
       </c>
       <c r="B137" t="n">
-        <v>79365</v>
+        <v>89300</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14441,21 +14441,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14465,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594845</v>
+        <v>594735</v>
       </c>
       <c r="R137" t="n">
-        <v>6947767</v>
+        <v>6947729</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14537,10 +14537,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312294</v>
+        <v>133312221</v>
       </c>
       <c r="B138" t="n">
-        <v>89300</v>
+        <v>57958</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,34 +14548,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594735</v>
+        <v>594741</v>
       </c>
       <c r="R138" t="n">
-        <v>6947729</v>
+        <v>6947668</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14607,7 +14615,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14617,7 +14625,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14644,10 +14657,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312221</v>
+        <v>133312299</v>
       </c>
       <c r="B139" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14655,42 +14668,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594741</v>
+        <v>594747</v>
       </c>
       <c r="R139" t="n">
-        <v>6947668</v>
+        <v>6947714</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14722,7 +14727,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14732,12 +14737,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312226</v>
+        <v>133312297</v>
       </c>
       <c r="B140" t="n">
-        <v>5199</v>
+        <v>91918</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594755</v>
+        <v>594737</v>
       </c>
       <c r="R140" t="n">
-        <v>6947670</v>
+        <v>6947721</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312297</v>
+        <v>133312226</v>
       </c>
       <c r="B143" t="n">
-        <v>91918</v>
+        <v>5199</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,13 +15120,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594737</v>
+        <v>594755</v>
       </c>
       <c r="R143" t="n">
-        <v>6947721</v>
+        <v>6947670</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15406,7 +15406,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133312181</v>
+        <v>133312252</v>
       </c>
       <c r="B146" t="n">
         <v>91918</v>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>594723</v>
+        <v>594811</v>
       </c>
       <c r="R146" t="n">
-        <v>6947583</v>
+        <v>6947698</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15513,10 +15513,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133312250</v>
+        <v>133312181</v>
       </c>
       <c r="B147" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15524,21 +15524,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15548,10 +15548,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>594805</v>
+        <v>594723</v>
       </c>
       <c r="R147" t="n">
-        <v>6947701</v>
+        <v>6947583</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15620,7 +15620,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133312304</v>
+        <v>133312250</v>
       </c>
       <c r="B148" t="n">
         <v>92217</v>
@@ -15655,7 +15655,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>594716</v>
+        <v>594805</v>
       </c>
       <c r="R148" t="n">
         <v>6947701</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15727,10 +15727,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133312288</v>
+        <v>133312304</v>
       </c>
       <c r="B149" t="n">
-        <v>79952</v>
+        <v>92217</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15738,21 +15738,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>594771</v>
+        <v>594716</v>
       </c>
       <c r="R149" t="n">
-        <v>6947766</v>
+        <v>6947701</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15834,10 +15834,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133312252</v>
+        <v>133312288</v>
       </c>
       <c r="B150" t="n">
-        <v>91918</v>
+        <v>79952</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15845,21 +15845,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>594811</v>
+        <v>594771</v>
       </c>
       <c r="R150" t="n">
-        <v>6947698</v>
+        <v>6947766</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16048,32 +16048,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312218</v>
+        <v>133312186</v>
       </c>
       <c r="B152" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16083,13 +16083,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594717</v>
+        <v>594705</v>
       </c>
       <c r="R152" t="n">
-        <v>6947668</v>
+        <v>6947589</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16128,12 +16128,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16160,32 +16155,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312186</v>
+        <v>133312271</v>
       </c>
       <c r="B153" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16195,13 +16190,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594705</v>
+        <v>594798</v>
       </c>
       <c r="R153" t="n">
-        <v>6947589</v>
+        <v>6947776</v>
       </c>
       <c r="S153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16230,7 +16225,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16240,7 +16235,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16267,10 +16262,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133312271</v>
+        <v>133312218</v>
       </c>
       <c r="B154" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16278,21 +16273,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16302,10 +16297,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>594798</v>
+        <v>594717</v>
       </c>
       <c r="R154" t="n">
-        <v>6947776</v>
+        <v>6947668</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -16337,7 +16332,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16347,7 +16342,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16481,10 +16481,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133312253</v>
+        <v>133312295</v>
       </c>
       <c r="B156" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16492,21 +16492,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>594812</v>
+        <v>594733</v>
       </c>
       <c r="R156" t="n">
-        <v>6947696</v>
+        <v>6947724</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16588,32 +16588,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133312182</v>
+        <v>133312269</v>
       </c>
       <c r="B157" t="n">
-        <v>79365</v>
+        <v>5179</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16623,10 +16623,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>594709</v>
+        <v>594804</v>
       </c>
       <c r="R157" t="n">
-        <v>6947587</v>
+        <v>6947763</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16695,10 +16695,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133312295</v>
+        <v>133312253</v>
       </c>
       <c r="B158" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16706,21 +16706,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16730,10 +16730,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>594733</v>
+        <v>594812</v>
       </c>
       <c r="R158" t="n">
-        <v>6947724</v>
+        <v>6947696</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16802,32 +16802,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133312269</v>
+        <v>133312182</v>
       </c>
       <c r="B159" t="n">
-        <v>5179</v>
+        <v>79365</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16837,10 +16837,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>594804</v>
+        <v>594709</v>
       </c>
       <c r="R159" t="n">
-        <v>6947763</v>
+        <v>6947587</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16909,10 +16909,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133312198</v>
+        <v>133312306</v>
       </c>
       <c r="B160" t="n">
-        <v>75433</v>
+        <v>80342</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16920,21 +16920,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16944,13 +16944,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>594683</v>
+        <v>594711</v>
       </c>
       <c r="R160" t="n">
-        <v>6947603</v>
+        <v>6947680</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17016,10 +17016,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133312306</v>
+        <v>133312206</v>
       </c>
       <c r="B161" t="n">
-        <v>80342</v>
+        <v>75433</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17027,21 +17027,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17051,13 +17051,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>594711</v>
+        <v>594719</v>
       </c>
       <c r="R161" t="n">
-        <v>6947680</v>
+        <v>6947615</v>
       </c>
       <c r="S161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17123,32 +17123,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312206</v>
+        <v>133312208</v>
       </c>
       <c r="B162" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17158,10 +17158,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594719</v>
+        <v>594728</v>
       </c>
       <c r="R162" t="n">
-        <v>6947615</v>
+        <v>6947607</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17230,32 +17230,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133312208</v>
+        <v>133312198</v>
       </c>
       <c r="B163" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>594728</v>
+        <v>594683</v>
       </c>
       <c r="R163" t="n">
-        <v>6947607</v>
+        <v>6947603</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17337,10 +17337,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>133312203</v>
+        <v>133312279</v>
       </c>
       <c r="B164" t="n">
-        <v>83181</v>
+        <v>92217</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17348,21 +17348,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17372,10 +17372,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>594694</v>
+        <v>594835</v>
       </c>
       <c r="R164" t="n">
-        <v>6947611</v>
+        <v>6947822</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133312279</v>
+        <v>133312203</v>
       </c>
       <c r="B165" t="n">
-        <v>92217</v>
+        <v>83181</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17455,21 +17455,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>594835</v>
+        <v>594694</v>
       </c>
       <c r="R165" t="n">
-        <v>6947822</v>
+        <v>6947611</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17765,32 +17765,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312313</v>
+        <v>133312319</v>
       </c>
       <c r="B168" t="n">
-        <v>80474</v>
+        <v>91918</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594697</v>
+        <v>594662</v>
       </c>
       <c r="R168" t="n">
-        <v>6947661</v>
+        <v>6947577</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312259</v>
+        <v>133312313</v>
       </c>
       <c r="B169" t="n">
-        <v>79952</v>
+        <v>80474</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594814</v>
+        <v>594697</v>
       </c>
       <c r="R169" t="n">
-        <v>6947723</v>
+        <v>6947661</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,32 +17979,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312216</v>
+        <v>133312259</v>
       </c>
       <c r="B170" t="n">
-        <v>92641</v>
+        <v>79952</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3298</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594730</v>
+        <v>594814</v>
       </c>
       <c r="R170" t="n">
-        <v>6947646</v>
+        <v>6947723</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,32 +18086,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312280</v>
+        <v>133312216</v>
       </c>
       <c r="B171" t="n">
-        <v>79090</v>
+        <v>92641</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6446</v>
+        <v>3298</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594788</v>
+        <v>594730</v>
       </c>
       <c r="R171" t="n">
-        <v>6947813</v>
+        <v>6947646</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,10 +18193,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312319</v>
+        <v>133312280</v>
       </c>
       <c r="B172" t="n">
-        <v>91918</v>
+        <v>79090</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18204,21 +18204,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594662</v>
+        <v>594788</v>
       </c>
       <c r="R172" t="n">
-        <v>6947577</v>
+        <v>6947813</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18407,32 +18407,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133312243</v>
+        <v>133312308</v>
       </c>
       <c r="B174" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>594794</v>
+        <v>594707</v>
       </c>
       <c r="R174" t="n">
-        <v>6947729</v>
+        <v>6947669</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18733,32 +18733,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312308</v>
+        <v>133312243</v>
       </c>
       <c r="B177" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18768,10 +18768,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594707</v>
+        <v>594794</v>
       </c>
       <c r="R177" t="n">
-        <v>6947669</v>
+        <v>6947729</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18803,7 +18803,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18813,7 +18813,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18840,10 +18840,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>133312213</v>
+        <v>133312179</v>
       </c>
       <c r="B178" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18851,21 +18851,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18875,10 +18875,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>594725</v>
+        <v>594731</v>
       </c>
       <c r="R178" t="n">
-        <v>6947645</v>
+        <v>6947567</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18947,10 +18947,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>133312179</v>
+        <v>133312213</v>
       </c>
       <c r="B179" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18958,21 +18958,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18982,10 +18982,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>594731</v>
+        <v>594725</v>
       </c>
       <c r="R179" t="n">
-        <v>6947567</v>
+        <v>6947645</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312240</v>
+        <v>133312194</v>
       </c>
       <c r="B182" t="n">
-        <v>92217</v>
+        <v>83315</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,10 +19303,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594782</v>
+        <v>594690</v>
       </c>
       <c r="R182" t="n">
-        <v>6947711</v>
+        <v>6947596</v>
       </c>
       <c r="S182" t="n">
         <v>6</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,7 +19375,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312298</v>
+        <v>133312240</v>
       </c>
       <c r="B183" t="n">
         <v>92217</v>
@@ -19410,13 +19410,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594740</v>
+        <v>594782</v>
       </c>
       <c r="R183" t="n">
-        <v>6947716</v>
+        <v>6947711</v>
       </c>
       <c r="S183" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19482,10 +19482,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312265</v>
+        <v>133312298</v>
       </c>
       <c r="B184" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19493,21 +19493,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19517,10 +19517,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594823</v>
+        <v>594740</v>
       </c>
       <c r="R184" t="n">
-        <v>6947773</v>
+        <v>6947716</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19589,10 +19589,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133312194</v>
+        <v>133312265</v>
       </c>
       <c r="B185" t="n">
-        <v>83315</v>
+        <v>79365</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19600,21 +19600,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19624,13 +19624,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>594690</v>
+        <v>594823</v>
       </c>
       <c r="R185" t="n">
-        <v>6947596</v>
+        <v>6947773</v>
       </c>
       <c r="S185" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19696,10 +19696,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312276</v>
+        <v>133312316</v>
       </c>
       <c r="B186" t="n">
-        <v>80398</v>
+        <v>75433</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19707,21 +19707,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594856</v>
+        <v>594666</v>
       </c>
       <c r="R186" t="n">
-        <v>6947759</v>
+        <v>6947640</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19803,7 +19803,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312316</v>
+        <v>133312188</v>
       </c>
       <c r="B187" t="n">
         <v>75433</v>
@@ -19838,13 +19838,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594666</v>
+        <v>594698</v>
       </c>
       <c r="R187" t="n">
-        <v>6947640</v>
+        <v>6947587</v>
       </c>
       <c r="S187" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,10 +19910,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312188</v>
+        <v>133312236</v>
       </c>
       <c r="B188" t="n">
-        <v>75433</v>
+        <v>79357</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19921,21 +19921,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6426</v>
+        <v>6434</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,13 +19945,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594698</v>
+        <v>594742</v>
       </c>
       <c r="R188" t="n">
-        <v>6947587</v>
+        <v>6947701</v>
       </c>
       <c r="S188" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,10 +20017,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312236</v>
+        <v>133312197</v>
       </c>
       <c r="B189" t="n">
-        <v>79357</v>
+        <v>75433</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20028,21 +20028,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6434</v>
+        <v>6426</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594742</v>
+        <v>594687</v>
       </c>
       <c r="R189" t="n">
-        <v>6947701</v>
+        <v>6947597</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,10 +20124,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312266</v>
+        <v>133312318</v>
       </c>
       <c r="B190" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20135,21 +20135,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20159,10 +20159,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594820</v>
+        <v>594678</v>
       </c>
       <c r="R190" t="n">
-        <v>6947773</v>
+        <v>6947597</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,7 +20231,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312197</v>
+        <v>133312317</v>
       </c>
       <c r="B191" t="n">
         <v>75433</v>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594687</v>
+        <v>594682</v>
       </c>
       <c r="R191" t="n">
-        <v>6947597</v>
+        <v>6947610</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,10 +20338,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312318</v>
+        <v>133312289</v>
       </c>
       <c r="B192" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20349,21 +20349,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594678</v>
+        <v>594777</v>
       </c>
       <c r="R192" t="n">
-        <v>6947597</v>
+        <v>6947757</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312317</v>
+        <v>133312266</v>
       </c>
       <c r="B193" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,13 +20480,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594682</v>
+        <v>594820</v>
       </c>
       <c r="R193" t="n">
-        <v>6947610</v>
+        <v>6947773</v>
       </c>
       <c r="S193" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20659,32 +20659,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133312289</v>
+        <v>133312276</v>
       </c>
       <c r="B195" t="n">
-        <v>92217</v>
+        <v>80398</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20694,10 +20694,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>594777</v>
+        <v>594856</v>
       </c>
       <c r="R195" t="n">
-        <v>6947757</v>
+        <v>6947759</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312215</v>
+        <v>133312219</v>
       </c>
       <c r="B196" t="n">
-        <v>92217</v>
+        <v>91932</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594730</v>
+        <v>594728</v>
       </c>
       <c r="R196" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,7 +20873,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312224</v>
+        <v>133312215</v>
       </c>
       <c r="B197" t="n">
         <v>92217</v>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594755</v>
+        <v>594730</v>
       </c>
       <c r="R197" t="n">
-        <v>6947667</v>
+        <v>6947645</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,10 +20980,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312219</v>
+        <v>133312224</v>
       </c>
       <c r="B198" t="n">
-        <v>91932</v>
+        <v>92217</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20991,21 +20991,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21015,7 +21015,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594728</v>
+        <v>594755</v>
       </c>
       <c r="R198" t="n">
         <v>6947667</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21194,32 +21194,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133312277</v>
+        <v>133312209</v>
       </c>
       <c r="B200" t="n">
-        <v>92566</v>
+        <v>92217</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21229,10 +21229,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>594860</v>
+        <v>594725</v>
       </c>
       <c r="R200" t="n">
-        <v>6947799</v>
+        <v>6947645</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21274,12 +21274,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21288,7 +21283,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -21307,32 +21301,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133312209</v>
+        <v>133312277</v>
       </c>
       <c r="B201" t="n">
-        <v>92217</v>
+        <v>92566</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21342,10 +21336,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>594725</v>
+        <v>594860</v>
       </c>
       <c r="R201" t="n">
-        <v>6947645</v>
+        <v>6947799</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -21377,7 +21371,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21387,7 +21381,12 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21396,6 +21395,7 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12922,10 +12922,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312293</v>
+        <v>133312274</v>
       </c>
       <c r="B123" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12933,21 +12933,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,13 +12957,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594745</v>
+        <v>594857</v>
       </c>
       <c r="R123" t="n">
-        <v>6947738</v>
+        <v>6947775</v>
       </c>
       <c r="S123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312274</v>
+        <v>133312293</v>
       </c>
       <c r="B124" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,13 +13064,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594857</v>
+        <v>594745</v>
       </c>
       <c r="R124" t="n">
-        <v>6947775</v>
+        <v>6947738</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13457,10 +13457,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312263</v>
+        <v>133312257</v>
       </c>
       <c r="B128" t="n">
-        <v>57955</v>
+        <v>79365</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13468,21 +13468,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,10 +13492,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594826</v>
+        <v>594820</v>
       </c>
       <c r="R128" t="n">
-        <v>6947773</v>
+        <v>6947705</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,12 +13537,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13569,32 +13564,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312257</v>
+        <v>133312184</v>
       </c>
       <c r="B129" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13604,10 +13599,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594820</v>
+        <v>594713</v>
       </c>
       <c r="R129" t="n">
-        <v>6947705</v>
+        <v>6947589</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13639,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13649,7 +13644,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13676,32 +13671,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312184</v>
+        <v>133312246</v>
       </c>
       <c r="B130" t="n">
-        <v>75433</v>
+        <v>79952</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13711,13 +13706,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594713</v>
+        <v>594810</v>
       </c>
       <c r="R130" t="n">
-        <v>6947589</v>
+        <v>6947725</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13746,7 +13741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13756,7 +13751,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13783,10 +13778,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312246</v>
+        <v>133312263</v>
       </c>
       <c r="B131" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13794,21 +13789,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13818,13 +13813,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594810</v>
+        <v>594826</v>
       </c>
       <c r="R131" t="n">
-        <v>6947725</v>
+        <v>6947773</v>
       </c>
       <c r="S131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13853,7 +13848,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13863,7 +13858,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312302</v>
+        <v>133312294</v>
       </c>
       <c r="B135" t="n">
-        <v>79365</v>
+        <v>89300</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,21 +14227,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594703</v>
+        <v>594735</v>
       </c>
       <c r="R135" t="n">
-        <v>6947719</v>
+        <v>6947729</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14430,10 +14430,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312294</v>
+        <v>133312299</v>
       </c>
       <c r="B137" t="n">
-        <v>89300</v>
+        <v>92217</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14441,21 +14441,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14465,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594735</v>
+        <v>594747</v>
       </c>
       <c r="R137" t="n">
-        <v>6947729</v>
+        <v>6947714</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14537,10 +14537,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312221</v>
+        <v>133312302</v>
       </c>
       <c r="B138" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,42 +14548,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594741</v>
+        <v>594703</v>
       </c>
       <c r="R138" t="n">
-        <v>6947668</v>
+        <v>6947719</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14615,7 +14607,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14625,12 +14617,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14657,10 +14644,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312299</v>
+        <v>133312221</v>
       </c>
       <c r="B139" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14668,34 +14655,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594747</v>
+        <v>594741</v>
       </c>
       <c r="R139" t="n">
-        <v>6947714</v>
+        <v>6947668</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14727,7 +14722,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14737,7 +14732,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14764,10 +14764,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312297</v>
+        <v>133312320</v>
       </c>
       <c r="B140" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14775,21 +14775,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594737</v>
+        <v>594653</v>
       </c>
       <c r="R140" t="n">
-        <v>6947721</v>
+        <v>6947566</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312320</v>
+        <v>133312297</v>
       </c>
       <c r="B141" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594653</v>
+        <v>594737</v>
       </c>
       <c r="R141" t="n">
-        <v>6947566</v>
+        <v>6947721</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15941,32 +15941,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133312303</v>
+        <v>133312218</v>
       </c>
       <c r="B151" t="n">
-        <v>80466</v>
+        <v>92217</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15976,10 +15976,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>594701</v>
+        <v>594717</v>
       </c>
       <c r="R151" t="n">
-        <v>6947707</v>
+        <v>6947668</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16021,7 +16021,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16048,32 +16053,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312186</v>
+        <v>133312189</v>
       </c>
       <c r="B152" t="n">
-        <v>75433</v>
+        <v>83181</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6426</v>
+        <v>1312</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16083,10 +16088,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594705</v>
+        <v>594688</v>
       </c>
       <c r="R152" t="n">
-        <v>6947589</v>
+        <v>6947584</v>
       </c>
       <c r="S152" t="n">
         <v>6</v>
@@ -16118,7 +16123,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16128,7 +16133,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16155,32 +16160,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312271</v>
+        <v>133312186</v>
       </c>
       <c r="B153" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16190,13 +16195,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594798</v>
+        <v>594705</v>
       </c>
       <c r="R153" t="n">
-        <v>6947776</v>
+        <v>6947589</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16225,7 +16230,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16235,7 +16240,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16262,10 +16267,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133312218</v>
+        <v>133312271</v>
       </c>
       <c r="B154" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16273,21 +16278,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16297,10 +16302,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>594717</v>
+        <v>594798</v>
       </c>
       <c r="R154" t="n">
-        <v>6947668</v>
+        <v>6947776</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -16332,7 +16337,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16342,12 +16347,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16374,32 +16374,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133312189</v>
+        <v>133312303</v>
       </c>
       <c r="B155" t="n">
-        <v>83181</v>
+        <v>80466</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16409,13 +16409,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>594688</v>
+        <v>594701</v>
       </c>
       <c r="R155" t="n">
-        <v>6947584</v>
+        <v>6947707</v>
       </c>
       <c r="S155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16481,10 +16481,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133312295</v>
+        <v>133312182</v>
       </c>
       <c r="B156" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16492,21 +16492,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>594733</v>
+        <v>594709</v>
       </c>
       <c r="R156" t="n">
-        <v>6947724</v>
+        <v>6947587</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16588,32 +16588,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133312269</v>
+        <v>133312253</v>
       </c>
       <c r="B157" t="n">
-        <v>5179</v>
+        <v>79365</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16623,10 +16623,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>594804</v>
+        <v>594812</v>
       </c>
       <c r="R157" t="n">
-        <v>6947763</v>
+        <v>6947696</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16695,10 +16695,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133312253</v>
+        <v>133312295</v>
       </c>
       <c r="B158" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16706,21 +16706,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16730,10 +16730,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>594812</v>
+        <v>594733</v>
       </c>
       <c r="R158" t="n">
-        <v>6947696</v>
+        <v>6947724</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16802,32 +16802,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133312182</v>
+        <v>133312269</v>
       </c>
       <c r="B159" t="n">
-        <v>79365</v>
+        <v>5179</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16837,10 +16837,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>594709</v>
+        <v>594804</v>
       </c>
       <c r="R159" t="n">
-        <v>6947587</v>
+        <v>6947763</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16909,32 +16909,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133312306</v>
+        <v>133312208</v>
       </c>
       <c r="B160" t="n">
-        <v>80342</v>
+        <v>91918</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16944,13 +16944,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>594711</v>
+        <v>594728</v>
       </c>
       <c r="R160" t="n">
-        <v>6947680</v>
+        <v>6947607</v>
       </c>
       <c r="S160" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17016,7 +17016,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133312206</v>
+        <v>133312198</v>
       </c>
       <c r="B161" t="n">
         <v>75433</v>
@@ -17051,10 +17051,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>594719</v>
+        <v>594683</v>
       </c>
       <c r="R161" t="n">
-        <v>6947615</v>
+        <v>6947603</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17123,32 +17123,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312208</v>
+        <v>133312306</v>
       </c>
       <c r="B162" t="n">
-        <v>91918</v>
+        <v>80342</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17158,13 +17158,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594728</v>
+        <v>594711</v>
       </c>
       <c r="R162" t="n">
-        <v>6947607</v>
+        <v>6947680</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17230,7 +17230,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133312198</v>
+        <v>133312206</v>
       </c>
       <c r="B163" t="n">
         <v>75433</v>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>594683</v>
+        <v>594719</v>
       </c>
       <c r="R163" t="n">
-        <v>6947603</v>
+        <v>6947615</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133312203</v>
+        <v>133312234</v>
       </c>
       <c r="B165" t="n">
-        <v>83181</v>
+        <v>92217</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17455,21 +17455,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>594694</v>
+        <v>594753</v>
       </c>
       <c r="R165" t="n">
-        <v>6947611</v>
+        <v>6947684</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17551,10 +17551,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133312300</v>
+        <v>133312203</v>
       </c>
       <c r="B166" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>594724</v>
+        <v>594694</v>
       </c>
       <c r="R166" t="n">
-        <v>6947715</v>
+        <v>6947611</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17658,10 +17658,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133312234</v>
+        <v>133312300</v>
       </c>
       <c r="B167" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17669,21 +17669,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17693,10 +17693,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>594753</v>
+        <v>594724</v>
       </c>
       <c r="R167" t="n">
-        <v>6947684</v>
+        <v>6947715</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17765,32 +17765,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312319</v>
+        <v>133312216</v>
       </c>
       <c r="B168" t="n">
-        <v>91918</v>
+        <v>92641</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594662</v>
+        <v>594730</v>
       </c>
       <c r="R168" t="n">
-        <v>6947577</v>
+        <v>6947646</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312313</v>
+        <v>133312259</v>
       </c>
       <c r="B169" t="n">
-        <v>80474</v>
+        <v>79952</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594697</v>
+        <v>594814</v>
       </c>
       <c r="R169" t="n">
-        <v>6947661</v>
+        <v>6947723</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,10 +17979,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312259</v>
+        <v>133312280</v>
       </c>
       <c r="B170" t="n">
-        <v>79952</v>
+        <v>79090</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17990,21 +17990,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594814</v>
+        <v>594788</v>
       </c>
       <c r="R170" t="n">
-        <v>6947723</v>
+        <v>6947813</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,10 +18086,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312216</v>
+        <v>133312313</v>
       </c>
       <c r="B171" t="n">
-        <v>92641</v>
+        <v>80474</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18097,21 +18097,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594730</v>
+        <v>594697</v>
       </c>
       <c r="R171" t="n">
-        <v>6947646</v>
+        <v>6947661</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,10 +18193,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312280</v>
+        <v>133312319</v>
       </c>
       <c r="B172" t="n">
-        <v>79090</v>
+        <v>91918</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18204,21 +18204,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594788</v>
+        <v>594662</v>
       </c>
       <c r="R172" t="n">
-        <v>6947813</v>
+        <v>6947577</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18407,32 +18407,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133312308</v>
+        <v>133312212</v>
       </c>
       <c r="B174" t="n">
-        <v>75433</v>
+        <v>91932</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6426</v>
+        <v>1204</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>594707</v>
+        <v>594721</v>
       </c>
       <c r="R174" t="n">
-        <v>6947669</v>
+        <v>6947646</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18514,10 +18514,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312268</v>
+        <v>133312243</v>
       </c>
       <c r="B175" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594805</v>
+        <v>594794</v>
       </c>
       <c r="R175" t="n">
-        <v>6947762</v>
+        <v>6947729</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,12 +18594,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18626,10 +18621,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312212</v>
+        <v>133312268</v>
       </c>
       <c r="B176" t="n">
-        <v>91932</v>
+        <v>57955</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18637,21 +18632,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18661,10 +18656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594721</v>
+        <v>594805</v>
       </c>
       <c r="R176" t="n">
-        <v>6947646</v>
+        <v>6947762</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18696,7 +18691,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18706,7 +18701,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18733,32 +18733,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312243</v>
+        <v>133312308</v>
       </c>
       <c r="B177" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18768,10 +18768,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594794</v>
+        <v>594707</v>
       </c>
       <c r="R177" t="n">
-        <v>6947729</v>
+        <v>6947669</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18803,7 +18803,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18813,7 +18813,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19482,10 +19482,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312298</v>
+        <v>133312265</v>
       </c>
       <c r="B184" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19493,21 +19493,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19517,10 +19517,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594740</v>
+        <v>594823</v>
       </c>
       <c r="R184" t="n">
-        <v>6947716</v>
+        <v>6947773</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19589,10 +19589,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133312265</v>
+        <v>133312298</v>
       </c>
       <c r="B185" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19600,21 +19600,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19624,10 +19624,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>594823</v>
+        <v>594740</v>
       </c>
       <c r="R185" t="n">
-        <v>6947773</v>
+        <v>6947716</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19696,32 +19696,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312316</v>
+        <v>133312289</v>
       </c>
       <c r="B186" t="n">
-        <v>75433</v>
+        <v>92217</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594666</v>
+        <v>594777</v>
       </c>
       <c r="R186" t="n">
-        <v>6947640</v>
+        <v>6947757</v>
       </c>
       <c r="S186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19803,32 +19803,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312188</v>
+        <v>133312266</v>
       </c>
       <c r="B187" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,13 +19838,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594698</v>
+        <v>594820</v>
       </c>
       <c r="R187" t="n">
-        <v>6947587</v>
+        <v>6947773</v>
       </c>
       <c r="S187" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,32 +19910,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312236</v>
+        <v>133312225</v>
       </c>
       <c r="B188" t="n">
-        <v>79357</v>
+        <v>91918</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,10 +19945,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594742</v>
+        <v>594757</v>
       </c>
       <c r="R188" t="n">
-        <v>6947701</v>
+        <v>6947666</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,7 +20017,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312197</v>
+        <v>133312316</v>
       </c>
       <c r="B189" t="n">
         <v>75433</v>
@@ -20052,13 +20052,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594687</v>
+        <v>594666</v>
       </c>
       <c r="R189" t="n">
-        <v>6947597</v>
+        <v>6947640</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,32 +20124,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312318</v>
+        <v>133312188</v>
       </c>
       <c r="B190" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20159,13 +20159,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594678</v>
+        <v>594698</v>
       </c>
       <c r="R190" t="n">
-        <v>6947597</v>
+        <v>6947587</v>
       </c>
       <c r="S190" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,10 +20231,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312317</v>
+        <v>133312236</v>
       </c>
       <c r="B191" t="n">
-        <v>75433</v>
+        <v>79357</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20242,21 +20242,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6426</v>
+        <v>6434</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594682</v>
+        <v>594742</v>
       </c>
       <c r="R191" t="n">
-        <v>6947610</v>
+        <v>6947701</v>
       </c>
       <c r="S191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,32 +20338,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312289</v>
+        <v>133312197</v>
       </c>
       <c r="B192" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594777</v>
+        <v>594687</v>
       </c>
       <c r="R192" t="n">
-        <v>6947757</v>
+        <v>6947597</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,10 +20445,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312266</v>
+        <v>133312318</v>
       </c>
       <c r="B193" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20456,21 +20456,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,10 +20480,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594820</v>
+        <v>594678</v>
       </c>
       <c r="R193" t="n">
-        <v>6947773</v>
+        <v>6947597</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20552,32 +20552,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133312225</v>
+        <v>133312317</v>
       </c>
       <c r="B194" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20587,13 +20587,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>594757</v>
+        <v>594682</v>
       </c>
       <c r="R194" t="n">
-        <v>6947666</v>
+        <v>6947610</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312219</v>
+        <v>133312239</v>
       </c>
       <c r="B196" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594728</v>
+        <v>594784</v>
       </c>
       <c r="R196" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312239</v>
+        <v>133312219</v>
       </c>
       <c r="B199" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594784</v>
+        <v>594728</v>
       </c>
       <c r="R199" t="n">
-        <v>6947700</v>
+        <v>6947667</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD199" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12387,10 +12387,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133312232</v>
+        <v>133312282</v>
       </c>
       <c r="B118" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>594755</v>
+        <v>594775</v>
       </c>
       <c r="R118" t="n">
-        <v>6947677</v>
+        <v>6947806</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133312282</v>
+        <v>133312232</v>
       </c>
       <c r="B119" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>594775</v>
+        <v>594755</v>
       </c>
       <c r="R119" t="n">
-        <v>6947806</v>
+        <v>6947677</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12708,32 +12708,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312229</v>
+        <v>133312205</v>
       </c>
       <c r="B121" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594755</v>
+        <v>594702</v>
       </c>
       <c r="R121" t="n">
-        <v>6947668</v>
+        <v>6947615</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,32 +12815,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312284</v>
+        <v>133312200</v>
       </c>
       <c r="B122" t="n">
-        <v>91868</v>
+        <v>75433</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>112</v>
+        <v>6426</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594757</v>
+        <v>594692</v>
       </c>
       <c r="R122" t="n">
-        <v>6947805</v>
+        <v>6947605</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,10 +12922,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312274</v>
+        <v>133312241</v>
       </c>
       <c r="B123" t="n">
-        <v>92217</v>
+        <v>79952</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12933,21 +12933,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594857</v>
+        <v>594784</v>
       </c>
       <c r="R123" t="n">
-        <v>6947775</v>
+        <v>6947732</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312293</v>
+        <v>133312229</v>
       </c>
       <c r="B124" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,13 +13064,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594745</v>
+        <v>594755</v>
       </c>
       <c r="R124" t="n">
-        <v>6947738</v>
+        <v>6947668</v>
       </c>
       <c r="S124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312200</v>
+        <v>133312293</v>
       </c>
       <c r="B125" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,13 +13171,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594692</v>
+        <v>594745</v>
       </c>
       <c r="R125" t="n">
-        <v>6947605</v>
+        <v>6947738</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,10 +13243,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312241</v>
+        <v>133312274</v>
       </c>
       <c r="B126" t="n">
-        <v>79952</v>
+        <v>92217</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,21 +13254,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594784</v>
+        <v>594857</v>
       </c>
       <c r="R126" t="n">
-        <v>6947732</v>
+        <v>6947775</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,32 +13350,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312205</v>
+        <v>133312284</v>
       </c>
       <c r="B127" t="n">
-        <v>75433</v>
+        <v>91868</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6426</v>
+        <v>112</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594702</v>
+        <v>594757</v>
       </c>
       <c r="R127" t="n">
-        <v>6947615</v>
+        <v>6947805</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13457,10 +13457,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312257</v>
+        <v>133312246</v>
       </c>
       <c r="B128" t="n">
-        <v>79365</v>
+        <v>79952</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13468,21 +13468,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,13 +13492,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594820</v>
+        <v>594810</v>
       </c>
       <c r="R128" t="n">
-        <v>6947705</v>
+        <v>6947725</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13671,10 +13671,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312246</v>
+        <v>133312257</v>
       </c>
       <c r="B130" t="n">
-        <v>79952</v>
+        <v>79365</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13682,21 +13682,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13706,13 +13706,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594810</v>
+        <v>594820</v>
       </c>
       <c r="R130" t="n">
-        <v>6947725</v>
+        <v>6947705</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312305</v>
+        <v>133312244</v>
       </c>
       <c r="B133" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,13 +14032,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594707</v>
+        <v>594797</v>
       </c>
       <c r="R133" t="n">
-        <v>6947692</v>
+        <v>6947735</v>
       </c>
       <c r="S133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,7 +14077,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14104,32 +14109,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312244</v>
+        <v>133312305</v>
       </c>
       <c r="B134" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14139,13 +14144,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594797</v>
+        <v>594707</v>
       </c>
       <c r="R134" t="n">
-        <v>6947735</v>
+        <v>6947692</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14174,7 +14179,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14184,12 +14189,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312294</v>
+        <v>133312302</v>
       </c>
       <c r="B135" t="n">
-        <v>89300</v>
+        <v>79365</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,21 +14227,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594735</v>
+        <v>594703</v>
       </c>
       <c r="R135" t="n">
-        <v>6947729</v>
+        <v>6947719</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14323,10 +14323,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312262</v>
+        <v>133312299</v>
       </c>
       <c r="B136" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14334,21 +14334,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594845</v>
+        <v>594747</v>
       </c>
       <c r="R136" t="n">
-        <v>6947767</v>
+        <v>6947714</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14430,10 +14430,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312299</v>
+        <v>133312262</v>
       </c>
       <c r="B137" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14441,21 +14441,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14465,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594747</v>
+        <v>594845</v>
       </c>
       <c r="R137" t="n">
-        <v>6947714</v>
+        <v>6947767</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14537,10 +14537,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312302</v>
+        <v>133312294</v>
       </c>
       <c r="B138" t="n">
-        <v>79365</v>
+        <v>89300</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,21 +14548,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14572,10 +14572,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594703</v>
+        <v>594735</v>
       </c>
       <c r="R138" t="n">
-        <v>6947719</v>
+        <v>6947729</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14978,32 +14978,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133312272</v>
+        <v>133312226</v>
       </c>
       <c r="B142" t="n">
-        <v>83315</v>
+        <v>5199</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>594856</v>
+        <v>594755</v>
       </c>
       <c r="R142" t="n">
-        <v>6947779</v>
+        <v>6947670</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312226</v>
+        <v>133312272</v>
       </c>
       <c r="B143" t="n">
-        <v>5199</v>
+        <v>83315</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594755</v>
+        <v>594856</v>
       </c>
       <c r="R143" t="n">
-        <v>6947670</v>
+        <v>6947779</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15406,10 +15406,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133312252</v>
+        <v>133312288</v>
       </c>
       <c r="B146" t="n">
-        <v>91918</v>
+        <v>79952</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15417,21 +15417,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>594811</v>
+        <v>594771</v>
       </c>
       <c r="R146" t="n">
-        <v>6947698</v>
+        <v>6947766</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15513,7 +15513,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133312181</v>
+        <v>133312252</v>
       </c>
       <c r="B147" t="n">
         <v>91918</v>
@@ -15548,10 +15548,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>594723</v>
+        <v>594811</v>
       </c>
       <c r="R147" t="n">
-        <v>6947583</v>
+        <v>6947698</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15620,10 +15620,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133312250</v>
+        <v>133312181</v>
       </c>
       <c r="B148" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15631,21 +15631,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>594805</v>
+        <v>594723</v>
       </c>
       <c r="R148" t="n">
-        <v>6947701</v>
+        <v>6947583</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15727,7 +15727,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133312304</v>
+        <v>133312250</v>
       </c>
       <c r="B149" t="n">
         <v>92217</v>
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>594716</v>
+        <v>594805</v>
       </c>
       <c r="R149" t="n">
         <v>6947701</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15834,10 +15834,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133312288</v>
+        <v>133312304</v>
       </c>
       <c r="B150" t="n">
-        <v>79952</v>
+        <v>92217</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15845,21 +15845,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>594771</v>
+        <v>594716</v>
       </c>
       <c r="R150" t="n">
-        <v>6947766</v>
+        <v>6947701</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15941,32 +15941,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133312218</v>
+        <v>133312186</v>
       </c>
       <c r="B151" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15976,13 +15976,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>594717</v>
+        <v>594705</v>
       </c>
       <c r="R151" t="n">
-        <v>6947668</v>
+        <v>6947589</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16021,12 +16021,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16053,32 +16048,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312189</v>
+        <v>133312303</v>
       </c>
       <c r="B152" t="n">
-        <v>83181</v>
+        <v>80466</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16088,13 +16083,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594688</v>
+        <v>594701</v>
       </c>
       <c r="R152" t="n">
-        <v>6947584</v>
+        <v>6947707</v>
       </c>
       <c r="S152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16123,7 +16118,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16133,7 +16128,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16160,32 +16155,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312186</v>
+        <v>133312271</v>
       </c>
       <c r="B153" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16195,13 +16190,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594705</v>
+        <v>594798</v>
       </c>
       <c r="R153" t="n">
-        <v>6947589</v>
+        <v>6947776</v>
       </c>
       <c r="S153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16230,7 +16225,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16240,7 +16235,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16267,10 +16262,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133312271</v>
+        <v>133312218</v>
       </c>
       <c r="B154" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16278,21 +16273,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16302,10 +16297,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>594798</v>
+        <v>594717</v>
       </c>
       <c r="R154" t="n">
-        <v>6947776</v>
+        <v>6947668</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -16337,7 +16332,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16347,7 +16342,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16374,32 +16374,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133312303</v>
+        <v>133312189</v>
       </c>
       <c r="B155" t="n">
-        <v>80466</v>
+        <v>83181</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16409,13 +16409,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>594701</v>
+        <v>594688</v>
       </c>
       <c r="R155" t="n">
-        <v>6947707</v>
+        <v>6947584</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16481,7 +16481,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133312182</v>
+        <v>133312253</v>
       </c>
       <c r="B156" t="n">
         <v>79365</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>594709</v>
+        <v>594812</v>
       </c>
       <c r="R156" t="n">
-        <v>6947587</v>
+        <v>6947696</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16588,7 +16588,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133312253</v>
+        <v>133312182</v>
       </c>
       <c r="B157" t="n">
         <v>79365</v>
@@ -16623,10 +16623,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>594812</v>
+        <v>594709</v>
       </c>
       <c r="R157" t="n">
-        <v>6947696</v>
+        <v>6947587</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16909,32 +16909,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133312208</v>
+        <v>133312306</v>
       </c>
       <c r="B160" t="n">
-        <v>91918</v>
+        <v>80342</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16944,13 +16944,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>594728</v>
+        <v>594711</v>
       </c>
       <c r="R160" t="n">
-        <v>6947607</v>
+        <v>6947680</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17016,7 +17016,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133312198</v>
+        <v>133312206</v>
       </c>
       <c r="B161" t="n">
         <v>75433</v>
@@ -17051,10 +17051,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>594683</v>
+        <v>594719</v>
       </c>
       <c r="R161" t="n">
-        <v>6947603</v>
+        <v>6947615</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17123,10 +17123,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312306</v>
+        <v>133312198</v>
       </c>
       <c r="B162" t="n">
-        <v>80342</v>
+        <v>75433</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17134,21 +17134,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17158,13 +17158,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594711</v>
+        <v>594683</v>
       </c>
       <c r="R162" t="n">
-        <v>6947680</v>
+        <v>6947603</v>
       </c>
       <c r="S162" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17230,32 +17230,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133312206</v>
+        <v>133312208</v>
       </c>
       <c r="B163" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>594719</v>
+        <v>594728</v>
       </c>
       <c r="R163" t="n">
-        <v>6947615</v>
+        <v>6947607</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17337,10 +17337,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>133312279</v>
+        <v>133312300</v>
       </c>
       <c r="B164" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17348,21 +17348,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17372,10 +17372,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>594835</v>
+        <v>594724</v>
       </c>
       <c r="R164" t="n">
-        <v>6947822</v>
+        <v>6947715</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17551,10 +17551,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133312203</v>
+        <v>133312279</v>
       </c>
       <c r="B166" t="n">
-        <v>83181</v>
+        <v>92217</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>594694</v>
+        <v>594835</v>
       </c>
       <c r="R166" t="n">
-        <v>6947611</v>
+        <v>6947822</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17658,10 +17658,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133312300</v>
+        <v>133312203</v>
       </c>
       <c r="B167" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17669,21 +17669,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17693,10 +17693,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>594724</v>
+        <v>594694</v>
       </c>
       <c r="R167" t="n">
-        <v>6947715</v>
+        <v>6947611</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17765,10 +17765,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312216</v>
+        <v>133312312</v>
       </c>
       <c r="B168" t="n">
-        <v>92641</v>
+        <v>80398</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17776,21 +17776,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,13 +17800,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594730</v>
+        <v>594697</v>
       </c>
       <c r="R168" t="n">
-        <v>6947646</v>
+        <v>6947661</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312259</v>
+        <v>133312313</v>
       </c>
       <c r="B169" t="n">
-        <v>79952</v>
+        <v>80474</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594814</v>
+        <v>594697</v>
       </c>
       <c r="R169" t="n">
-        <v>6947723</v>
+        <v>6947661</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18086,32 +18086,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312313</v>
+        <v>133312259</v>
       </c>
       <c r="B171" t="n">
-        <v>80474</v>
+        <v>79952</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594697</v>
+        <v>594814</v>
       </c>
       <c r="R171" t="n">
-        <v>6947661</v>
+        <v>6947723</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,32 +18193,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312319</v>
+        <v>133312216</v>
       </c>
       <c r="B172" t="n">
-        <v>91918</v>
+        <v>92641</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594662</v>
+        <v>594730</v>
       </c>
       <c r="R172" t="n">
-        <v>6947577</v>
+        <v>6947646</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18300,32 +18300,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312312</v>
+        <v>133312319</v>
       </c>
       <c r="B173" t="n">
-        <v>80398</v>
+        <v>91918</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>594697</v>
+        <v>594662</v>
       </c>
       <c r="R173" t="n">
-        <v>6947661</v>
+        <v>6947577</v>
       </c>
       <c r="S173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18621,32 +18621,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312268</v>
+        <v>133312308</v>
       </c>
       <c r="B176" t="n">
-        <v>57955</v>
+        <v>75433</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18656,10 +18656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594805</v>
+        <v>594707</v>
       </c>
       <c r="R176" t="n">
-        <v>6947762</v>
+        <v>6947669</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18701,12 +18701,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18733,32 +18728,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312308</v>
+        <v>133312268</v>
       </c>
       <c r="B177" t="n">
-        <v>75433</v>
+        <v>57955</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18768,10 +18763,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594707</v>
+        <v>594805</v>
       </c>
       <c r="R177" t="n">
-        <v>6947669</v>
+        <v>6947762</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18803,7 +18798,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18813,7 +18808,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18840,10 +18840,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>133312179</v>
+        <v>133312213</v>
       </c>
       <c r="B178" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18851,21 +18851,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18875,10 +18875,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>594731</v>
+        <v>594725</v>
       </c>
       <c r="R178" t="n">
-        <v>6947567</v>
+        <v>6947645</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18947,10 +18947,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>133312213</v>
+        <v>133312179</v>
       </c>
       <c r="B179" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18958,21 +18958,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18982,10 +18982,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>594725</v>
+        <v>594731</v>
       </c>
       <c r="R179" t="n">
-        <v>6947645</v>
+        <v>6947567</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19054,32 +19054,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>133312286</v>
+        <v>133312192</v>
       </c>
       <c r="B180" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19089,13 +19089,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>594762</v>
+        <v>594689</v>
       </c>
       <c r="R180" t="n">
-        <v>6947765</v>
+        <v>6947592</v>
       </c>
       <c r="S180" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19161,32 +19161,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>133312192</v>
+        <v>133312286</v>
       </c>
       <c r="B181" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19196,13 +19196,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>594689</v>
+        <v>594762</v>
       </c>
       <c r="R181" t="n">
-        <v>6947592</v>
+        <v>6947765</v>
       </c>
       <c r="S181" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312194</v>
+        <v>133312240</v>
       </c>
       <c r="B182" t="n">
-        <v>83315</v>
+        <v>92217</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,10 +19303,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594690</v>
+        <v>594782</v>
       </c>
       <c r="R182" t="n">
-        <v>6947596</v>
+        <v>6947711</v>
       </c>
       <c r="S182" t="n">
         <v>6</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,10 +19375,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312240</v>
+        <v>133312194</v>
       </c>
       <c r="B183" t="n">
-        <v>92217</v>
+        <v>83315</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19386,21 +19386,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19410,10 +19410,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594782</v>
+        <v>594690</v>
       </c>
       <c r="R183" t="n">
-        <v>6947711</v>
+        <v>6947596</v>
       </c>
       <c r="S183" t="n">
         <v>6</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19482,10 +19482,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312265</v>
+        <v>133312298</v>
       </c>
       <c r="B184" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19493,21 +19493,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19517,10 +19517,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594823</v>
+        <v>594740</v>
       </c>
       <c r="R184" t="n">
-        <v>6947773</v>
+        <v>6947716</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19589,10 +19589,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133312298</v>
+        <v>133312265</v>
       </c>
       <c r="B185" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19600,21 +19600,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19624,10 +19624,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>594740</v>
+        <v>594823</v>
       </c>
       <c r="R185" t="n">
-        <v>6947716</v>
+        <v>6947773</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19696,32 +19696,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312289</v>
+        <v>133312317</v>
       </c>
       <c r="B186" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594777</v>
+        <v>594682</v>
       </c>
       <c r="R186" t="n">
-        <v>6947757</v>
+        <v>6947610</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19803,32 +19803,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312266</v>
+        <v>133312236</v>
       </c>
       <c r="B187" t="n">
-        <v>91918</v>
+        <v>79357</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,10 +19838,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594820</v>
+        <v>594742</v>
       </c>
       <c r="R187" t="n">
-        <v>6947773</v>
+        <v>6947701</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,32 +19910,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312225</v>
+        <v>133312197</v>
       </c>
       <c r="B188" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,10 +19945,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594757</v>
+        <v>594687</v>
       </c>
       <c r="R188" t="n">
-        <v>6947666</v>
+        <v>6947597</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,32 +20017,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312316</v>
+        <v>133312318</v>
       </c>
       <c r="B189" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,13 +20052,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594666</v>
+        <v>594678</v>
       </c>
       <c r="R189" t="n">
-        <v>6947640</v>
+        <v>6947597</v>
       </c>
       <c r="S189" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20231,10 +20231,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312236</v>
+        <v>133312316</v>
       </c>
       <c r="B191" t="n">
-        <v>79357</v>
+        <v>75433</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20242,21 +20242,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6434</v>
+        <v>6426</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594742</v>
+        <v>594666</v>
       </c>
       <c r="R191" t="n">
-        <v>6947701</v>
+        <v>6947640</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,32 +20338,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312197</v>
+        <v>133312289</v>
       </c>
       <c r="B192" t="n">
-        <v>75433</v>
+        <v>92217</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594687</v>
+        <v>594777</v>
       </c>
       <c r="R192" t="n">
-        <v>6947597</v>
+        <v>6947757</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,10 +20445,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312318</v>
+        <v>133312266</v>
       </c>
       <c r="B193" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20456,21 +20456,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,10 +20480,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594678</v>
+        <v>594820</v>
       </c>
       <c r="R193" t="n">
-        <v>6947597</v>
+        <v>6947773</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20552,32 +20552,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133312317</v>
+        <v>133312225</v>
       </c>
       <c r="B194" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20587,13 +20587,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>594682</v>
+        <v>594757</v>
       </c>
       <c r="R194" t="n">
-        <v>6947610</v>
+        <v>6947666</v>
       </c>
       <c r="S194" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312239</v>
+        <v>133312219</v>
       </c>
       <c r="B196" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594784</v>
+        <v>594728</v>
       </c>
       <c r="R196" t="n">
-        <v>6947700</v>
+        <v>6947667</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312219</v>
+        <v>133312239</v>
       </c>
       <c r="B199" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594728</v>
+        <v>594784</v>
       </c>
       <c r="R199" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21194,32 +21194,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133312209</v>
+        <v>133312277</v>
       </c>
       <c r="B200" t="n">
-        <v>92217</v>
+        <v>92566</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21229,10 +21229,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>594725</v>
+        <v>594860</v>
       </c>
       <c r="R200" t="n">
-        <v>6947645</v>
+        <v>6947799</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21274,7 +21274,12 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21283,6 +21288,7 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -21301,32 +21307,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133312277</v>
+        <v>133312209</v>
       </c>
       <c r="B201" t="n">
-        <v>92566</v>
+        <v>92217</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21336,10 +21342,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>594860</v>
+        <v>594725</v>
       </c>
       <c r="R201" t="n">
-        <v>6947799</v>
+        <v>6947645</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -21371,7 +21377,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21381,12 +21387,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21395,7 +21396,6 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12708,32 +12708,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312205</v>
+        <v>133312229</v>
       </c>
       <c r="B121" t="n">
-        <v>75433</v>
+        <v>79365</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594702</v>
+        <v>594755</v>
       </c>
       <c r="R121" t="n">
-        <v>6947615</v>
+        <v>6947668</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,32 +12815,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312200</v>
+        <v>133312293</v>
       </c>
       <c r="B122" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,13 +12850,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594692</v>
+        <v>594745</v>
       </c>
       <c r="R122" t="n">
-        <v>6947605</v>
+        <v>6947738</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,10 +12922,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312241</v>
+        <v>133312274</v>
       </c>
       <c r="B123" t="n">
-        <v>79952</v>
+        <v>92217</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12933,21 +12933,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594784</v>
+        <v>594857</v>
       </c>
       <c r="R123" t="n">
-        <v>6947732</v>
+        <v>6947775</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312229</v>
+        <v>133312284</v>
       </c>
       <c r="B124" t="n">
-        <v>79365</v>
+        <v>91868</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594755</v>
+        <v>594757</v>
       </c>
       <c r="R124" t="n">
-        <v>6947668</v>
+        <v>6947805</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312293</v>
+        <v>133312205</v>
       </c>
       <c r="B125" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,13 +13171,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594745</v>
+        <v>594702</v>
       </c>
       <c r="R125" t="n">
-        <v>6947738</v>
+        <v>6947615</v>
       </c>
       <c r="S125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,32 +13243,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312274</v>
+        <v>133312200</v>
       </c>
       <c r="B126" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594857</v>
+        <v>594692</v>
       </c>
       <c r="R126" t="n">
-        <v>6947775</v>
+        <v>6947605</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,10 +13350,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312284</v>
+        <v>133312241</v>
       </c>
       <c r="B127" t="n">
-        <v>91868</v>
+        <v>79952</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13361,21 +13361,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594757</v>
+        <v>594784</v>
       </c>
       <c r="R127" t="n">
-        <v>6947805</v>
+        <v>6947732</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13457,10 +13457,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312246</v>
+        <v>133312257</v>
       </c>
       <c r="B128" t="n">
-        <v>79952</v>
+        <v>79365</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13468,21 +13468,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,13 +13492,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594810</v>
+        <v>594820</v>
       </c>
       <c r="R128" t="n">
-        <v>6947725</v>
+        <v>6947705</v>
       </c>
       <c r="S128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13564,32 +13564,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312184</v>
+        <v>133312246</v>
       </c>
       <c r="B129" t="n">
-        <v>75433</v>
+        <v>79952</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,13 +13599,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594713</v>
+        <v>594810</v>
       </c>
       <c r="R129" t="n">
-        <v>6947589</v>
+        <v>6947725</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13671,32 +13671,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312257</v>
+        <v>133312184</v>
       </c>
       <c r="B130" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13706,10 +13706,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594820</v>
+        <v>594713</v>
       </c>
       <c r="R130" t="n">
-        <v>6947705</v>
+        <v>6947589</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13890,32 +13890,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312247</v>
+        <v>133312244</v>
       </c>
       <c r="B132" t="n">
-        <v>92217</v>
+        <v>57145</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,10 +13925,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594801</v>
+        <v>594797</v>
       </c>
       <c r="R132" t="n">
-        <v>6947716</v>
+        <v>6947735</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13997,32 +14002,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312244</v>
+        <v>133312305</v>
       </c>
       <c r="B133" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,13 +14037,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594797</v>
+        <v>594707</v>
       </c>
       <c r="R133" t="n">
-        <v>6947735</v>
+        <v>6947692</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14067,7 +14072,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,12 +14082,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14109,10 +14109,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312305</v>
+        <v>133312247</v>
       </c>
       <c r="B134" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14120,21 +14120,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14144,13 +14144,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594707</v>
+        <v>594801</v>
       </c>
       <c r="R134" t="n">
-        <v>6947692</v>
+        <v>6947716</v>
       </c>
       <c r="S134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14764,10 +14764,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312320</v>
+        <v>133312272</v>
       </c>
       <c r="B140" t="n">
-        <v>79365</v>
+        <v>83315</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14775,21 +14775,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,10 +14799,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594653</v>
+        <v>594856</v>
       </c>
       <c r="R140" t="n">
-        <v>6947566</v>
+        <v>6947779</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312297</v>
+        <v>133312320</v>
       </c>
       <c r="B141" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594737</v>
+        <v>594653</v>
       </c>
       <c r="R141" t="n">
-        <v>6947721</v>
+        <v>6947566</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14978,32 +14978,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133312226</v>
+        <v>133312297</v>
       </c>
       <c r="B142" t="n">
-        <v>5199</v>
+        <v>91918</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,13 +15013,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>594755</v>
+        <v>594737</v>
       </c>
       <c r="R142" t="n">
-        <v>6947670</v>
+        <v>6947721</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312272</v>
+        <v>133312226</v>
       </c>
       <c r="B143" t="n">
-        <v>83315</v>
+        <v>5199</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594856</v>
+        <v>594755</v>
       </c>
       <c r="R143" t="n">
-        <v>6947779</v>
+        <v>6947670</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17765,10 +17765,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312312</v>
+        <v>133312313</v>
       </c>
       <c r="B168" t="n">
-        <v>80398</v>
+        <v>80474</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17776,21 +17776,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17806,7 +17806,7 @@
         <v>6947661</v>
       </c>
       <c r="S168" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312313</v>
+        <v>133312280</v>
       </c>
       <c r="B169" t="n">
-        <v>80474</v>
+        <v>79090</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594697</v>
+        <v>594788</v>
       </c>
       <c r="R169" t="n">
-        <v>6947661</v>
+        <v>6947813</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,10 +17979,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312280</v>
+        <v>133312259</v>
       </c>
       <c r="B170" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17990,21 +17990,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594788</v>
+        <v>594814</v>
       </c>
       <c r="R170" t="n">
-        <v>6947813</v>
+        <v>6947723</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,32 +18086,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312259</v>
+        <v>133312216</v>
       </c>
       <c r="B171" t="n">
-        <v>79952</v>
+        <v>92641</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>3298</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594814</v>
+        <v>594730</v>
       </c>
       <c r="R171" t="n">
-        <v>6947723</v>
+        <v>6947646</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,32 +18193,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312216</v>
+        <v>133312319</v>
       </c>
       <c r="B172" t="n">
-        <v>92641</v>
+        <v>91918</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594730</v>
+        <v>594662</v>
       </c>
       <c r="R172" t="n">
-        <v>6947646</v>
+        <v>6947577</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18300,32 +18300,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312319</v>
+        <v>133312312</v>
       </c>
       <c r="B173" t="n">
-        <v>91918</v>
+        <v>80398</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>594662</v>
+        <v>594697</v>
       </c>
       <c r="R173" t="n">
-        <v>6947577</v>
+        <v>6947661</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18621,32 +18621,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312308</v>
+        <v>133312268</v>
       </c>
       <c r="B176" t="n">
-        <v>75433</v>
+        <v>57955</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18656,10 +18656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594707</v>
+        <v>594805</v>
       </c>
       <c r="R176" t="n">
-        <v>6947669</v>
+        <v>6947762</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18701,7 +18701,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18728,32 +18733,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312268</v>
+        <v>133312308</v>
       </c>
       <c r="B177" t="n">
-        <v>57955</v>
+        <v>75433</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18763,10 +18768,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594805</v>
+        <v>594707</v>
       </c>
       <c r="R177" t="n">
-        <v>6947762</v>
+        <v>6947669</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18798,7 +18803,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18808,12 +18813,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312240</v>
+        <v>133312194</v>
       </c>
       <c r="B182" t="n">
-        <v>92217</v>
+        <v>83315</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,10 +19303,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594782</v>
+        <v>594690</v>
       </c>
       <c r="R182" t="n">
-        <v>6947711</v>
+        <v>6947596</v>
       </c>
       <c r="S182" t="n">
         <v>6</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,10 +19375,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312194</v>
+        <v>133312298</v>
       </c>
       <c r="B183" t="n">
-        <v>83315</v>
+        <v>92217</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19386,21 +19386,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19410,13 +19410,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594690</v>
+        <v>594740</v>
       </c>
       <c r="R183" t="n">
-        <v>6947596</v>
+        <v>6947716</v>
       </c>
       <c r="S183" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19482,10 +19482,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312298</v>
+        <v>133312265</v>
       </c>
       <c r="B184" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19493,21 +19493,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19517,10 +19517,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594740</v>
+        <v>594823</v>
       </c>
       <c r="R184" t="n">
-        <v>6947716</v>
+        <v>6947773</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19589,10 +19589,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133312265</v>
+        <v>133312240</v>
       </c>
       <c r="B185" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19600,21 +19600,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19624,13 +19624,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>594823</v>
+        <v>594782</v>
       </c>
       <c r="R185" t="n">
-        <v>6947773</v>
+        <v>6947711</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD185" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12708,32 +12708,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312229</v>
+        <v>133312200</v>
       </c>
       <c r="B121" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594755</v>
+        <v>594692</v>
       </c>
       <c r="R121" t="n">
-        <v>6947668</v>
+        <v>6947605</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312293</v>
+        <v>133312241</v>
       </c>
       <c r="B122" t="n">
-        <v>91918</v>
+        <v>79952</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,13 +12850,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594745</v>
+        <v>594784</v>
       </c>
       <c r="R122" t="n">
-        <v>6947738</v>
+        <v>6947732</v>
       </c>
       <c r="S122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,32 +12922,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312274</v>
+        <v>133312205</v>
       </c>
       <c r="B123" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594857</v>
+        <v>594702</v>
       </c>
       <c r="R123" t="n">
-        <v>6947775</v>
+        <v>6947615</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312284</v>
+        <v>133312293</v>
       </c>
       <c r="B124" t="n">
-        <v>91868</v>
+        <v>91918</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,13 +13064,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594757</v>
+        <v>594745</v>
       </c>
       <c r="R124" t="n">
-        <v>6947805</v>
+        <v>6947738</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312205</v>
+        <v>133312229</v>
       </c>
       <c r="B125" t="n">
-        <v>75433</v>
+        <v>79365</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594702</v>
+        <v>594755</v>
       </c>
       <c r="R125" t="n">
-        <v>6947615</v>
+        <v>6947668</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,32 +13243,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312200</v>
+        <v>133312274</v>
       </c>
       <c r="B126" t="n">
-        <v>75433</v>
+        <v>92217</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594692</v>
+        <v>594857</v>
       </c>
       <c r="R126" t="n">
-        <v>6947605</v>
+        <v>6947775</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,10 +13350,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312241</v>
+        <v>133312284</v>
       </c>
       <c r="B127" t="n">
-        <v>79952</v>
+        <v>91868</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13361,21 +13361,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594784</v>
+        <v>594757</v>
       </c>
       <c r="R127" t="n">
-        <v>6947732</v>
+        <v>6947805</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13564,32 +13564,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312246</v>
+        <v>133312184</v>
       </c>
       <c r="B129" t="n">
-        <v>79952</v>
+        <v>75433</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,13 +13599,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594810</v>
+        <v>594713</v>
       </c>
       <c r="R129" t="n">
-        <v>6947725</v>
+        <v>6947589</v>
       </c>
       <c r="S129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13671,32 +13671,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312184</v>
+        <v>133312246</v>
       </c>
       <c r="B130" t="n">
-        <v>75433</v>
+        <v>79952</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13706,13 +13706,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594713</v>
+        <v>594810</v>
       </c>
       <c r="R130" t="n">
-        <v>6947589</v>
+        <v>6947725</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13890,32 +13890,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312244</v>
+        <v>133312247</v>
       </c>
       <c r="B132" t="n">
-        <v>57145</v>
+        <v>92217</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,10 +13925,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594797</v>
+        <v>594801</v>
       </c>
       <c r="R132" t="n">
-        <v>6947735</v>
+        <v>6947716</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,12 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14002,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312305</v>
+        <v>133312244</v>
       </c>
       <c r="B133" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14037,13 +14032,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594707</v>
+        <v>594797</v>
       </c>
       <c r="R133" t="n">
-        <v>6947692</v>
+        <v>6947735</v>
       </c>
       <c r="S133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14072,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14082,7 +14077,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14109,10 +14109,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312247</v>
+        <v>133312305</v>
       </c>
       <c r="B134" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14120,21 +14120,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14144,13 +14144,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594801</v>
+        <v>594707</v>
       </c>
       <c r="R134" t="n">
-        <v>6947716</v>
+        <v>6947692</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312302</v>
+        <v>133312299</v>
       </c>
       <c r="B135" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,21 +14227,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594703</v>
+        <v>594747</v>
       </c>
       <c r="R135" t="n">
-        <v>6947719</v>
+        <v>6947714</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14323,10 +14323,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312299</v>
+        <v>133312302</v>
       </c>
       <c r="B136" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14334,21 +14334,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594747</v>
+        <v>594703</v>
       </c>
       <c r="R136" t="n">
-        <v>6947714</v>
+        <v>6947719</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14430,10 +14430,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312262</v>
+        <v>133312294</v>
       </c>
       <c r="B137" t="n">
-        <v>79365</v>
+        <v>89300</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14441,21 +14441,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14465,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594845</v>
+        <v>594735</v>
       </c>
       <c r="R137" t="n">
-        <v>6947767</v>
+        <v>6947729</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14537,10 +14537,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312294</v>
+        <v>133312262</v>
       </c>
       <c r="B138" t="n">
-        <v>89300</v>
+        <v>79365</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,21 +14548,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14572,10 +14572,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594735</v>
+        <v>594845</v>
       </c>
       <c r="R138" t="n">
-        <v>6947729</v>
+        <v>6947767</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312272</v>
+        <v>133312226</v>
       </c>
       <c r="B140" t="n">
-        <v>83315</v>
+        <v>5199</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,10 +14799,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594856</v>
+        <v>594755</v>
       </c>
       <c r="R140" t="n">
-        <v>6947779</v>
+        <v>6947670</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312320</v>
+        <v>133312297</v>
       </c>
       <c r="B141" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594653</v>
+        <v>594737</v>
       </c>
       <c r="R141" t="n">
-        <v>6947566</v>
+        <v>6947721</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14978,10 +14978,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133312297</v>
+        <v>133312320</v>
       </c>
       <c r="B142" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14989,21 +14989,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,13 +15013,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>594737</v>
+        <v>594653</v>
       </c>
       <c r="R142" t="n">
-        <v>6947721</v>
+        <v>6947566</v>
       </c>
       <c r="S142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312226</v>
+        <v>133312272</v>
       </c>
       <c r="B143" t="n">
-        <v>5199</v>
+        <v>83315</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594755</v>
+        <v>594856</v>
       </c>
       <c r="R143" t="n">
-        <v>6947670</v>
+        <v>6947779</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15192,10 +15192,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133312195</v>
+        <v>133312222</v>
       </c>
       <c r="B144" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15203,21 +15203,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15227,13 +15227,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>594690</v>
+        <v>594755</v>
       </c>
       <c r="R144" t="n">
-        <v>6947596</v>
+        <v>6947667</v>
       </c>
       <c r="S144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15299,10 +15299,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133312222</v>
+        <v>133312195</v>
       </c>
       <c r="B145" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15310,21 +15310,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>594755</v>
+        <v>594690</v>
       </c>
       <c r="R145" t="n">
-        <v>6947667</v>
+        <v>6947596</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15406,10 +15406,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133312288</v>
+        <v>133312304</v>
       </c>
       <c r="B146" t="n">
-        <v>79952</v>
+        <v>92217</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15417,21 +15417,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>594771</v>
+        <v>594716</v>
       </c>
       <c r="R146" t="n">
-        <v>6947766</v>
+        <v>6947701</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15513,10 +15513,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133312252</v>
+        <v>133312250</v>
       </c>
       <c r="B147" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15524,21 +15524,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15548,10 +15548,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>594811</v>
+        <v>594805</v>
       </c>
       <c r="R147" t="n">
-        <v>6947698</v>
+        <v>6947701</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15727,10 +15727,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133312250</v>
+        <v>133312252</v>
       </c>
       <c r="B149" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15738,21 +15738,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>594805</v>
+        <v>594811</v>
       </c>
       <c r="R149" t="n">
-        <v>6947701</v>
+        <v>6947698</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15834,10 +15834,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133312304</v>
+        <v>133312288</v>
       </c>
       <c r="B150" t="n">
-        <v>92217</v>
+        <v>79952</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15845,21 +15845,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>594716</v>
+        <v>594771</v>
       </c>
       <c r="R150" t="n">
-        <v>6947701</v>
+        <v>6947766</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15941,32 +15941,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133312186</v>
+        <v>133312218</v>
       </c>
       <c r="B151" t="n">
-        <v>75433</v>
+        <v>92217</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15976,13 +15976,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>594705</v>
+        <v>594717</v>
       </c>
       <c r="R151" t="n">
-        <v>6947589</v>
+        <v>6947668</v>
       </c>
       <c r="S151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16021,7 +16021,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16048,32 +16053,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312303</v>
+        <v>133312189</v>
       </c>
       <c r="B152" t="n">
-        <v>80466</v>
+        <v>83181</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16083,13 +16088,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594701</v>
+        <v>594688</v>
       </c>
       <c r="R152" t="n">
-        <v>6947707</v>
+        <v>6947584</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16118,7 +16123,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16128,7 +16133,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16155,32 +16160,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312271</v>
+        <v>133312303</v>
       </c>
       <c r="B153" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16190,10 +16195,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594798</v>
+        <v>594701</v>
       </c>
       <c r="R153" t="n">
-        <v>6947776</v>
+        <v>6947707</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -16225,7 +16230,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16235,7 +16240,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16262,32 +16267,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133312218</v>
+        <v>133312186</v>
       </c>
       <c r="B154" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16297,13 +16302,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>594717</v>
+        <v>594705</v>
       </c>
       <c r="R154" t="n">
-        <v>6947668</v>
+        <v>6947589</v>
       </c>
       <c r="S154" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16332,7 +16337,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16342,12 +16347,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16374,10 +16374,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133312189</v>
+        <v>133312271</v>
       </c>
       <c r="B155" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16385,21 +16385,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16409,13 +16409,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>594688</v>
+        <v>594798</v>
       </c>
       <c r="R155" t="n">
-        <v>6947584</v>
+        <v>6947776</v>
       </c>
       <c r="S155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16588,10 +16588,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133312182</v>
+        <v>133312295</v>
       </c>
       <c r="B157" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16599,21 +16599,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16623,10 +16623,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>594709</v>
+        <v>594733</v>
       </c>
       <c r="R157" t="n">
-        <v>6947587</v>
+        <v>6947724</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16695,10 +16695,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133312295</v>
+        <v>133312182</v>
       </c>
       <c r="B158" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16706,21 +16706,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16730,10 +16730,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>594733</v>
+        <v>594709</v>
       </c>
       <c r="R158" t="n">
-        <v>6947724</v>
+        <v>6947587</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16909,10 +16909,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133312306</v>
+        <v>133312198</v>
       </c>
       <c r="B160" t="n">
-        <v>80342</v>
+        <v>75433</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16920,21 +16920,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16944,13 +16944,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>594711</v>
+        <v>594683</v>
       </c>
       <c r="R160" t="n">
-        <v>6947680</v>
+        <v>6947603</v>
       </c>
       <c r="S160" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17016,10 +17016,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133312206</v>
+        <v>133312306</v>
       </c>
       <c r="B161" t="n">
-        <v>75433</v>
+        <v>80342</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17027,21 +17027,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17051,13 +17051,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>594719</v>
+        <v>594711</v>
       </c>
       <c r="R161" t="n">
-        <v>6947615</v>
+        <v>6947680</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17123,7 +17123,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312198</v>
+        <v>133312206</v>
       </c>
       <c r="B162" t="n">
         <v>75433</v>
@@ -17158,10 +17158,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594683</v>
+        <v>594719</v>
       </c>
       <c r="R162" t="n">
-        <v>6947603</v>
+        <v>6947615</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17337,10 +17337,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>133312300</v>
+        <v>133312279</v>
       </c>
       <c r="B164" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17348,21 +17348,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17372,10 +17372,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>594724</v>
+        <v>594835</v>
       </c>
       <c r="R164" t="n">
-        <v>6947715</v>
+        <v>6947822</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133312234</v>
+        <v>133312300</v>
       </c>
       <c r="B165" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17455,21 +17455,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>594753</v>
+        <v>594724</v>
       </c>
       <c r="R165" t="n">
-        <v>6947684</v>
+        <v>6947715</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17551,10 +17551,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133312279</v>
+        <v>133312203</v>
       </c>
       <c r="B166" t="n">
-        <v>92217</v>
+        <v>83181</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>594835</v>
+        <v>594694</v>
       </c>
       <c r="R166" t="n">
-        <v>6947822</v>
+        <v>6947611</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17658,10 +17658,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133312203</v>
+        <v>133312234</v>
       </c>
       <c r="B167" t="n">
-        <v>83181</v>
+        <v>92217</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17669,21 +17669,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17693,10 +17693,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>594694</v>
+        <v>594753</v>
       </c>
       <c r="R167" t="n">
-        <v>6947611</v>
+        <v>6947684</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17765,32 +17765,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312313</v>
+        <v>133312319</v>
       </c>
       <c r="B168" t="n">
-        <v>80474</v>
+        <v>91918</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594697</v>
+        <v>594662</v>
       </c>
       <c r="R168" t="n">
-        <v>6947661</v>
+        <v>6947577</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,10 +17872,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312280</v>
+        <v>133312259</v>
       </c>
       <c r="B169" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17883,21 +17883,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594788</v>
+        <v>594814</v>
       </c>
       <c r="R169" t="n">
-        <v>6947813</v>
+        <v>6947723</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,32 +17979,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312259</v>
+        <v>133312216</v>
       </c>
       <c r="B170" t="n">
-        <v>79952</v>
+        <v>92641</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>3298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594814</v>
+        <v>594730</v>
       </c>
       <c r="R170" t="n">
-        <v>6947723</v>
+        <v>6947646</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,32 +18086,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312216</v>
+        <v>133312280</v>
       </c>
       <c r="B171" t="n">
-        <v>92641</v>
+        <v>79090</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3298</v>
+        <v>6446</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594730</v>
+        <v>594788</v>
       </c>
       <c r="R171" t="n">
-        <v>6947646</v>
+        <v>6947813</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,32 +18193,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312319</v>
+        <v>133312313</v>
       </c>
       <c r="B172" t="n">
-        <v>91918</v>
+        <v>80474</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594662</v>
+        <v>594697</v>
       </c>
       <c r="R172" t="n">
-        <v>6947577</v>
+        <v>6947661</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18407,10 +18407,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133312212</v>
+        <v>133312243</v>
       </c>
       <c r="B174" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18418,21 +18418,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>594721</v>
+        <v>594794</v>
       </c>
       <c r="R174" t="n">
-        <v>6947646</v>
+        <v>6947729</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18514,10 +18514,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312243</v>
+        <v>133312212</v>
       </c>
       <c r="B175" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594794</v>
+        <v>594721</v>
       </c>
       <c r="R175" t="n">
-        <v>6947729</v>
+        <v>6947646</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18621,32 +18621,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312268</v>
+        <v>133312308</v>
       </c>
       <c r="B176" t="n">
-        <v>57955</v>
+        <v>75433</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18656,10 +18656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594805</v>
+        <v>594707</v>
       </c>
       <c r="R176" t="n">
-        <v>6947762</v>
+        <v>6947669</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18701,12 +18701,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18733,32 +18728,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312308</v>
+        <v>133312268</v>
       </c>
       <c r="B177" t="n">
-        <v>75433</v>
+        <v>57955</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18768,10 +18763,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594707</v>
+        <v>594805</v>
       </c>
       <c r="R177" t="n">
-        <v>6947669</v>
+        <v>6947762</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18803,7 +18798,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18813,7 +18808,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18840,10 +18840,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>133312213</v>
+        <v>133312179</v>
       </c>
       <c r="B178" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18851,21 +18851,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18875,10 +18875,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>594725</v>
+        <v>594731</v>
       </c>
       <c r="R178" t="n">
-        <v>6947645</v>
+        <v>6947567</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18947,10 +18947,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>133312179</v>
+        <v>133312213</v>
       </c>
       <c r="B179" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18958,21 +18958,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18982,10 +18982,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>594731</v>
+        <v>594725</v>
       </c>
       <c r="R179" t="n">
-        <v>6947567</v>
+        <v>6947645</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19054,32 +19054,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>133312192</v>
+        <v>133312286</v>
       </c>
       <c r="B180" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19089,13 +19089,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>594689</v>
+        <v>594762</v>
       </c>
       <c r="R180" t="n">
-        <v>6947592</v>
+        <v>6947765</v>
       </c>
       <c r="S180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19161,32 +19161,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>133312286</v>
+        <v>133312192</v>
       </c>
       <c r="B181" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19196,13 +19196,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>594762</v>
+        <v>594689</v>
       </c>
       <c r="R181" t="n">
-        <v>6947765</v>
+        <v>6947592</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312194</v>
+        <v>133312265</v>
       </c>
       <c r="B182" t="n">
-        <v>83315</v>
+        <v>79365</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,13 +19303,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594690</v>
+        <v>594823</v>
       </c>
       <c r="R182" t="n">
-        <v>6947596</v>
+        <v>6947773</v>
       </c>
       <c r="S182" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19482,10 +19482,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312265</v>
+        <v>133312240</v>
       </c>
       <c r="B184" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19493,21 +19493,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19517,13 +19517,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594823</v>
+        <v>594782</v>
       </c>
       <c r="R184" t="n">
-        <v>6947773</v>
+        <v>6947711</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19589,10 +19589,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133312240</v>
+        <v>133312194</v>
       </c>
       <c r="B185" t="n">
-        <v>92217</v>
+        <v>83315</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19600,21 +19600,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19624,10 +19624,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>594782</v>
+        <v>594690</v>
       </c>
       <c r="R185" t="n">
-        <v>6947711</v>
+        <v>6947596</v>
       </c>
       <c r="S185" t="n">
         <v>6</v>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19696,10 +19696,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312317</v>
+        <v>133312276</v>
       </c>
       <c r="B186" t="n">
-        <v>75433</v>
+        <v>80398</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19707,21 +19707,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594682</v>
+        <v>594856</v>
       </c>
       <c r="R186" t="n">
-        <v>6947610</v>
+        <v>6947759</v>
       </c>
       <c r="S186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19803,32 +19803,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312236</v>
+        <v>133312289</v>
       </c>
       <c r="B187" t="n">
-        <v>79357</v>
+        <v>92217</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6434</v>
+        <v>658</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,10 +19838,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594742</v>
+        <v>594777</v>
       </c>
       <c r="R187" t="n">
-        <v>6947701</v>
+        <v>6947757</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,32 +19910,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312197</v>
+        <v>133312225</v>
       </c>
       <c r="B188" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,10 +19945,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594687</v>
+        <v>594757</v>
       </c>
       <c r="R188" t="n">
-        <v>6947597</v>
+        <v>6947666</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,10 +20017,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312318</v>
+        <v>133312266</v>
       </c>
       <c r="B189" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20028,21 +20028,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594678</v>
+        <v>594820</v>
       </c>
       <c r="R189" t="n">
-        <v>6947597</v>
+        <v>6947773</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,7 +20124,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312188</v>
+        <v>133312316</v>
       </c>
       <c r="B190" t="n">
         <v>75433</v>
@@ -20159,13 +20159,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594698</v>
+        <v>594666</v>
       </c>
       <c r="R190" t="n">
-        <v>6947587</v>
+        <v>6947640</v>
       </c>
       <c r="S190" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,7 +20231,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312316</v>
+        <v>133312188</v>
       </c>
       <c r="B191" t="n">
         <v>75433</v>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594666</v>
+        <v>594698</v>
       </c>
       <c r="R191" t="n">
-        <v>6947640</v>
+        <v>6947587</v>
       </c>
       <c r="S191" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,32 +20338,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312289</v>
+        <v>133312236</v>
       </c>
       <c r="B192" t="n">
-        <v>92217</v>
+        <v>79357</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>658</v>
+        <v>6434</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594777</v>
+        <v>594742</v>
       </c>
       <c r="R192" t="n">
-        <v>6947757</v>
+        <v>6947701</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312266</v>
+        <v>133312197</v>
       </c>
       <c r="B193" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,10 +20480,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594820</v>
+        <v>594687</v>
       </c>
       <c r="R193" t="n">
-        <v>6947773</v>
+        <v>6947597</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20552,10 +20552,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133312225</v>
+        <v>133312318</v>
       </c>
       <c r="B194" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20563,21 +20563,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>594757</v>
+        <v>594678</v>
       </c>
       <c r="R194" t="n">
-        <v>6947666</v>
+        <v>6947597</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20659,10 +20659,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133312276</v>
+        <v>133312317</v>
       </c>
       <c r="B195" t="n">
-        <v>80398</v>
+        <v>75433</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20670,21 +20670,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20694,13 +20694,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>594856</v>
+        <v>594682</v>
       </c>
       <c r="R195" t="n">
-        <v>6947759</v>
+        <v>6947610</v>
       </c>
       <c r="S195" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312219</v>
+        <v>133312239</v>
       </c>
       <c r="B196" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594728</v>
+        <v>594784</v>
       </c>
       <c r="R196" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312215</v>
+        <v>133312219</v>
       </c>
       <c r="B197" t="n">
-        <v>92217</v>
+        <v>91932</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20884,21 +20884,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594730</v>
+        <v>594728</v>
       </c>
       <c r="R197" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,7 +20980,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312224</v>
+        <v>133312215</v>
       </c>
       <c r="B198" t="n">
         <v>92217</v>
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594755</v>
+        <v>594730</v>
       </c>
       <c r="R198" t="n">
-        <v>6947667</v>
+        <v>6947645</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312239</v>
+        <v>133312224</v>
       </c>
       <c r="B199" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594784</v>
+        <v>594755</v>
       </c>
       <c r="R199" t="n">
-        <v>6947700</v>
+        <v>6947667</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21194,32 +21194,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133312277</v>
+        <v>133312209</v>
       </c>
       <c r="B200" t="n">
-        <v>92566</v>
+        <v>92217</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21229,10 +21229,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>594860</v>
+        <v>594725</v>
       </c>
       <c r="R200" t="n">
-        <v>6947799</v>
+        <v>6947645</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21274,12 +21274,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21288,7 +21283,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -21307,32 +21301,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133312209</v>
+        <v>133312277</v>
       </c>
       <c r="B201" t="n">
-        <v>92217</v>
+        <v>92566</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21342,10 +21336,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>594725</v>
+        <v>594860</v>
       </c>
       <c r="R201" t="n">
-        <v>6947645</v>
+        <v>6947799</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -21377,7 +21371,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21387,7 +21381,12 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21396,6 +21395,7 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12708,32 +12708,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312200</v>
+        <v>133312293</v>
       </c>
       <c r="B121" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594692</v>
+        <v>594745</v>
       </c>
       <c r="R121" t="n">
-        <v>6947605</v>
+        <v>6947738</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312241</v>
+        <v>133312229</v>
       </c>
       <c r="B122" t="n">
-        <v>79952</v>
+        <v>79365</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594784</v>
+        <v>594755</v>
       </c>
       <c r="R122" t="n">
-        <v>6947732</v>
+        <v>6947668</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,32 +12922,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312205</v>
+        <v>133312274</v>
       </c>
       <c r="B123" t="n">
-        <v>75433</v>
+        <v>92217</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594702</v>
+        <v>594857</v>
       </c>
       <c r="R123" t="n">
-        <v>6947615</v>
+        <v>6947775</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312293</v>
+        <v>133312284</v>
       </c>
       <c r="B124" t="n">
-        <v>91918</v>
+        <v>91868</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,13 +13064,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594745</v>
+        <v>594757</v>
       </c>
       <c r="R124" t="n">
-        <v>6947738</v>
+        <v>6947805</v>
       </c>
       <c r="S124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312229</v>
+        <v>133312200</v>
       </c>
       <c r="B125" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594755</v>
+        <v>594692</v>
       </c>
       <c r="R125" t="n">
-        <v>6947668</v>
+        <v>6947605</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,10 +13243,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312274</v>
+        <v>133312241</v>
       </c>
       <c r="B126" t="n">
-        <v>92217</v>
+        <v>79952</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,21 +13254,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594857</v>
+        <v>594784</v>
       </c>
       <c r="R126" t="n">
-        <v>6947775</v>
+        <v>6947732</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,32 +13350,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312284</v>
+        <v>133312205</v>
       </c>
       <c r="B127" t="n">
-        <v>91868</v>
+        <v>75433</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>112</v>
+        <v>6426</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594757</v>
+        <v>594702</v>
       </c>
       <c r="R127" t="n">
-        <v>6947805</v>
+        <v>6947615</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13890,10 +13890,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312247</v>
+        <v>133312305</v>
       </c>
       <c r="B132" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13901,21 +13901,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,13 +13925,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594801</v>
+        <v>594707</v>
       </c>
       <c r="R132" t="n">
-        <v>6947716</v>
+        <v>6947692</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312244</v>
+        <v>133312247</v>
       </c>
       <c r="B133" t="n">
-        <v>57145</v>
+        <v>92217</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594797</v>
+        <v>594801</v>
       </c>
       <c r="R133" t="n">
-        <v>6947735</v>
+        <v>6947716</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,12 +14077,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14109,32 +14104,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312305</v>
+        <v>133312244</v>
       </c>
       <c r="B134" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14144,13 +14139,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594707</v>
+        <v>594797</v>
       </c>
       <c r="R134" t="n">
-        <v>6947692</v>
+        <v>6947735</v>
       </c>
       <c r="S134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14179,7 +14174,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14189,7 +14184,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312299</v>
+        <v>133312221</v>
       </c>
       <c r="B135" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,34 +14227,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594747</v>
+        <v>594741</v>
       </c>
       <c r="R135" t="n">
-        <v>6947714</v>
+        <v>6947668</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14286,7 +14294,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14304,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14323,10 +14336,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312302</v>
+        <v>133312299</v>
       </c>
       <c r="B136" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14334,21 +14347,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14358,10 +14371,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594703</v>
+        <v>594747</v>
       </c>
       <c r="R136" t="n">
-        <v>6947719</v>
+        <v>6947714</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14393,7 +14406,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14403,7 +14416,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14430,10 +14443,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312294</v>
+        <v>133312302</v>
       </c>
       <c r="B137" t="n">
-        <v>89300</v>
+        <v>79365</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14441,21 +14454,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14465,10 +14478,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594735</v>
+        <v>594703</v>
       </c>
       <c r="R137" t="n">
-        <v>6947729</v>
+        <v>6947719</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14500,7 +14513,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14510,7 +14523,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14537,10 +14550,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312262</v>
+        <v>133312294</v>
       </c>
       <c r="B138" t="n">
-        <v>79365</v>
+        <v>89300</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,21 +14561,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14572,10 +14585,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594845</v>
+        <v>594735</v>
       </c>
       <c r="R138" t="n">
-        <v>6947767</v>
+        <v>6947729</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14607,7 +14620,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14617,7 +14630,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14644,10 +14657,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312221</v>
+        <v>133312262</v>
       </c>
       <c r="B139" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14655,42 +14668,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594741</v>
+        <v>594845</v>
       </c>
       <c r="R139" t="n">
-        <v>6947668</v>
+        <v>6947767</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14722,7 +14727,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14732,12 +14737,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312226</v>
+        <v>133312297</v>
       </c>
       <c r="B140" t="n">
-        <v>5199</v>
+        <v>91918</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594755</v>
+        <v>594737</v>
       </c>
       <c r="R140" t="n">
-        <v>6947670</v>
+        <v>6947721</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312297</v>
+        <v>133312272</v>
       </c>
       <c r="B141" t="n">
-        <v>91918</v>
+        <v>83315</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594737</v>
+        <v>594856</v>
       </c>
       <c r="R141" t="n">
-        <v>6947721</v>
+        <v>6947779</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312272</v>
+        <v>133312226</v>
       </c>
       <c r="B143" t="n">
-        <v>83315</v>
+        <v>5199</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594856</v>
+        <v>594755</v>
       </c>
       <c r="R143" t="n">
-        <v>6947779</v>
+        <v>6947670</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17765,10 +17765,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312319</v>
+        <v>133312259</v>
       </c>
       <c r="B168" t="n">
-        <v>91918</v>
+        <v>79952</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17776,21 +17776,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594662</v>
+        <v>594814</v>
       </c>
       <c r="R168" t="n">
-        <v>6947577</v>
+        <v>6947723</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312259</v>
+        <v>133312216</v>
       </c>
       <c r="B169" t="n">
-        <v>79952</v>
+        <v>92641</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>3298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594814</v>
+        <v>594730</v>
       </c>
       <c r="R169" t="n">
-        <v>6947723</v>
+        <v>6947646</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,32 +17979,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312216</v>
+        <v>133312280</v>
       </c>
       <c r="B170" t="n">
-        <v>92641</v>
+        <v>79090</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3298</v>
+        <v>6446</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594730</v>
+        <v>594788</v>
       </c>
       <c r="R170" t="n">
-        <v>6947646</v>
+        <v>6947813</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,32 +18086,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312280</v>
+        <v>133312313</v>
       </c>
       <c r="B171" t="n">
-        <v>79090</v>
+        <v>80474</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594788</v>
+        <v>594697</v>
       </c>
       <c r="R171" t="n">
-        <v>6947813</v>
+        <v>6947661</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,10 +18193,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312313</v>
+        <v>133312312</v>
       </c>
       <c r="B172" t="n">
-        <v>80474</v>
+        <v>80398</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18204,21 +18204,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18234,7 +18234,7 @@
         <v>6947661</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18300,32 +18300,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312312</v>
+        <v>133312319</v>
       </c>
       <c r="B173" t="n">
-        <v>80398</v>
+        <v>91918</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>594697</v>
+        <v>594662</v>
       </c>
       <c r="R173" t="n">
-        <v>6947661</v>
+        <v>6947577</v>
       </c>
       <c r="S173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18407,32 +18407,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133312243</v>
+        <v>133312308</v>
       </c>
       <c r="B174" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>594794</v>
+        <v>594707</v>
       </c>
       <c r="R174" t="n">
-        <v>6947729</v>
+        <v>6947669</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18514,10 +18514,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312212</v>
+        <v>133312243</v>
       </c>
       <c r="B175" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594721</v>
+        <v>594794</v>
       </c>
       <c r="R175" t="n">
-        <v>6947646</v>
+        <v>6947729</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18621,32 +18621,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312308</v>
+        <v>133312212</v>
       </c>
       <c r="B176" t="n">
-        <v>75433</v>
+        <v>91932</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6426</v>
+        <v>1204</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18656,10 +18656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594707</v>
+        <v>594721</v>
       </c>
       <c r="R176" t="n">
-        <v>6947669</v>
+        <v>6947646</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312265</v>
+        <v>133312194</v>
       </c>
       <c r="B182" t="n">
-        <v>79365</v>
+        <v>83315</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,13 +19303,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594823</v>
+        <v>594690</v>
       </c>
       <c r="R182" t="n">
-        <v>6947773</v>
+        <v>6947596</v>
       </c>
       <c r="S182" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,10 +19375,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312298</v>
+        <v>133312265</v>
       </c>
       <c r="B183" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19386,21 +19386,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19410,10 +19410,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594740</v>
+        <v>594823</v>
       </c>
       <c r="R183" t="n">
-        <v>6947716</v>
+        <v>6947773</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19482,7 +19482,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312240</v>
+        <v>133312298</v>
       </c>
       <c r="B184" t="n">
         <v>92217</v>
@@ -19517,13 +19517,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594782</v>
+        <v>594740</v>
       </c>
       <c r="R184" t="n">
-        <v>6947711</v>
+        <v>6947716</v>
       </c>
       <c r="S184" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19589,10 +19589,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133312194</v>
+        <v>133312240</v>
       </c>
       <c r="B185" t="n">
-        <v>83315</v>
+        <v>92217</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19600,21 +19600,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19624,10 +19624,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>594690</v>
+        <v>594782</v>
       </c>
       <c r="R185" t="n">
-        <v>6947596</v>
+        <v>6947711</v>
       </c>
       <c r="S185" t="n">
         <v>6</v>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19696,32 +19696,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312276</v>
+        <v>133312289</v>
       </c>
       <c r="B186" t="n">
-        <v>80398</v>
+        <v>92217</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,10 +19731,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594856</v>
+        <v>594777</v>
       </c>
       <c r="R186" t="n">
-        <v>6947759</v>
+        <v>6947757</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19803,10 +19803,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312289</v>
+        <v>133312225</v>
       </c>
       <c r="B187" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19814,21 +19814,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,10 +19838,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594777</v>
+        <v>594757</v>
       </c>
       <c r="R187" t="n">
-        <v>6947757</v>
+        <v>6947666</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,7 +19910,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312225</v>
+        <v>133312266</v>
       </c>
       <c r="B188" t="n">
         <v>91918</v>
@@ -19945,10 +19945,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594757</v>
+        <v>594820</v>
       </c>
       <c r="R188" t="n">
-        <v>6947666</v>
+        <v>6947773</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,32 +20017,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312266</v>
+        <v>133312316</v>
       </c>
       <c r="B189" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,13 +20052,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594820</v>
+        <v>594666</v>
       </c>
       <c r="R189" t="n">
-        <v>6947773</v>
+        <v>6947640</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,7 +20124,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312316</v>
+        <v>133312188</v>
       </c>
       <c r="B190" t="n">
         <v>75433</v>
@@ -20159,13 +20159,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594666</v>
+        <v>594698</v>
       </c>
       <c r="R190" t="n">
-        <v>6947640</v>
+        <v>6947587</v>
       </c>
       <c r="S190" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,10 +20231,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312188</v>
+        <v>133312236</v>
       </c>
       <c r="B191" t="n">
-        <v>75433</v>
+        <v>79357</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20242,21 +20242,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6426</v>
+        <v>6434</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594698</v>
+        <v>594742</v>
       </c>
       <c r="R191" t="n">
-        <v>6947587</v>
+        <v>6947701</v>
       </c>
       <c r="S191" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,10 +20338,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312236</v>
+        <v>133312197</v>
       </c>
       <c r="B192" t="n">
-        <v>79357</v>
+        <v>75433</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20349,21 +20349,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6434</v>
+        <v>6426</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594742</v>
+        <v>594687</v>
       </c>
       <c r="R192" t="n">
-        <v>6947701</v>
+        <v>6947597</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312197</v>
+        <v>133312318</v>
       </c>
       <c r="B193" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,7 +20480,7 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594687</v>
+        <v>594678</v>
       </c>
       <c r="R193" t="n">
         <v>6947597</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20552,32 +20552,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133312318</v>
+        <v>133312317</v>
       </c>
       <c r="B194" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20587,13 +20587,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>594678</v>
+        <v>594682</v>
       </c>
       <c r="R194" t="n">
-        <v>6947597</v>
+        <v>6947610</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20659,10 +20659,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133312317</v>
+        <v>133312276</v>
       </c>
       <c r="B195" t="n">
-        <v>75433</v>
+        <v>80398</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20670,21 +20670,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20694,13 +20694,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>594682</v>
+        <v>594856</v>
       </c>
       <c r="R195" t="n">
-        <v>6947610</v>
+        <v>6947759</v>
       </c>
       <c r="S195" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312239</v>
+        <v>133312219</v>
       </c>
       <c r="B196" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594784</v>
+        <v>594728</v>
       </c>
       <c r="R196" t="n">
-        <v>6947700</v>
+        <v>6947667</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312219</v>
+        <v>133312215</v>
       </c>
       <c r="B197" t="n">
-        <v>91932</v>
+        <v>92217</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20884,21 +20884,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594728</v>
+        <v>594730</v>
       </c>
       <c r="R197" t="n">
-        <v>6947667</v>
+        <v>6947645</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,7 +20980,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312215</v>
+        <v>133312224</v>
       </c>
       <c r="B198" t="n">
         <v>92217</v>
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594730</v>
+        <v>594755</v>
       </c>
       <c r="R198" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312224</v>
+        <v>133312239</v>
       </c>
       <c r="B199" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594755</v>
+        <v>594784</v>
       </c>
       <c r="R199" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD199" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12708,32 +12708,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312293</v>
+        <v>133312200</v>
       </c>
       <c r="B121" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594745</v>
+        <v>594692</v>
       </c>
       <c r="R121" t="n">
-        <v>6947738</v>
+        <v>6947605</v>
       </c>
       <c r="S121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312229</v>
+        <v>133312241</v>
       </c>
       <c r="B122" t="n">
-        <v>79365</v>
+        <v>79952</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594755</v>
+        <v>594784</v>
       </c>
       <c r="R122" t="n">
-        <v>6947668</v>
+        <v>6947732</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,32 +12922,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312274</v>
+        <v>133312205</v>
       </c>
       <c r="B123" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594857</v>
+        <v>594702</v>
       </c>
       <c r="R123" t="n">
-        <v>6947775</v>
+        <v>6947615</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312284</v>
+        <v>133312293</v>
       </c>
       <c r="B124" t="n">
-        <v>91868</v>
+        <v>91918</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,13 +13064,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594757</v>
+        <v>594745</v>
       </c>
       <c r="R124" t="n">
-        <v>6947805</v>
+        <v>6947738</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312200</v>
+        <v>133312229</v>
       </c>
       <c r="B125" t="n">
-        <v>75433</v>
+        <v>79365</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594692</v>
+        <v>594755</v>
       </c>
       <c r="R125" t="n">
-        <v>6947605</v>
+        <v>6947668</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,10 +13243,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312241</v>
+        <v>133312274</v>
       </c>
       <c r="B126" t="n">
-        <v>79952</v>
+        <v>92217</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,21 +13254,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594784</v>
+        <v>594857</v>
       </c>
       <c r="R126" t="n">
-        <v>6947732</v>
+        <v>6947775</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,32 +13350,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312205</v>
+        <v>133312284</v>
       </c>
       <c r="B127" t="n">
-        <v>75433</v>
+        <v>91868</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6426</v>
+        <v>112</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594702</v>
+        <v>594757</v>
       </c>
       <c r="R127" t="n">
-        <v>6947615</v>
+        <v>6947805</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13457,32 +13457,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312257</v>
+        <v>133312184</v>
       </c>
       <c r="B128" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,10 +13492,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594820</v>
+        <v>594713</v>
       </c>
       <c r="R128" t="n">
-        <v>6947705</v>
+        <v>6947589</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13564,32 +13564,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312184</v>
+        <v>133312246</v>
       </c>
       <c r="B129" t="n">
-        <v>75433</v>
+        <v>79952</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,13 +13599,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594713</v>
+        <v>594810</v>
       </c>
       <c r="R129" t="n">
-        <v>6947589</v>
+        <v>6947725</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13671,10 +13671,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312246</v>
+        <v>133312263</v>
       </c>
       <c r="B130" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13682,21 +13682,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13706,13 +13706,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594810</v>
+        <v>594826</v>
       </c>
       <c r="R130" t="n">
-        <v>6947725</v>
+        <v>6947773</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13751,7 +13751,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13778,10 +13783,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312263</v>
+        <v>133312257</v>
       </c>
       <c r="B131" t="n">
-        <v>57955</v>
+        <v>79365</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13789,21 +13794,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13813,10 +13818,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594826</v>
+        <v>594820</v>
       </c>
       <c r="R131" t="n">
-        <v>6947773</v>
+        <v>6947705</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -13848,7 +13853,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13858,12 +13863,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13890,10 +13890,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312305</v>
+        <v>133312247</v>
       </c>
       <c r="B132" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13901,21 +13901,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,13 +13925,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594707</v>
+        <v>594801</v>
       </c>
       <c r="R132" t="n">
-        <v>6947692</v>
+        <v>6947716</v>
       </c>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312247</v>
+        <v>133312244</v>
       </c>
       <c r="B133" t="n">
-        <v>92217</v>
+        <v>57145</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594801</v>
+        <v>594797</v>
       </c>
       <c r="R133" t="n">
-        <v>6947716</v>
+        <v>6947735</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,7 +14077,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14104,32 +14109,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312244</v>
+        <v>133312305</v>
       </c>
       <c r="B134" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14139,13 +14144,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594797</v>
+        <v>594707</v>
       </c>
       <c r="R134" t="n">
-        <v>6947735</v>
+        <v>6947692</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14174,7 +14179,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14184,12 +14189,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312297</v>
+        <v>133312226</v>
       </c>
       <c r="B140" t="n">
-        <v>91918</v>
+        <v>5199</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594737</v>
+        <v>594755</v>
       </c>
       <c r="R140" t="n">
-        <v>6947721</v>
+        <v>6947670</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312272</v>
+        <v>133312297</v>
       </c>
       <c r="B141" t="n">
-        <v>83315</v>
+        <v>91918</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594856</v>
+        <v>594737</v>
       </c>
       <c r="R141" t="n">
-        <v>6947779</v>
+        <v>6947721</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312226</v>
+        <v>133312272</v>
       </c>
       <c r="B143" t="n">
-        <v>5199</v>
+        <v>83315</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594755</v>
+        <v>594856</v>
       </c>
       <c r="R143" t="n">
-        <v>6947670</v>
+        <v>6947779</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16909,32 +16909,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133312198</v>
+        <v>133312208</v>
       </c>
       <c r="B160" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16944,10 +16944,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>594683</v>
+        <v>594728</v>
       </c>
       <c r="R160" t="n">
-        <v>6947603</v>
+        <v>6947607</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17016,10 +17016,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133312306</v>
+        <v>133312198</v>
       </c>
       <c r="B161" t="n">
-        <v>80342</v>
+        <v>75433</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17027,21 +17027,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17051,13 +17051,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>594711</v>
+        <v>594683</v>
       </c>
       <c r="R161" t="n">
-        <v>6947680</v>
+        <v>6947603</v>
       </c>
       <c r="S161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17123,10 +17123,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312206</v>
+        <v>133312306</v>
       </c>
       <c r="B162" t="n">
-        <v>75433</v>
+        <v>80342</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17134,21 +17134,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17158,13 +17158,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594719</v>
+        <v>594711</v>
       </c>
       <c r="R162" t="n">
-        <v>6947615</v>
+        <v>6947680</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17230,32 +17230,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133312208</v>
+        <v>133312206</v>
       </c>
       <c r="B163" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>594728</v>
+        <v>594719</v>
       </c>
       <c r="R163" t="n">
-        <v>6947607</v>
+        <v>6947615</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312219</v>
+        <v>133312239</v>
       </c>
       <c r="B196" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594728</v>
+        <v>594784</v>
       </c>
       <c r="R196" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312215</v>
+        <v>133312219</v>
       </c>
       <c r="B197" t="n">
-        <v>92217</v>
+        <v>91932</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20884,21 +20884,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594730</v>
+        <v>594728</v>
       </c>
       <c r="R197" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,7 +20980,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312224</v>
+        <v>133312215</v>
       </c>
       <c r="B198" t="n">
         <v>92217</v>
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594755</v>
+        <v>594730</v>
       </c>
       <c r="R198" t="n">
-        <v>6947667</v>
+        <v>6947645</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312239</v>
+        <v>133312224</v>
       </c>
       <c r="B199" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594784</v>
+        <v>594755</v>
       </c>
       <c r="R199" t="n">
-        <v>6947700</v>
+        <v>6947667</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD199" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312194</v>
+        <v>133312265</v>
       </c>
       <c r="B182" t="n">
-        <v>83315</v>
+        <v>79365</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,13 +19303,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594690</v>
+        <v>594823</v>
       </c>
       <c r="R182" t="n">
-        <v>6947596</v>
+        <v>6947773</v>
       </c>
       <c r="S182" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,10 +19375,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312265</v>
+        <v>133312298</v>
       </c>
       <c r="B183" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19386,21 +19386,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19410,10 +19410,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594823</v>
+        <v>594740</v>
       </c>
       <c r="R183" t="n">
-        <v>6947773</v>
+        <v>6947716</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19482,7 +19482,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312298</v>
+        <v>133312240</v>
       </c>
       <c r="B184" t="n">
         <v>92217</v>
@@ -19517,13 +19517,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594740</v>
+        <v>594782</v>
       </c>
       <c r="R184" t="n">
-        <v>6947716</v>
+        <v>6947711</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19589,10 +19589,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133312240</v>
+        <v>133312194</v>
       </c>
       <c r="B185" t="n">
-        <v>92217</v>
+        <v>83315</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19600,21 +19600,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19624,10 +19624,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>594782</v>
+        <v>594690</v>
       </c>
       <c r="R185" t="n">
-        <v>6947711</v>
+        <v>6947596</v>
       </c>
       <c r="S185" t="n">
         <v>6</v>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD185" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12708,32 +12708,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312200</v>
+        <v>133312293</v>
       </c>
       <c r="B121" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594692</v>
+        <v>594745</v>
       </c>
       <c r="R121" t="n">
-        <v>6947605</v>
+        <v>6947738</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312241</v>
+        <v>133312229</v>
       </c>
       <c r="B122" t="n">
-        <v>79952</v>
+        <v>79365</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594784</v>
+        <v>594755</v>
       </c>
       <c r="R122" t="n">
-        <v>6947732</v>
+        <v>6947668</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,32 +12922,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312205</v>
+        <v>133312274</v>
       </c>
       <c r="B123" t="n">
-        <v>75433</v>
+        <v>92217</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594702</v>
+        <v>594857</v>
       </c>
       <c r="R123" t="n">
-        <v>6947615</v>
+        <v>6947775</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312293</v>
+        <v>133312284</v>
       </c>
       <c r="B124" t="n">
-        <v>91918</v>
+        <v>91868</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,13 +13064,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594745</v>
+        <v>594757</v>
       </c>
       <c r="R124" t="n">
-        <v>6947738</v>
+        <v>6947805</v>
       </c>
       <c r="S124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312229</v>
+        <v>133312200</v>
       </c>
       <c r="B125" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594755</v>
+        <v>594692</v>
       </c>
       <c r="R125" t="n">
-        <v>6947668</v>
+        <v>6947605</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,10 +13243,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312274</v>
+        <v>133312241</v>
       </c>
       <c r="B126" t="n">
-        <v>92217</v>
+        <v>79952</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,21 +13254,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594857</v>
+        <v>594784</v>
       </c>
       <c r="R126" t="n">
-        <v>6947775</v>
+        <v>6947732</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,32 +13350,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312284</v>
+        <v>133312205</v>
       </c>
       <c r="B127" t="n">
-        <v>91868</v>
+        <v>75433</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>112</v>
+        <v>6426</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594757</v>
+        <v>594702</v>
       </c>
       <c r="R127" t="n">
-        <v>6947805</v>
+        <v>6947615</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13457,32 +13457,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312184</v>
+        <v>133312257</v>
       </c>
       <c r="B128" t="n">
-        <v>75433</v>
+        <v>79365</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,10 +13492,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594713</v>
+        <v>594820</v>
       </c>
       <c r="R128" t="n">
-        <v>6947589</v>
+        <v>6947705</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13564,32 +13564,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312246</v>
+        <v>133312184</v>
       </c>
       <c r="B129" t="n">
-        <v>79952</v>
+        <v>75433</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,13 +13599,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594810</v>
+        <v>594713</v>
       </c>
       <c r="R129" t="n">
-        <v>6947725</v>
+        <v>6947589</v>
       </c>
       <c r="S129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13671,10 +13671,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312263</v>
+        <v>133312246</v>
       </c>
       <c r="B130" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13682,21 +13682,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13706,13 +13706,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594826</v>
+        <v>594810</v>
       </c>
       <c r="R130" t="n">
-        <v>6947773</v>
+        <v>6947725</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13751,12 +13751,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13783,10 +13778,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312257</v>
+        <v>133312263</v>
       </c>
       <c r="B131" t="n">
-        <v>79365</v>
+        <v>57955</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13794,21 +13789,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13818,10 +13813,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594820</v>
+        <v>594826</v>
       </c>
       <c r="R131" t="n">
-        <v>6947705</v>
+        <v>6947773</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -13853,7 +13848,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13863,7 +13858,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312221</v>
+        <v>133312299</v>
       </c>
       <c r="B135" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,42 +14227,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594741</v>
+        <v>594747</v>
       </c>
       <c r="R135" t="n">
-        <v>6947668</v>
+        <v>6947714</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14294,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14304,12 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14336,10 +14323,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312299</v>
+        <v>133312302</v>
       </c>
       <c r="B136" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14347,21 +14334,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14371,10 +14358,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594747</v>
+        <v>594703</v>
       </c>
       <c r="R136" t="n">
-        <v>6947714</v>
+        <v>6947719</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14406,7 +14393,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14416,7 +14403,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14443,10 +14430,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312302</v>
+        <v>133312294</v>
       </c>
       <c r="B137" t="n">
-        <v>79365</v>
+        <v>89300</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14454,21 +14441,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14478,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594703</v>
+        <v>594735</v>
       </c>
       <c r="R137" t="n">
-        <v>6947719</v>
+        <v>6947729</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14513,7 +14500,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14523,7 +14510,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14550,10 +14537,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312294</v>
+        <v>133312262</v>
       </c>
       <c r="B138" t="n">
-        <v>89300</v>
+        <v>79365</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14561,21 +14548,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14585,10 +14572,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594735</v>
+        <v>594845</v>
       </c>
       <c r="R138" t="n">
-        <v>6947729</v>
+        <v>6947767</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14620,7 +14607,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14630,7 +14617,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14657,10 +14644,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312262</v>
+        <v>133312221</v>
       </c>
       <c r="B139" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14668,34 +14655,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594845</v>
+        <v>594741</v>
       </c>
       <c r="R139" t="n">
-        <v>6947767</v>
+        <v>6947668</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14727,7 +14722,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14737,7 +14732,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312226</v>
+        <v>133312297</v>
       </c>
       <c r="B140" t="n">
-        <v>5199</v>
+        <v>91918</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594755</v>
+        <v>594737</v>
       </c>
       <c r="R140" t="n">
-        <v>6947670</v>
+        <v>6947721</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312297</v>
+        <v>133312272</v>
       </c>
       <c r="B141" t="n">
-        <v>91918</v>
+        <v>83315</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594737</v>
+        <v>594856</v>
       </c>
       <c r="R141" t="n">
-        <v>6947721</v>
+        <v>6947779</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312272</v>
+        <v>133312226</v>
       </c>
       <c r="B143" t="n">
-        <v>83315</v>
+        <v>5199</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594856</v>
+        <v>594755</v>
       </c>
       <c r="R143" t="n">
-        <v>6947779</v>
+        <v>6947670</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16909,32 +16909,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133312208</v>
+        <v>133312198</v>
       </c>
       <c r="B160" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16944,10 +16944,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>594728</v>
+        <v>594683</v>
       </c>
       <c r="R160" t="n">
-        <v>6947607</v>
+        <v>6947603</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17016,10 +17016,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133312198</v>
+        <v>133312306</v>
       </c>
       <c r="B161" t="n">
-        <v>75433</v>
+        <v>80342</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17027,21 +17027,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17051,13 +17051,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>594683</v>
+        <v>594711</v>
       </c>
       <c r="R161" t="n">
-        <v>6947603</v>
+        <v>6947680</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17123,10 +17123,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312306</v>
+        <v>133312206</v>
       </c>
       <c r="B162" t="n">
-        <v>80342</v>
+        <v>75433</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17134,21 +17134,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17158,13 +17158,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594711</v>
+        <v>594719</v>
       </c>
       <c r="R162" t="n">
-        <v>6947680</v>
+        <v>6947615</v>
       </c>
       <c r="S162" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17230,32 +17230,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133312206</v>
+        <v>133312208</v>
       </c>
       <c r="B163" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>594719</v>
+        <v>594728</v>
       </c>
       <c r="R163" t="n">
-        <v>6947615</v>
+        <v>6947607</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18407,32 +18407,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133312308</v>
+        <v>133312243</v>
       </c>
       <c r="B174" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>594707</v>
+        <v>594794</v>
       </c>
       <c r="R174" t="n">
-        <v>6947669</v>
+        <v>6947729</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18514,10 +18514,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312243</v>
+        <v>133312212</v>
       </c>
       <c r="B175" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594794</v>
+        <v>594721</v>
       </c>
       <c r="R175" t="n">
-        <v>6947729</v>
+        <v>6947646</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18621,32 +18621,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312212</v>
+        <v>133312308</v>
       </c>
       <c r="B176" t="n">
-        <v>91932</v>
+        <v>75433</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1204</v>
+        <v>6426</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18656,10 +18656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594721</v>
+        <v>594707</v>
       </c>
       <c r="R176" t="n">
-        <v>6947646</v>
+        <v>6947669</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312265</v>
+        <v>133312194</v>
       </c>
       <c r="B182" t="n">
-        <v>79365</v>
+        <v>83315</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,13 +19303,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594823</v>
+        <v>594690</v>
       </c>
       <c r="R182" t="n">
-        <v>6947773</v>
+        <v>6947596</v>
       </c>
       <c r="S182" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,10 +19375,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312298</v>
+        <v>133312265</v>
       </c>
       <c r="B183" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19386,21 +19386,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19410,10 +19410,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594740</v>
+        <v>594823</v>
       </c>
       <c r="R183" t="n">
-        <v>6947716</v>
+        <v>6947773</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19482,7 +19482,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312240</v>
+        <v>133312298</v>
       </c>
       <c r="B184" t="n">
         <v>92217</v>
@@ -19517,13 +19517,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594782</v>
+        <v>594740</v>
       </c>
       <c r="R184" t="n">
-        <v>6947711</v>
+        <v>6947716</v>
       </c>
       <c r="S184" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19589,10 +19589,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133312194</v>
+        <v>133312240</v>
       </c>
       <c r="B185" t="n">
-        <v>83315</v>
+        <v>92217</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19600,21 +19600,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19624,10 +19624,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>594690</v>
+        <v>594782</v>
       </c>
       <c r="R185" t="n">
-        <v>6947596</v>
+        <v>6947711</v>
       </c>
       <c r="S185" t="n">
         <v>6</v>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312239</v>
+        <v>133312219</v>
       </c>
       <c r="B196" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594784</v>
+        <v>594728</v>
       </c>
       <c r="R196" t="n">
-        <v>6947700</v>
+        <v>6947667</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312219</v>
+        <v>133312215</v>
       </c>
       <c r="B197" t="n">
-        <v>91932</v>
+        <v>92217</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20884,21 +20884,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594728</v>
+        <v>594730</v>
       </c>
       <c r="R197" t="n">
-        <v>6947667</v>
+        <v>6947645</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,7 +20980,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312215</v>
+        <v>133312224</v>
       </c>
       <c r="B198" t="n">
         <v>92217</v>
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594730</v>
+        <v>594755</v>
       </c>
       <c r="R198" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312224</v>
+        <v>133312239</v>
       </c>
       <c r="B199" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594755</v>
+        <v>594784</v>
       </c>
       <c r="R199" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD199" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12390,7 +12390,7 @@
         <v>133312282</v>
       </c>
       <c r="B118" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>133312232</v>
       </c>
       <c r="B119" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>133312291</v>
       </c>
       <c r="B120" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>133312293</v>
       </c>
       <c r="B121" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12815,10 +12815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312229</v>
+        <v>133312274</v>
       </c>
       <c r="B122" t="n">
-        <v>79365</v>
+        <v>92219</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594755</v>
+        <v>594857</v>
       </c>
       <c r="R122" t="n">
-        <v>6947668</v>
+        <v>6947775</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,32 +12922,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312274</v>
+        <v>133312200</v>
       </c>
       <c r="B123" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594857</v>
+        <v>594692</v>
       </c>
       <c r="R123" t="n">
-        <v>6947775</v>
+        <v>6947605</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312284</v>
+        <v>133312241</v>
       </c>
       <c r="B124" t="n">
-        <v>91868</v>
+        <v>79953</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594757</v>
+        <v>594784</v>
       </c>
       <c r="R124" t="n">
-        <v>6947805</v>
+        <v>6947732</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,7 +13136,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312200</v>
+        <v>133312205</v>
       </c>
       <c r="B125" t="n">
         <v>75433</v>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594692</v>
+        <v>594702</v>
       </c>
       <c r="R125" t="n">
-        <v>6947605</v>
+        <v>6947615</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,10 +13243,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312241</v>
+        <v>133312229</v>
       </c>
       <c r="B126" t="n">
-        <v>79952</v>
+        <v>79366</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,21 +13254,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594784</v>
+        <v>594755</v>
       </c>
       <c r="R126" t="n">
-        <v>6947732</v>
+        <v>6947668</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,32 +13350,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312205</v>
+        <v>133312284</v>
       </c>
       <c r="B127" t="n">
-        <v>75433</v>
+        <v>91870</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6426</v>
+        <v>112</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594702</v>
+        <v>594757</v>
       </c>
       <c r="R127" t="n">
-        <v>6947615</v>
+        <v>6947805</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13460,7 +13460,7 @@
         <v>133312257</v>
       </c>
       <c r="B128" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>133312246</v>
       </c>
       <c r="B130" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13890,10 +13890,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312247</v>
+        <v>133312305</v>
       </c>
       <c r="B132" t="n">
-        <v>92217</v>
+        <v>79334</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13901,21 +13901,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,13 +13925,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594801</v>
+        <v>594707</v>
       </c>
       <c r="R132" t="n">
-        <v>6947716</v>
+        <v>6947692</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14109,10 +14109,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312305</v>
+        <v>133312247</v>
       </c>
       <c r="B134" t="n">
-        <v>79333</v>
+        <v>92219</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14120,21 +14120,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14144,13 +14144,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594707</v>
+        <v>594801</v>
       </c>
       <c r="R134" t="n">
-        <v>6947692</v>
+        <v>6947716</v>
       </c>
       <c r="S134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312299</v>
+        <v>133312221</v>
       </c>
       <c r="B135" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,34 +14227,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594747</v>
+        <v>594741</v>
       </c>
       <c r="R135" t="n">
-        <v>6947714</v>
+        <v>6947668</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14286,7 +14294,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14304,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14326,7 +14339,7 @@
         <v>133312302</v>
       </c>
       <c r="B136" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14430,10 +14443,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312294</v>
+        <v>133312299</v>
       </c>
       <c r="B137" t="n">
-        <v>89300</v>
+        <v>92219</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14441,21 +14454,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14465,10 +14478,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594735</v>
+        <v>594747</v>
       </c>
       <c r="R137" t="n">
-        <v>6947729</v>
+        <v>6947714</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14500,7 +14513,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14510,7 +14523,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14537,10 +14550,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312262</v>
+        <v>133312294</v>
       </c>
       <c r="B138" t="n">
-        <v>79365</v>
+        <v>89302</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,21 +14561,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14572,10 +14585,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594845</v>
+        <v>594735</v>
       </c>
       <c r="R138" t="n">
-        <v>6947767</v>
+        <v>6947729</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14607,7 +14620,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14617,7 +14630,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14644,10 +14657,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312221</v>
+        <v>133312262</v>
       </c>
       <c r="B139" t="n">
-        <v>57958</v>
+        <v>79366</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14655,42 +14668,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594741</v>
+        <v>594845</v>
       </c>
       <c r="R139" t="n">
-        <v>6947668</v>
+        <v>6947767</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14722,7 +14727,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14732,12 +14737,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312297</v>
+        <v>133312226</v>
       </c>
       <c r="B140" t="n">
-        <v>91918</v>
+        <v>5199</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594737</v>
+        <v>594755</v>
       </c>
       <c r="R140" t="n">
-        <v>6947721</v>
+        <v>6947670</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14874,7 +14874,7 @@
         <v>133312272</v>
       </c>
       <c r="B141" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14978,10 +14978,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133312320</v>
+        <v>133312297</v>
       </c>
       <c r="B142" t="n">
-        <v>79365</v>
+        <v>91920</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14989,21 +14989,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,13 +15013,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>594653</v>
+        <v>594737</v>
       </c>
       <c r="R142" t="n">
-        <v>6947566</v>
+        <v>6947721</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312226</v>
+        <v>133312320</v>
       </c>
       <c r="B143" t="n">
-        <v>5199</v>
+        <v>79366</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594755</v>
+        <v>594653</v>
       </c>
       <c r="R143" t="n">
-        <v>6947670</v>
+        <v>6947566</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15192,10 +15192,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133312222</v>
+        <v>133312195</v>
       </c>
       <c r="B144" t="n">
-        <v>91932</v>
+        <v>83182</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15203,21 +15203,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15227,13 +15227,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>594755</v>
+        <v>594690</v>
       </c>
       <c r="R144" t="n">
-        <v>6947667</v>
+        <v>6947596</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15299,10 +15299,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133312195</v>
+        <v>133312222</v>
       </c>
       <c r="B145" t="n">
-        <v>83181</v>
+        <v>91934</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15310,21 +15310,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>594690</v>
+        <v>594755</v>
       </c>
       <c r="R145" t="n">
-        <v>6947596</v>
+        <v>6947667</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15406,10 +15406,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133312304</v>
+        <v>133312288</v>
       </c>
       <c r="B146" t="n">
-        <v>92217</v>
+        <v>79953</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15417,21 +15417,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>594716</v>
+        <v>594771</v>
       </c>
       <c r="R146" t="n">
-        <v>6947701</v>
+        <v>6947766</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15516,7 +15516,7 @@
         <v>133312250</v>
       </c>
       <c r="B147" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15620,10 +15620,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133312181</v>
+        <v>133312304</v>
       </c>
       <c r="B148" t="n">
-        <v>91918</v>
+        <v>92219</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15631,21 +15631,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>594723</v>
+        <v>594716</v>
       </c>
       <c r="R148" t="n">
-        <v>6947583</v>
+        <v>6947701</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15730,7 +15730,7 @@
         <v>133312252</v>
       </c>
       <c r="B149" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15834,10 +15834,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133312288</v>
+        <v>133312181</v>
       </c>
       <c r="B150" t="n">
-        <v>79952</v>
+        <v>91920</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15845,21 +15845,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>594771</v>
+        <v>594723</v>
       </c>
       <c r="R150" t="n">
-        <v>6947766</v>
+        <v>6947583</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15944,7 +15944,7 @@
         <v>133312218</v>
       </c>
       <c r="B151" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>133312189</v>
       </c>
       <c r="B152" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>133312303</v>
       </c>
       <c r="B153" t="n">
-        <v>80466</v>
+        <v>80467</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>133312271</v>
       </c>
       <c r="B155" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>133312253</v>
       </c>
       <c r="B156" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16588,10 +16588,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133312295</v>
+        <v>133312182</v>
       </c>
       <c r="B157" t="n">
-        <v>92217</v>
+        <v>79366</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16599,21 +16599,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16623,10 +16623,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>594733</v>
+        <v>594709</v>
       </c>
       <c r="R157" t="n">
-        <v>6947724</v>
+        <v>6947587</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16695,10 +16695,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133312182</v>
+        <v>133312295</v>
       </c>
       <c r="B158" t="n">
-        <v>79365</v>
+        <v>92219</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16706,21 +16706,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16730,10 +16730,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>594709</v>
+        <v>594733</v>
       </c>
       <c r="R158" t="n">
-        <v>6947587</v>
+        <v>6947724</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16909,32 +16909,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133312198</v>
+        <v>133312208</v>
       </c>
       <c r="B160" t="n">
-        <v>75433</v>
+        <v>91920</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16944,10 +16944,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>594683</v>
+        <v>594728</v>
       </c>
       <c r="R160" t="n">
-        <v>6947603</v>
+        <v>6947607</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17016,10 +17016,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133312306</v>
+        <v>133312198</v>
       </c>
       <c r="B161" t="n">
-        <v>80342</v>
+        <v>75433</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17027,21 +17027,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17051,13 +17051,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>594711</v>
+        <v>594683</v>
       </c>
       <c r="R161" t="n">
-        <v>6947680</v>
+        <v>6947603</v>
       </c>
       <c r="S161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17123,10 +17123,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312206</v>
+        <v>133312306</v>
       </c>
       <c r="B162" t="n">
-        <v>75433</v>
+        <v>80343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17134,21 +17134,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17158,13 +17158,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594719</v>
+        <v>594711</v>
       </c>
       <c r="R162" t="n">
-        <v>6947615</v>
+        <v>6947680</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17230,32 +17230,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133312208</v>
+        <v>133312206</v>
       </c>
       <c r="B163" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>594728</v>
+        <v>594719</v>
       </c>
       <c r="R163" t="n">
-        <v>6947607</v>
+        <v>6947615</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17340,7 +17340,7 @@
         <v>133312279</v>
       </c>
       <c r="B164" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17444,10 +17444,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133312300</v>
+        <v>133312203</v>
       </c>
       <c r="B165" t="n">
-        <v>91918</v>
+        <v>83182</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17455,21 +17455,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>594724</v>
+        <v>594694</v>
       </c>
       <c r="R165" t="n">
-        <v>6947715</v>
+        <v>6947611</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17551,10 +17551,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133312203</v>
+        <v>133312300</v>
       </c>
       <c r="B166" t="n">
-        <v>83181</v>
+        <v>91920</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>594694</v>
+        <v>594724</v>
       </c>
       <c r="R166" t="n">
-        <v>6947611</v>
+        <v>6947715</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17661,7 +17661,7 @@
         <v>133312234</v>
       </c>
       <c r="B167" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312259</v>
+        <v>133312312</v>
       </c>
       <c r="B168" t="n">
-        <v>79952</v>
+        <v>80399</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,13 +17800,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594814</v>
+        <v>594697</v>
       </c>
       <c r="R168" t="n">
-        <v>6947723</v>
+        <v>6947661</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17875,7 +17875,7 @@
         <v>133312216</v>
       </c>
       <c r="B169" t="n">
-        <v>92641</v>
+        <v>92643</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17979,10 +17979,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312280</v>
+        <v>133312319</v>
       </c>
       <c r="B170" t="n">
-        <v>79090</v>
+        <v>91920</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17990,21 +17990,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594788</v>
+        <v>594662</v>
       </c>
       <c r="R170" t="n">
-        <v>6947813</v>
+        <v>6947577</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,32 +18086,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312313</v>
+        <v>133312259</v>
       </c>
       <c r="B171" t="n">
-        <v>80474</v>
+        <v>79953</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594697</v>
+        <v>594814</v>
       </c>
       <c r="R171" t="n">
-        <v>6947661</v>
+        <v>6947723</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,32 +18193,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312312</v>
+        <v>133312280</v>
       </c>
       <c r="B172" t="n">
-        <v>80398</v>
+        <v>79091</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,13 +18228,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594697</v>
+        <v>594788</v>
       </c>
       <c r="R172" t="n">
-        <v>6947661</v>
+        <v>6947813</v>
       </c>
       <c r="S172" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18300,32 +18300,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312319</v>
+        <v>133312313</v>
       </c>
       <c r="B173" t="n">
-        <v>91918</v>
+        <v>80475</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18335,10 +18335,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>594662</v>
+        <v>594697</v>
       </c>
       <c r="R173" t="n">
-        <v>6947577</v>
+        <v>6947661</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18407,10 +18407,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133312243</v>
+        <v>133312212</v>
       </c>
       <c r="B174" t="n">
-        <v>91918</v>
+        <v>91934</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18418,21 +18418,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>594794</v>
+        <v>594721</v>
       </c>
       <c r="R174" t="n">
-        <v>6947729</v>
+        <v>6947646</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18514,10 +18514,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312212</v>
+        <v>133312243</v>
       </c>
       <c r="B175" t="n">
-        <v>91932</v>
+        <v>91920</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594721</v>
+        <v>594794</v>
       </c>
       <c r="R175" t="n">
-        <v>6947646</v>
+        <v>6947729</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18840,10 +18840,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>133312179</v>
+        <v>133312213</v>
       </c>
       <c r="B178" t="n">
-        <v>79365</v>
+        <v>91920</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18851,21 +18851,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18875,10 +18875,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>594731</v>
+        <v>594725</v>
       </c>
       <c r="R178" t="n">
-        <v>6947567</v>
+        <v>6947645</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18947,10 +18947,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>133312213</v>
+        <v>133312179</v>
       </c>
       <c r="B179" t="n">
-        <v>91918</v>
+        <v>79366</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18958,21 +18958,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18982,10 +18982,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>594725</v>
+        <v>594731</v>
       </c>
       <c r="R179" t="n">
-        <v>6947645</v>
+        <v>6947567</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19057,7 +19057,7 @@
         <v>133312286</v>
       </c>
       <c r="B180" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>133312194</v>
       </c>
       <c r="B182" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19375,10 +19375,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312265</v>
+        <v>133312240</v>
       </c>
       <c r="B183" t="n">
-        <v>79365</v>
+        <v>92219</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19386,21 +19386,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19410,13 +19410,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594823</v>
+        <v>594782</v>
       </c>
       <c r="R183" t="n">
-        <v>6947773</v>
+        <v>6947711</v>
       </c>
       <c r="S183" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19485,7 +19485,7 @@
         <v>133312298</v>
       </c>
       <c r="B184" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19589,10 +19589,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133312240</v>
+        <v>133312265</v>
       </c>
       <c r="B185" t="n">
-        <v>92217</v>
+        <v>79366</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19600,21 +19600,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19624,13 +19624,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>594782</v>
+        <v>594823</v>
       </c>
       <c r="R185" t="n">
-        <v>6947711</v>
+        <v>6947773</v>
       </c>
       <c r="S185" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19696,32 +19696,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312289</v>
+        <v>133312316</v>
       </c>
       <c r="B186" t="n">
-        <v>92217</v>
+        <v>75433</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594777</v>
+        <v>594666</v>
       </c>
       <c r="R186" t="n">
-        <v>6947757</v>
+        <v>6947640</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19803,32 +19803,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312225</v>
+        <v>133312188</v>
       </c>
       <c r="B187" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,13 +19838,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594757</v>
+        <v>594698</v>
       </c>
       <c r="R187" t="n">
-        <v>6947666</v>
+        <v>6947587</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,32 +19910,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312266</v>
+        <v>133312236</v>
       </c>
       <c r="B188" t="n">
-        <v>91918</v>
+        <v>79358</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,10 +19945,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594820</v>
+        <v>594742</v>
       </c>
       <c r="R188" t="n">
-        <v>6947773</v>
+        <v>6947701</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,7 +20017,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312316</v>
+        <v>133312197</v>
       </c>
       <c r="B189" t="n">
         <v>75433</v>
@@ -20052,13 +20052,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594666</v>
+        <v>594687</v>
       </c>
       <c r="R189" t="n">
-        <v>6947640</v>
+        <v>6947597</v>
       </c>
       <c r="S189" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,32 +20124,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312188</v>
+        <v>133312318</v>
       </c>
       <c r="B190" t="n">
-        <v>75433</v>
+        <v>79334</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20159,13 +20159,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594698</v>
+        <v>594678</v>
       </c>
       <c r="R190" t="n">
-        <v>6947587</v>
+        <v>6947597</v>
       </c>
       <c r="S190" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,10 +20231,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312236</v>
+        <v>133312317</v>
       </c>
       <c r="B191" t="n">
-        <v>79357</v>
+        <v>75433</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20242,21 +20242,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6434</v>
+        <v>6426</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594742</v>
+        <v>594682</v>
       </c>
       <c r="R191" t="n">
-        <v>6947701</v>
+        <v>6947610</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,10 +20338,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312197</v>
+        <v>133312276</v>
       </c>
       <c r="B192" t="n">
-        <v>75433</v>
+        <v>80399</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20349,21 +20349,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594687</v>
+        <v>594856</v>
       </c>
       <c r="R192" t="n">
-        <v>6947597</v>
+        <v>6947759</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,10 +20445,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312318</v>
+        <v>133312289</v>
       </c>
       <c r="B193" t="n">
-        <v>79333</v>
+        <v>92219</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20456,21 +20456,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,10 +20480,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594678</v>
+        <v>594777</v>
       </c>
       <c r="R193" t="n">
-        <v>6947597</v>
+        <v>6947757</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20552,32 +20552,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133312317</v>
+        <v>133312266</v>
       </c>
       <c r="B194" t="n">
-        <v>75433</v>
+        <v>91920</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20587,13 +20587,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>594682</v>
+        <v>594820</v>
       </c>
       <c r="R194" t="n">
-        <v>6947610</v>
+        <v>6947773</v>
       </c>
       <c r="S194" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20659,32 +20659,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133312276</v>
+        <v>133312225</v>
       </c>
       <c r="B195" t="n">
-        <v>80398</v>
+        <v>91920</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20694,10 +20694,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>594856</v>
+        <v>594757</v>
       </c>
       <c r="R195" t="n">
-        <v>6947759</v>
+        <v>6947666</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20769,7 +20769,7 @@
         <v>133312219</v>
       </c>
       <c r="B196" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>133312215</v>
       </c>
       <c r="B197" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>133312224</v>
       </c>
       <c r="B198" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>133312239</v>
       </c>
       <c r="B199" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21194,32 +21194,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133312209</v>
+        <v>133312277</v>
       </c>
       <c r="B200" t="n">
-        <v>92217</v>
+        <v>92568</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21229,10 +21229,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>594725</v>
+        <v>594860</v>
       </c>
       <c r="R200" t="n">
-        <v>6947645</v>
+        <v>6947799</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21274,7 +21274,12 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21283,6 +21288,7 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -21301,32 +21307,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133312277</v>
+        <v>133312209</v>
       </c>
       <c r="B201" t="n">
-        <v>92566</v>
+        <v>92219</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21336,10 +21342,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>594860</v>
+        <v>594725</v>
       </c>
       <c r="R201" t="n">
-        <v>6947799</v>
+        <v>6947645</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -21371,7 +21377,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21381,12 +21387,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21395,7 +21396,6 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -13457,10 +13457,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312257</v>
+        <v>133312263</v>
       </c>
       <c r="B128" t="n">
-        <v>79366</v>
+        <v>57955</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13468,21 +13468,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,10 +13492,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594820</v>
+        <v>594826</v>
       </c>
       <c r="R128" t="n">
-        <v>6947705</v>
+        <v>6947773</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,7 +13537,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13564,32 +13569,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312184</v>
+        <v>133312257</v>
       </c>
       <c r="B129" t="n">
-        <v>75433</v>
+        <v>79366</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,10 +13604,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594713</v>
+        <v>594820</v>
       </c>
       <c r="R129" t="n">
-        <v>6947589</v>
+        <v>6947705</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13634,7 +13639,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,7 +13649,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13671,32 +13676,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312246</v>
+        <v>133312184</v>
       </c>
       <c r="B130" t="n">
-        <v>79953</v>
+        <v>75433</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13706,13 +13711,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594810</v>
+        <v>594713</v>
       </c>
       <c r="R130" t="n">
-        <v>6947725</v>
+        <v>6947589</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13741,7 +13746,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13751,7 +13756,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13778,10 +13783,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312263</v>
+        <v>133312246</v>
       </c>
       <c r="B131" t="n">
-        <v>57955</v>
+        <v>79953</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13789,21 +13794,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13813,13 +13818,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594826</v>
+        <v>594810</v>
       </c>
       <c r="R131" t="n">
-        <v>6947773</v>
+        <v>6947725</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13848,7 +13853,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13858,12 +13863,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13890,10 +13890,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312305</v>
+        <v>133312247</v>
       </c>
       <c r="B132" t="n">
-        <v>79334</v>
+        <v>92219</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13901,21 +13901,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,13 +13925,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594707</v>
+        <v>594801</v>
       </c>
       <c r="R132" t="n">
-        <v>6947692</v>
+        <v>6947716</v>
       </c>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312244</v>
+        <v>133312305</v>
       </c>
       <c r="B133" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,13 +14032,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594797</v>
+        <v>594707</v>
       </c>
       <c r="R133" t="n">
-        <v>6947735</v>
+        <v>6947692</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,12 +14077,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14109,32 +14104,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312247</v>
+        <v>133312244</v>
       </c>
       <c r="B134" t="n">
-        <v>92219</v>
+        <v>57145</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14144,10 +14139,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594801</v>
+        <v>594797</v>
       </c>
       <c r="R134" t="n">
-        <v>6947716</v>
+        <v>6947735</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14179,7 +14174,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14189,7 +14184,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312221</v>
+        <v>133312302</v>
       </c>
       <c r="B135" t="n">
-        <v>57958</v>
+        <v>79366</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,42 +14227,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594741</v>
+        <v>594703</v>
       </c>
       <c r="R135" t="n">
-        <v>6947668</v>
+        <v>6947719</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14294,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14304,12 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14336,10 +14323,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312302</v>
+        <v>133312299</v>
       </c>
       <c r="B136" t="n">
-        <v>79366</v>
+        <v>92219</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14347,21 +14334,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14371,10 +14358,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594703</v>
+        <v>594747</v>
       </c>
       <c r="R136" t="n">
-        <v>6947719</v>
+        <v>6947714</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14406,7 +14393,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14416,7 +14403,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14443,10 +14430,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312299</v>
+        <v>133312294</v>
       </c>
       <c r="B137" t="n">
-        <v>92219</v>
+        <v>89302</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14454,21 +14441,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14478,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594747</v>
+        <v>594735</v>
       </c>
       <c r="R137" t="n">
-        <v>6947714</v>
+        <v>6947729</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14513,7 +14500,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14523,7 +14510,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14550,10 +14537,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312294</v>
+        <v>133312262</v>
       </c>
       <c r="B138" t="n">
-        <v>89302</v>
+        <v>79366</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14561,21 +14548,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14585,10 +14572,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594735</v>
+        <v>594845</v>
       </c>
       <c r="R138" t="n">
-        <v>6947729</v>
+        <v>6947767</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14620,7 +14607,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14630,7 +14617,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14657,10 +14644,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312262</v>
+        <v>133312221</v>
       </c>
       <c r="B139" t="n">
-        <v>79366</v>
+        <v>57958</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14668,34 +14655,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594845</v>
+        <v>594741</v>
       </c>
       <c r="R139" t="n">
-        <v>6947767</v>
+        <v>6947668</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14727,7 +14722,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14737,7 +14732,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312226</v>
+        <v>133312297</v>
       </c>
       <c r="B140" t="n">
-        <v>5199</v>
+        <v>91920</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594755</v>
+        <v>594737</v>
       </c>
       <c r="R140" t="n">
-        <v>6947670</v>
+        <v>6947721</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14978,10 +14978,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133312297</v>
+        <v>133312320</v>
       </c>
       <c r="B142" t="n">
-        <v>91920</v>
+        <v>79366</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14989,21 +14989,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,13 +15013,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>594737</v>
+        <v>594653</v>
       </c>
       <c r="R142" t="n">
-        <v>6947721</v>
+        <v>6947566</v>
       </c>
       <c r="S142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312320</v>
+        <v>133312226</v>
       </c>
       <c r="B143" t="n">
-        <v>79366</v>
+        <v>5199</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594653</v>
+        <v>594755</v>
       </c>
       <c r="R143" t="n">
-        <v>6947566</v>
+        <v>6947670</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17765,10 +17765,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312312</v>
+        <v>133312216</v>
       </c>
       <c r="B168" t="n">
-        <v>80399</v>
+        <v>92643</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17776,21 +17776,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,13 +17800,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594697</v>
+        <v>594730</v>
       </c>
       <c r="R168" t="n">
-        <v>6947661</v>
+        <v>6947646</v>
       </c>
       <c r="S168" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312216</v>
+        <v>133312319</v>
       </c>
       <c r="B169" t="n">
-        <v>92643</v>
+        <v>91920</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594730</v>
+        <v>594662</v>
       </c>
       <c r="R169" t="n">
-        <v>6947646</v>
+        <v>6947577</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,32 +17979,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312319</v>
+        <v>133312312</v>
       </c>
       <c r="B170" t="n">
-        <v>91920</v>
+        <v>80399</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,13 +18014,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594662</v>
+        <v>594697</v>
       </c>
       <c r="R170" t="n">
-        <v>6947577</v>
+        <v>6947661</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312194</v>
+        <v>133312240</v>
       </c>
       <c r="B182" t="n">
-        <v>83316</v>
+        <v>92219</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,10 +19303,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594690</v>
+        <v>594782</v>
       </c>
       <c r="R182" t="n">
-        <v>6947596</v>
+        <v>6947711</v>
       </c>
       <c r="S182" t="n">
         <v>6</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,7 +19375,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312240</v>
+        <v>133312298</v>
       </c>
       <c r="B183" t="n">
         <v>92219</v>
@@ -19410,13 +19410,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594782</v>
+        <v>594740</v>
       </c>
       <c r="R183" t="n">
-        <v>6947711</v>
+        <v>6947716</v>
       </c>
       <c r="S183" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19482,10 +19482,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312298</v>
+        <v>133312194</v>
       </c>
       <c r="B184" t="n">
-        <v>92219</v>
+        <v>83316</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19493,21 +19493,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19517,13 +19517,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594740</v>
+        <v>594690</v>
       </c>
       <c r="R184" t="n">
-        <v>6947716</v>
+        <v>6947596</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD184" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -13457,10 +13457,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312263</v>
+        <v>133312257</v>
       </c>
       <c r="B128" t="n">
-        <v>57955</v>
+        <v>79366</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13468,21 +13468,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,10 +13492,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594826</v>
+        <v>594820</v>
       </c>
       <c r="R128" t="n">
-        <v>6947773</v>
+        <v>6947705</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,12 +13537,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13569,32 +13564,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312257</v>
+        <v>133312184</v>
       </c>
       <c r="B129" t="n">
-        <v>79366</v>
+        <v>75433</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13604,10 +13599,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594820</v>
+        <v>594713</v>
       </c>
       <c r="R129" t="n">
-        <v>6947705</v>
+        <v>6947589</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13639,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13649,7 +13644,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13676,32 +13671,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312184</v>
+        <v>133312246</v>
       </c>
       <c r="B130" t="n">
-        <v>75433</v>
+        <v>79953</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13711,13 +13706,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594713</v>
+        <v>594810</v>
       </c>
       <c r="R130" t="n">
-        <v>6947589</v>
+        <v>6947725</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13746,7 +13741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13756,7 +13751,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13783,10 +13778,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312246</v>
+        <v>133312263</v>
       </c>
       <c r="B131" t="n">
-        <v>79953</v>
+        <v>57955</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13794,21 +13789,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13818,13 +13813,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594810</v>
+        <v>594826</v>
       </c>
       <c r="R131" t="n">
-        <v>6947725</v>
+        <v>6947773</v>
       </c>
       <c r="S131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13853,7 +13848,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13863,7 +13858,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13890,10 +13890,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312247</v>
+        <v>133312305</v>
       </c>
       <c r="B132" t="n">
-        <v>92219</v>
+        <v>79334</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13901,21 +13901,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,13 +13925,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594801</v>
+        <v>594707</v>
       </c>
       <c r="R132" t="n">
-        <v>6947716</v>
+        <v>6947692</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312305</v>
+        <v>133312244</v>
       </c>
       <c r="B133" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,13 +14032,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594707</v>
+        <v>594797</v>
       </c>
       <c r="R133" t="n">
-        <v>6947692</v>
+        <v>6947735</v>
       </c>
       <c r="S133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,7 +14077,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14104,32 +14109,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312244</v>
+        <v>133312247</v>
       </c>
       <c r="B134" t="n">
-        <v>57145</v>
+        <v>92219</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14139,10 +14144,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594797</v>
+        <v>594801</v>
       </c>
       <c r="R134" t="n">
-        <v>6947735</v>
+        <v>6947716</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14174,7 +14179,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14184,12 +14189,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312302</v>
+        <v>133312221</v>
       </c>
       <c r="B135" t="n">
-        <v>79366</v>
+        <v>57958</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,34 +14227,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594703</v>
+        <v>594741</v>
       </c>
       <c r="R135" t="n">
-        <v>6947719</v>
+        <v>6947668</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14286,7 +14294,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14304,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14323,10 +14336,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312299</v>
+        <v>133312302</v>
       </c>
       <c r="B136" t="n">
-        <v>92219</v>
+        <v>79366</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14334,21 +14347,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14358,10 +14371,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594747</v>
+        <v>594703</v>
       </c>
       <c r="R136" t="n">
-        <v>6947714</v>
+        <v>6947719</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14393,7 +14406,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14403,7 +14416,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14430,10 +14443,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312294</v>
+        <v>133312299</v>
       </c>
       <c r="B137" t="n">
-        <v>89302</v>
+        <v>92219</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14441,21 +14454,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14465,10 +14478,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594735</v>
+        <v>594747</v>
       </c>
       <c r="R137" t="n">
-        <v>6947729</v>
+        <v>6947714</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14500,7 +14513,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14510,7 +14523,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14537,10 +14550,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312262</v>
+        <v>133312294</v>
       </c>
       <c r="B138" t="n">
-        <v>79366</v>
+        <v>89302</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,21 +14561,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14572,10 +14585,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594845</v>
+        <v>594735</v>
       </c>
       <c r="R138" t="n">
-        <v>6947767</v>
+        <v>6947729</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14607,7 +14620,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14617,7 +14630,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14644,10 +14657,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312221</v>
+        <v>133312262</v>
       </c>
       <c r="B139" t="n">
-        <v>57958</v>
+        <v>79366</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14655,42 +14668,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594741</v>
+        <v>594845</v>
       </c>
       <c r="R139" t="n">
-        <v>6947668</v>
+        <v>6947767</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14722,7 +14727,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14732,12 +14737,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18407,32 +18407,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133312212</v>
+        <v>133312308</v>
       </c>
       <c r="B174" t="n">
-        <v>91934</v>
+        <v>75433</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1204</v>
+        <v>6426</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>594721</v>
+        <v>594707</v>
       </c>
       <c r="R174" t="n">
-        <v>6947646</v>
+        <v>6947669</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18514,10 +18514,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312243</v>
+        <v>133312268</v>
       </c>
       <c r="B175" t="n">
-        <v>91920</v>
+        <v>57955</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594794</v>
+        <v>594805</v>
       </c>
       <c r="R175" t="n">
-        <v>6947729</v>
+        <v>6947762</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,7 +18594,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18621,32 +18626,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312308</v>
+        <v>133312212</v>
       </c>
       <c r="B176" t="n">
-        <v>75433</v>
+        <v>91934</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6426</v>
+        <v>1204</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18656,10 +18661,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594707</v>
+        <v>594721</v>
       </c>
       <c r="R176" t="n">
-        <v>6947669</v>
+        <v>6947646</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18691,7 +18696,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18701,7 +18706,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18728,10 +18733,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312268</v>
+        <v>133312243</v>
       </c>
       <c r="B177" t="n">
-        <v>57955</v>
+        <v>91920</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18739,21 +18744,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18763,10 +18768,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594805</v>
+        <v>594794</v>
       </c>
       <c r="R177" t="n">
-        <v>6947762</v>
+        <v>6947729</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18798,7 +18803,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18808,12 +18813,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD177" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12387,10 +12387,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133312282</v>
+        <v>133312232</v>
       </c>
       <c r="B118" t="n">
-        <v>79366</v>
+        <v>91942</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>594775</v>
+        <v>594755</v>
       </c>
       <c r="R118" t="n">
-        <v>6947806</v>
+        <v>6947677</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133312232</v>
+        <v>133312282</v>
       </c>
       <c r="B119" t="n">
-        <v>91934</v>
+        <v>79366</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>594755</v>
+        <v>594775</v>
       </c>
       <c r="R119" t="n">
-        <v>6947677</v>
+        <v>6947806</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12708,32 +12708,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312293</v>
+        <v>133312200</v>
       </c>
       <c r="B121" t="n">
-        <v>91920</v>
+        <v>75433</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594745</v>
+        <v>594692</v>
       </c>
       <c r="R121" t="n">
-        <v>6947738</v>
+        <v>6947605</v>
       </c>
       <c r="S121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312274</v>
+        <v>133312241</v>
       </c>
       <c r="B122" t="n">
-        <v>92219</v>
+        <v>79953</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594857</v>
+        <v>594784</v>
       </c>
       <c r="R122" t="n">
-        <v>6947775</v>
+        <v>6947732</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,7 +12922,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312200</v>
+        <v>133312205</v>
       </c>
       <c r="B123" t="n">
         <v>75433</v>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594692</v>
+        <v>594702</v>
       </c>
       <c r="R123" t="n">
-        <v>6947605</v>
+        <v>6947615</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312241</v>
+        <v>133312229</v>
       </c>
       <c r="B124" t="n">
-        <v>79953</v>
+        <v>79366</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594784</v>
+        <v>594755</v>
       </c>
       <c r="R124" t="n">
-        <v>6947732</v>
+        <v>6947668</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312205</v>
+        <v>133312284</v>
       </c>
       <c r="B125" t="n">
-        <v>75433</v>
+        <v>91878</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>112</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594702</v>
+        <v>594757</v>
       </c>
       <c r="R125" t="n">
-        <v>6947615</v>
+        <v>6947805</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,10 +13243,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312229</v>
+        <v>133312293</v>
       </c>
       <c r="B126" t="n">
-        <v>79366</v>
+        <v>91928</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,21 +13254,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,13 +13278,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594755</v>
+        <v>594745</v>
       </c>
       <c r="R126" t="n">
-        <v>6947668</v>
+        <v>6947738</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,10 +13350,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312284</v>
+        <v>133312274</v>
       </c>
       <c r="B127" t="n">
-        <v>91870</v>
+        <v>92227</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13361,21 +13361,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594757</v>
+        <v>594857</v>
       </c>
       <c r="R127" t="n">
-        <v>6947805</v>
+        <v>6947775</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13564,32 +13564,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312184</v>
+        <v>133312263</v>
       </c>
       <c r="B129" t="n">
-        <v>75433</v>
+        <v>57955</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,10 +13599,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594713</v>
+        <v>594826</v>
       </c>
       <c r="R129" t="n">
-        <v>6947589</v>
+        <v>6947773</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,7 +13644,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13671,32 +13676,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312246</v>
+        <v>133312184</v>
       </c>
       <c r="B130" t="n">
-        <v>79953</v>
+        <v>75433</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13706,13 +13711,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594810</v>
+        <v>594713</v>
       </c>
       <c r="R130" t="n">
-        <v>6947725</v>
+        <v>6947589</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13741,7 +13746,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13751,7 +13756,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13778,10 +13783,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312263</v>
+        <v>133312246</v>
       </c>
       <c r="B131" t="n">
-        <v>57955</v>
+        <v>79953</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13789,21 +13794,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13813,13 +13818,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594826</v>
+        <v>594810</v>
       </c>
       <c r="R131" t="n">
-        <v>6947773</v>
+        <v>6947725</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13848,7 +13853,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13858,12 +13863,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312244</v>
+        <v>133312247</v>
       </c>
       <c r="B133" t="n">
-        <v>57145</v>
+        <v>92227</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594797</v>
+        <v>594801</v>
       </c>
       <c r="R133" t="n">
-        <v>6947735</v>
+        <v>6947716</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,12 +14077,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14109,32 +14104,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312247</v>
+        <v>133312244</v>
       </c>
       <c r="B134" t="n">
-        <v>92219</v>
+        <v>57145</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14144,10 +14139,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594801</v>
+        <v>594797</v>
       </c>
       <c r="R134" t="n">
-        <v>6947716</v>
+        <v>6947735</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14179,7 +14174,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14189,7 +14184,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312221</v>
+        <v>133312299</v>
       </c>
       <c r="B135" t="n">
-        <v>57958</v>
+        <v>92227</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,42 +14227,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594741</v>
+        <v>594747</v>
       </c>
       <c r="R135" t="n">
-        <v>6947668</v>
+        <v>6947714</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14294,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14304,12 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14443,10 +14430,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312299</v>
+        <v>133312262</v>
       </c>
       <c r="B137" t="n">
-        <v>92219</v>
+        <v>79366</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14454,21 +14441,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14478,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594747</v>
+        <v>594845</v>
       </c>
       <c r="R137" t="n">
-        <v>6947714</v>
+        <v>6947767</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14513,7 +14500,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14523,7 +14510,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14553,7 +14540,7 @@
         <v>133312294</v>
       </c>
       <c r="B138" t="n">
-        <v>89302</v>
+        <v>89310</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14657,10 +14644,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312262</v>
+        <v>133312221</v>
       </c>
       <c r="B139" t="n">
-        <v>79366</v>
+        <v>57958</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14668,34 +14655,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594845</v>
+        <v>594741</v>
       </c>
       <c r="R139" t="n">
-        <v>6947767</v>
+        <v>6947668</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14727,7 +14722,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14737,7 +14732,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14767,7 +14767,7 @@
         <v>133312297</v>
       </c>
       <c r="B140" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>133312272</v>
       </c>
       <c r="B141" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>133312195</v>
       </c>
       <c r="B144" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>133312222</v>
       </c>
       <c r="B145" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15406,10 +15406,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133312288</v>
+        <v>133312252</v>
       </c>
       <c r="B146" t="n">
-        <v>79953</v>
+        <v>91928</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15417,21 +15417,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>594771</v>
+        <v>594811</v>
       </c>
       <c r="R146" t="n">
-        <v>6947766</v>
+        <v>6947698</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15513,10 +15513,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133312250</v>
+        <v>133312181</v>
       </c>
       <c r="B147" t="n">
-        <v>92219</v>
+        <v>91928</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15524,21 +15524,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15548,10 +15548,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>594805</v>
+        <v>594723</v>
       </c>
       <c r="R147" t="n">
-        <v>6947701</v>
+        <v>6947583</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15620,10 +15620,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133312304</v>
+        <v>133312250</v>
       </c>
       <c r="B148" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>594716</v>
+        <v>594805</v>
       </c>
       <c r="R148" t="n">
         <v>6947701</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15727,10 +15727,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133312252</v>
+        <v>133312304</v>
       </c>
       <c r="B149" t="n">
-        <v>91920</v>
+        <v>92227</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15738,21 +15738,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>594811</v>
+        <v>594716</v>
       </c>
       <c r="R149" t="n">
-        <v>6947698</v>
+        <v>6947701</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15834,10 +15834,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133312181</v>
+        <v>133312288</v>
       </c>
       <c r="B150" t="n">
-        <v>91920</v>
+        <v>79953</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15845,21 +15845,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>594723</v>
+        <v>594771</v>
       </c>
       <c r="R150" t="n">
-        <v>6947583</v>
+        <v>6947766</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15944,7 +15944,7 @@
         <v>133312218</v>
       </c>
       <c r="B151" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16053,10 +16053,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312189</v>
+        <v>133312271</v>
       </c>
       <c r="B152" t="n">
-        <v>83182</v>
+        <v>79334</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16064,21 +16064,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16088,13 +16088,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594688</v>
+        <v>594798</v>
       </c>
       <c r="R152" t="n">
-        <v>6947584</v>
+        <v>6947776</v>
       </c>
       <c r="S152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16160,32 +16160,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312303</v>
+        <v>133312189</v>
       </c>
       <c r="B153" t="n">
-        <v>80467</v>
+        <v>83183</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16195,13 +16195,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594701</v>
+        <v>594688</v>
       </c>
       <c r="R153" t="n">
-        <v>6947707</v>
+        <v>6947584</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16267,10 +16267,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133312186</v>
+        <v>133312303</v>
       </c>
       <c r="B154" t="n">
-        <v>75433</v>
+        <v>80467</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16278,21 +16278,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6426</v>
+        <v>6461</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16302,13 +16302,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>594705</v>
+        <v>594701</v>
       </c>
       <c r="R154" t="n">
-        <v>6947589</v>
+        <v>6947707</v>
       </c>
       <c r="S154" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16374,32 +16374,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133312271</v>
+        <v>133312186</v>
       </c>
       <c r="B155" t="n">
-        <v>79334</v>
+        <v>75433</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16409,13 +16409,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>594798</v>
+        <v>594705</v>
       </c>
       <c r="R155" t="n">
-        <v>6947776</v>
+        <v>6947589</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16698,7 +16698,7 @@
         <v>133312295</v>
       </c>
       <c r="B158" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>133312208</v>
       </c>
       <c r="B160" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>133312279</v>
       </c>
       <c r="B164" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>133312203</v>
       </c>
       <c r="B165" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>133312300</v>
       </c>
       <c r="B166" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>133312234</v>
       </c>
       <c r="B167" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312216</v>
+        <v>133312259</v>
       </c>
       <c r="B168" t="n">
-        <v>92643</v>
+        <v>79953</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3298</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594730</v>
+        <v>594814</v>
       </c>
       <c r="R168" t="n">
-        <v>6947646</v>
+        <v>6947723</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,10 +17872,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312319</v>
+        <v>133312280</v>
       </c>
       <c r="B169" t="n">
-        <v>91920</v>
+        <v>79091</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17883,21 +17883,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594662</v>
+        <v>594788</v>
       </c>
       <c r="R169" t="n">
-        <v>6947577</v>
+        <v>6947813</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,10 +17979,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312312</v>
+        <v>133312313</v>
       </c>
       <c r="B170" t="n">
-        <v>80399</v>
+        <v>80475</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17990,21 +17990,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18020,7 +18020,7 @@
         <v>6947661</v>
       </c>
       <c r="S170" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,32 +18086,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312259</v>
+        <v>133312216</v>
       </c>
       <c r="B171" t="n">
-        <v>79953</v>
+        <v>92651</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>3298</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594814</v>
+        <v>594730</v>
       </c>
       <c r="R171" t="n">
-        <v>6947723</v>
+        <v>6947646</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,10 +18193,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312280</v>
+        <v>133312319</v>
       </c>
       <c r="B172" t="n">
-        <v>79091</v>
+        <v>91928</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18204,21 +18204,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594788</v>
+        <v>594662</v>
       </c>
       <c r="R172" t="n">
-        <v>6947813</v>
+        <v>6947577</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18300,10 +18300,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312313</v>
+        <v>133312312</v>
       </c>
       <c r="B173" t="n">
-        <v>80475</v>
+        <v>80399</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18311,21 +18311,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18341,7 +18341,7 @@
         <v>6947661</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18407,32 +18407,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133312308</v>
+        <v>133312212</v>
       </c>
       <c r="B174" t="n">
-        <v>75433</v>
+        <v>91942</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6426</v>
+        <v>1204</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>594707</v>
+        <v>594721</v>
       </c>
       <c r="R174" t="n">
-        <v>6947669</v>
+        <v>6947646</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18514,10 +18514,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312268</v>
+        <v>133312243</v>
       </c>
       <c r="B175" t="n">
-        <v>57955</v>
+        <v>91928</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594805</v>
+        <v>594794</v>
       </c>
       <c r="R175" t="n">
-        <v>6947762</v>
+        <v>6947729</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,12 +18594,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18626,32 +18621,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312212</v>
+        <v>133312308</v>
       </c>
       <c r="B176" t="n">
-        <v>91934</v>
+        <v>75433</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1204</v>
+        <v>6426</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18661,10 +18656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594721</v>
+        <v>594707</v>
       </c>
       <c r="R176" t="n">
-        <v>6947646</v>
+        <v>6947669</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18696,7 +18691,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18706,7 +18701,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18733,10 +18728,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312243</v>
+        <v>133312268</v>
       </c>
       <c r="B177" t="n">
-        <v>91920</v>
+        <v>57955</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18744,21 +18739,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18768,10 +18763,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594794</v>
+        <v>594805</v>
       </c>
       <c r="R177" t="n">
-        <v>6947729</v>
+        <v>6947762</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18803,7 +18798,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18813,7 +18808,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18843,7 +18843,7 @@
         <v>133312213</v>
       </c>
       <c r="B178" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>133312240</v>
       </c>
       <c r="B182" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>133312298</v>
       </c>
       <c r="B183" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>133312194</v>
       </c>
       <c r="B184" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19696,32 +19696,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312316</v>
+        <v>133312289</v>
       </c>
       <c r="B186" t="n">
-        <v>75433</v>
+        <v>92227</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594666</v>
+        <v>594777</v>
       </c>
       <c r="R186" t="n">
-        <v>6947640</v>
+        <v>6947757</v>
       </c>
       <c r="S186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19803,32 +19803,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312188</v>
+        <v>133312266</v>
       </c>
       <c r="B187" t="n">
-        <v>75433</v>
+        <v>91928</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,13 +19838,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594698</v>
+        <v>594820</v>
       </c>
       <c r="R187" t="n">
-        <v>6947587</v>
+        <v>6947773</v>
       </c>
       <c r="S187" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,32 +19910,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312236</v>
+        <v>133312225</v>
       </c>
       <c r="B188" t="n">
-        <v>79358</v>
+        <v>91928</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,10 +19945,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594742</v>
+        <v>594757</v>
       </c>
       <c r="R188" t="n">
-        <v>6947701</v>
+        <v>6947666</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,10 +20017,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312197</v>
+        <v>133312276</v>
       </c>
       <c r="B189" t="n">
-        <v>75433</v>
+        <v>80399</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20028,21 +20028,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594687</v>
+        <v>594856</v>
       </c>
       <c r="R189" t="n">
-        <v>6947597</v>
+        <v>6947759</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,32 +20124,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312318</v>
+        <v>133312316</v>
       </c>
       <c r="B190" t="n">
-        <v>79334</v>
+        <v>75433</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20159,13 +20159,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594678</v>
+        <v>594666</v>
       </c>
       <c r="R190" t="n">
-        <v>6947597</v>
+        <v>6947640</v>
       </c>
       <c r="S190" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,7 +20231,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312317</v>
+        <v>133312188</v>
       </c>
       <c r="B191" t="n">
         <v>75433</v>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594682</v>
+        <v>594698</v>
       </c>
       <c r="R191" t="n">
-        <v>6947610</v>
+        <v>6947587</v>
       </c>
       <c r="S191" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,10 +20338,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312276</v>
+        <v>133312236</v>
       </c>
       <c r="B192" t="n">
-        <v>80399</v>
+        <v>79358</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20349,21 +20349,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>229497</v>
+        <v>6434</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594856</v>
+        <v>594742</v>
       </c>
       <c r="R192" t="n">
-        <v>6947759</v>
+        <v>6947701</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312289</v>
+        <v>133312197</v>
       </c>
       <c r="B193" t="n">
-        <v>92219</v>
+        <v>75433</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,10 +20480,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594777</v>
+        <v>594687</v>
       </c>
       <c r="R193" t="n">
-        <v>6947757</v>
+        <v>6947597</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20552,10 +20552,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133312266</v>
+        <v>133312318</v>
       </c>
       <c r="B194" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20563,21 +20563,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>594820</v>
+        <v>594678</v>
       </c>
       <c r="R194" t="n">
-        <v>6947773</v>
+        <v>6947597</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20659,32 +20659,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133312225</v>
+        <v>133312317</v>
       </c>
       <c r="B195" t="n">
-        <v>91920</v>
+        <v>75433</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20694,13 +20694,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>594757</v>
+        <v>594682</v>
       </c>
       <c r="R195" t="n">
-        <v>6947666</v>
+        <v>6947610</v>
       </c>
       <c r="S195" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20769,7 +20769,7 @@
         <v>133312219</v>
       </c>
       <c r="B196" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>133312215</v>
       </c>
       <c r="B197" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>133312224</v>
       </c>
       <c r="B198" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>133312277</v>
       </c>
       <c r="B200" t="n">
-        <v>92568</v>
+        <v>92576</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>133312209</v>
       </c>
       <c r="B201" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12708,32 +12708,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312200</v>
+        <v>133312293</v>
       </c>
       <c r="B121" t="n">
-        <v>75433</v>
+        <v>91928</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594692</v>
+        <v>594745</v>
       </c>
       <c r="R121" t="n">
-        <v>6947605</v>
+        <v>6947738</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312241</v>
+        <v>133312274</v>
       </c>
       <c r="B122" t="n">
-        <v>79953</v>
+        <v>92227</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594784</v>
+        <v>594857</v>
       </c>
       <c r="R122" t="n">
-        <v>6947732</v>
+        <v>6947775</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12922,7 +12922,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312205</v>
+        <v>133312200</v>
       </c>
       <c r="B123" t="n">
         <v>75433</v>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594702</v>
+        <v>594692</v>
       </c>
       <c r="R123" t="n">
-        <v>6947615</v>
+        <v>6947605</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312229</v>
+        <v>133312241</v>
       </c>
       <c r="B124" t="n">
-        <v>79366</v>
+        <v>79953</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594755</v>
+        <v>594784</v>
       </c>
       <c r="R124" t="n">
-        <v>6947668</v>
+        <v>6947732</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312284</v>
+        <v>133312205</v>
       </c>
       <c r="B125" t="n">
-        <v>91878</v>
+        <v>75433</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>112</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594757</v>
+        <v>594702</v>
       </c>
       <c r="R125" t="n">
-        <v>6947805</v>
+        <v>6947615</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,10 +13243,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312293</v>
+        <v>133312229</v>
       </c>
       <c r="B126" t="n">
-        <v>91928</v>
+        <v>79366</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,21 +13254,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,13 +13278,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594745</v>
+        <v>594755</v>
       </c>
       <c r="R126" t="n">
-        <v>6947738</v>
+        <v>6947668</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13350,10 +13350,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133312274</v>
+        <v>133312284</v>
       </c>
       <c r="B127" t="n">
-        <v>92227</v>
+        <v>91878</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13361,21 +13361,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>594857</v>
+        <v>594757</v>
       </c>
       <c r="R127" t="n">
-        <v>6947775</v>
+        <v>6947805</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13457,32 +13457,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133312257</v>
+        <v>133312184</v>
       </c>
       <c r="B128" t="n">
-        <v>79366</v>
+        <v>75433</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13492,10 +13492,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>594820</v>
+        <v>594713</v>
       </c>
       <c r="R128" t="n">
-        <v>6947705</v>
+        <v>6947589</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13564,10 +13564,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312263</v>
+        <v>133312246</v>
       </c>
       <c r="B129" t="n">
-        <v>57955</v>
+        <v>79953</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13575,21 +13575,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,13 +13599,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594826</v>
+        <v>594810</v>
       </c>
       <c r="R129" t="n">
-        <v>6947773</v>
+        <v>6947725</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,12 +13644,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13676,32 +13671,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312184</v>
+        <v>133312263</v>
       </c>
       <c r="B130" t="n">
-        <v>75433</v>
+        <v>57955</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13711,10 +13706,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594713</v>
+        <v>594826</v>
       </c>
       <c r="R130" t="n">
-        <v>6947589</v>
+        <v>6947773</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13746,7 +13741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13756,7 +13751,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13783,10 +13783,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312246</v>
+        <v>133312257</v>
       </c>
       <c r="B131" t="n">
-        <v>79953</v>
+        <v>79366</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13794,21 +13794,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13818,13 +13818,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594810</v>
+        <v>594820</v>
       </c>
       <c r="R131" t="n">
-        <v>6947725</v>
+        <v>6947705</v>
       </c>
       <c r="S131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312280</v>
+        <v>133312312</v>
       </c>
       <c r="B169" t="n">
-        <v>79091</v>
+        <v>80399</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6446</v>
+        <v>229497</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,13 +17907,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594788</v>
+        <v>594697</v>
       </c>
       <c r="R169" t="n">
-        <v>6947813</v>
+        <v>6947661</v>
       </c>
       <c r="S169" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,10 +17979,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312313</v>
+        <v>133312216</v>
       </c>
       <c r="B170" t="n">
-        <v>80475</v>
+        <v>92651</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17990,21 +17990,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594697</v>
+        <v>594730</v>
       </c>
       <c r="R170" t="n">
-        <v>6947661</v>
+        <v>6947646</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,32 +18086,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312216</v>
+        <v>133312319</v>
       </c>
       <c r="B171" t="n">
-        <v>92651</v>
+        <v>91928</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594730</v>
+        <v>594662</v>
       </c>
       <c r="R171" t="n">
-        <v>6947646</v>
+        <v>6947577</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,10 +18193,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312319</v>
+        <v>133312280</v>
       </c>
       <c r="B172" t="n">
-        <v>91928</v>
+        <v>79091</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18204,21 +18204,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594662</v>
+        <v>594788</v>
       </c>
       <c r="R172" t="n">
-        <v>6947577</v>
+        <v>6947813</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18300,10 +18300,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312312</v>
+        <v>133312313</v>
       </c>
       <c r="B173" t="n">
-        <v>80399</v>
+        <v>80475</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18311,21 +18311,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18341,7 +18341,7 @@
         <v>6947661</v>
       </c>
       <c r="S173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19696,32 +19696,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312289</v>
+        <v>133312316</v>
       </c>
       <c r="B186" t="n">
-        <v>92227</v>
+        <v>75433</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594777</v>
+        <v>594666</v>
       </c>
       <c r="R186" t="n">
-        <v>6947757</v>
+        <v>6947640</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19803,32 +19803,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312266</v>
+        <v>133312188</v>
       </c>
       <c r="B187" t="n">
-        <v>91928</v>
+        <v>75433</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,13 +19838,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594820</v>
+        <v>594698</v>
       </c>
       <c r="R187" t="n">
-        <v>6947773</v>
+        <v>6947587</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,32 +19910,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312225</v>
+        <v>133312236</v>
       </c>
       <c r="B188" t="n">
-        <v>91928</v>
+        <v>79358</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,10 +19945,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594757</v>
+        <v>594742</v>
       </c>
       <c r="R188" t="n">
-        <v>6947666</v>
+        <v>6947701</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,10 +20017,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312276</v>
+        <v>133312197</v>
       </c>
       <c r="B189" t="n">
-        <v>80399</v>
+        <v>75433</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20028,21 +20028,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594856</v>
+        <v>594687</v>
       </c>
       <c r="R189" t="n">
-        <v>6947759</v>
+        <v>6947597</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,10 +20124,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312316</v>
+        <v>133312276</v>
       </c>
       <c r="B190" t="n">
-        <v>75433</v>
+        <v>80399</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20135,21 +20135,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20159,13 +20159,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594666</v>
+        <v>594856</v>
       </c>
       <c r="R190" t="n">
-        <v>6947640</v>
+        <v>6947759</v>
       </c>
       <c r="S190" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,32 +20231,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312188</v>
+        <v>133312289</v>
       </c>
       <c r="B191" t="n">
-        <v>75433</v>
+        <v>92227</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594698</v>
+        <v>594777</v>
       </c>
       <c r="R191" t="n">
-        <v>6947587</v>
+        <v>6947757</v>
       </c>
       <c r="S191" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,32 +20338,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312236</v>
+        <v>133312266</v>
       </c>
       <c r="B192" t="n">
-        <v>79358</v>
+        <v>91928</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594742</v>
+        <v>594820</v>
       </c>
       <c r="R192" t="n">
-        <v>6947701</v>
+        <v>6947773</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312197</v>
+        <v>133312225</v>
       </c>
       <c r="B193" t="n">
-        <v>75433</v>
+        <v>91928</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,10 +20480,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594687</v>
+        <v>594757</v>
       </c>
       <c r="R193" t="n">
-        <v>6947597</v>
+        <v>6947666</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312219</v>
+        <v>133312239</v>
       </c>
       <c r="B196" t="n">
-        <v>91942</v>
+        <v>79334</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594728</v>
+        <v>594784</v>
       </c>
       <c r="R196" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312215</v>
+        <v>133312219</v>
       </c>
       <c r="B197" t="n">
-        <v>92227</v>
+        <v>91942</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20884,21 +20884,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594730</v>
+        <v>594728</v>
       </c>
       <c r="R197" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,7 +20980,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312224</v>
+        <v>133312215</v>
       </c>
       <c r="B198" t="n">
         <v>92227</v>
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594755</v>
+        <v>594730</v>
       </c>
       <c r="R198" t="n">
-        <v>6947667</v>
+        <v>6947645</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312239</v>
+        <v>133312224</v>
       </c>
       <c r="B199" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594784</v>
+        <v>594755</v>
       </c>
       <c r="R199" t="n">
-        <v>6947700</v>
+        <v>6947667</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21194,32 +21194,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133312277</v>
+        <v>133312209</v>
       </c>
       <c r="B200" t="n">
-        <v>92576</v>
+        <v>92227</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21229,10 +21229,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>594860</v>
+        <v>594725</v>
       </c>
       <c r="R200" t="n">
-        <v>6947799</v>
+        <v>6947645</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21274,12 +21274,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21288,7 +21283,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -21307,32 +21301,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133312209</v>
+        <v>133312277</v>
       </c>
       <c r="B201" t="n">
-        <v>92227</v>
+        <v>92576</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21342,10 +21336,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>594725</v>
+        <v>594860</v>
       </c>
       <c r="R201" t="n">
-        <v>6947645</v>
+        <v>6947799</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -21377,7 +21371,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21387,7 +21381,12 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21396,6 +21395,7 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -14764,10 +14764,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312297</v>
+        <v>133312272</v>
       </c>
       <c r="B140" t="n">
-        <v>91928</v>
+        <v>83319</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14775,21 +14775,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594737</v>
+        <v>594856</v>
       </c>
       <c r="R140" t="n">
-        <v>6947721</v>
+        <v>6947779</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312272</v>
+        <v>133312297</v>
       </c>
       <c r="B141" t="n">
-        <v>83319</v>
+        <v>91928</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594856</v>
+        <v>594737</v>
       </c>
       <c r="R141" t="n">
-        <v>6947779</v>
+        <v>6947721</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16481,10 +16481,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133312253</v>
+        <v>133312295</v>
       </c>
       <c r="B156" t="n">
-        <v>79366</v>
+        <v>92227</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16492,21 +16492,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>594812</v>
+        <v>594733</v>
       </c>
       <c r="R156" t="n">
-        <v>6947696</v>
+        <v>6947724</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16588,7 +16588,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133312182</v>
+        <v>133312253</v>
       </c>
       <c r="B157" t="n">
         <v>79366</v>
@@ -16623,10 +16623,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>594709</v>
+        <v>594812</v>
       </c>
       <c r="R157" t="n">
-        <v>6947587</v>
+        <v>6947696</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16695,10 +16695,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133312295</v>
+        <v>133312182</v>
       </c>
       <c r="B158" t="n">
-        <v>92227</v>
+        <v>79366</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16706,21 +16706,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16730,10 +16730,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>594733</v>
+        <v>594709</v>
       </c>
       <c r="R158" t="n">
-        <v>6947724</v>
+        <v>6947587</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD158" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -14764,10 +14764,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312272</v>
+        <v>133312297</v>
       </c>
       <c r="B140" t="n">
-        <v>83319</v>
+        <v>91928</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14775,21 +14775,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594856</v>
+        <v>594737</v>
       </c>
       <c r="R140" t="n">
-        <v>6947779</v>
+        <v>6947721</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312297</v>
+        <v>133312272</v>
       </c>
       <c r="B141" t="n">
-        <v>91928</v>
+        <v>83319</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594737</v>
+        <v>594856</v>
       </c>
       <c r="R141" t="n">
-        <v>6947721</v>
+        <v>6947779</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD141" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -14764,10 +14764,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312297</v>
+        <v>133312272</v>
       </c>
       <c r="B140" t="n">
-        <v>91928</v>
+        <v>83319</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14775,21 +14775,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594737</v>
+        <v>594856</v>
       </c>
       <c r="R140" t="n">
-        <v>6947721</v>
+        <v>6947779</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312272</v>
+        <v>133312297</v>
       </c>
       <c r="B141" t="n">
-        <v>83319</v>
+        <v>91928</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594856</v>
+        <v>594737</v>
       </c>
       <c r="R141" t="n">
-        <v>6947779</v>
+        <v>6947721</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD141" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -14764,10 +14764,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312272</v>
+        <v>133312297</v>
       </c>
       <c r="B140" t="n">
-        <v>83319</v>
+        <v>91928</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14775,21 +14775,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594856</v>
+        <v>594737</v>
       </c>
       <c r="R140" t="n">
-        <v>6947779</v>
+        <v>6947721</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14871,10 +14871,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133312297</v>
+        <v>133312272</v>
       </c>
       <c r="B141" t="n">
-        <v>91928</v>
+        <v>83319</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14882,21 +14882,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>594737</v>
+        <v>594856</v>
       </c>
       <c r="R141" t="n">
-        <v>6947721</v>
+        <v>6947779</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -18840,10 +18840,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>133312213</v>
+        <v>133312179</v>
       </c>
       <c r="B178" t="n">
-        <v>91928</v>
+        <v>79366</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18851,21 +18851,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18875,10 +18875,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>594725</v>
+        <v>594731</v>
       </c>
       <c r="R178" t="n">
-        <v>6947645</v>
+        <v>6947567</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18947,10 +18947,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>133312179</v>
+        <v>133312213</v>
       </c>
       <c r="B179" t="n">
-        <v>79366</v>
+        <v>91928</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18958,21 +18958,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18982,10 +18982,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>594731</v>
+        <v>594725</v>
       </c>
       <c r="R179" t="n">
-        <v>6947567</v>
+        <v>6947645</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD179" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12390,7 +12390,7 @@
         <v>133312232</v>
       </c>
       <c r="B118" t="n">
-        <v>91942</v>
+        <v>91961</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>133312282</v>
       </c>
       <c r="B119" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>133312291</v>
       </c>
       <c r="B120" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>133312293</v>
       </c>
       <c r="B121" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12815,10 +12815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312274</v>
+        <v>133312229</v>
       </c>
       <c r="B122" t="n">
-        <v>92227</v>
+        <v>79380</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594857</v>
+        <v>594755</v>
       </c>
       <c r="R122" t="n">
-        <v>6947775</v>
+        <v>6947668</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12925,7 +12925,7 @@
         <v>133312200</v>
       </c>
       <c r="B123" t="n">
-        <v>75433</v>
+        <v>75444</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312241</v>
+        <v>133312274</v>
       </c>
       <c r="B124" t="n">
-        <v>79953</v>
+        <v>92218</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594784</v>
+        <v>594857</v>
       </c>
       <c r="R124" t="n">
-        <v>6947732</v>
+        <v>6947775</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312205</v>
+        <v>133312241</v>
       </c>
       <c r="B125" t="n">
-        <v>75433</v>
+        <v>79967</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594702</v>
+        <v>594784</v>
       </c>
       <c r="R125" t="n">
-        <v>6947615</v>
+        <v>6947732</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13243,32 +13243,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133312229</v>
+        <v>133312205</v>
       </c>
       <c r="B126" t="n">
-        <v>79366</v>
+        <v>75444</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>594755</v>
+        <v>594702</v>
       </c>
       <c r="R126" t="n">
-        <v>6947668</v>
+        <v>6947615</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13353,7 +13353,7 @@
         <v>133312284</v>
       </c>
       <c r="B127" t="n">
-        <v>91878</v>
+        <v>91897</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>133312184</v>
       </c>
       <c r="B128" t="n">
-        <v>75433</v>
+        <v>75444</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>133312246</v>
       </c>
       <c r="B129" t="n">
-        <v>79953</v>
+        <v>79967</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>133312263</v>
       </c>
       <c r="B130" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>133312257</v>
       </c>
       <c r="B131" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13890,32 +13890,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312305</v>
+        <v>133312244</v>
       </c>
       <c r="B132" t="n">
-        <v>79334</v>
+        <v>57152</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,13 +13925,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594707</v>
+        <v>594797</v>
       </c>
       <c r="R132" t="n">
-        <v>6947692</v>
+        <v>6947735</v>
       </c>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13997,10 +14002,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312247</v>
+        <v>133312305</v>
       </c>
       <c r="B133" t="n">
-        <v>92227</v>
+        <v>79348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14008,21 +14013,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,13 +14037,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594801</v>
+        <v>594707</v>
       </c>
       <c r="R133" t="n">
-        <v>6947716</v>
+        <v>6947692</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14067,7 +14072,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,7 +14082,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14104,32 +14109,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312244</v>
+        <v>133312247</v>
       </c>
       <c r="B134" t="n">
-        <v>57145</v>
+        <v>92218</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14139,10 +14144,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594797</v>
+        <v>594801</v>
       </c>
       <c r="R134" t="n">
-        <v>6947735</v>
+        <v>6947716</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14174,7 +14179,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14184,12 +14189,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312299</v>
+        <v>133312221</v>
       </c>
       <c r="B135" t="n">
-        <v>92227</v>
+        <v>57965</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,34 +14227,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594747</v>
+        <v>594741</v>
       </c>
       <c r="R135" t="n">
-        <v>6947714</v>
+        <v>6947668</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14286,7 +14294,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14304,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14323,10 +14336,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312302</v>
+        <v>133312262</v>
       </c>
       <c r="B136" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14358,10 +14371,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594703</v>
+        <v>594845</v>
       </c>
       <c r="R136" t="n">
-        <v>6947719</v>
+        <v>6947767</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14393,7 +14406,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14403,7 +14416,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14430,10 +14443,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312262</v>
+        <v>133312302</v>
       </c>
       <c r="B137" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14465,10 +14478,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594845</v>
+        <v>594703</v>
       </c>
       <c r="R137" t="n">
-        <v>6947767</v>
+        <v>6947719</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14500,7 +14513,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14510,7 +14523,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14537,10 +14550,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312294</v>
+        <v>133312299</v>
       </c>
       <c r="B138" t="n">
-        <v>89310</v>
+        <v>92218</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,21 +14561,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14572,10 +14585,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594735</v>
+        <v>594747</v>
       </c>
       <c r="R138" t="n">
-        <v>6947729</v>
+        <v>6947714</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14607,7 +14620,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14617,7 +14630,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14644,10 +14657,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312221</v>
+        <v>133312294</v>
       </c>
       <c r="B139" t="n">
-        <v>57958</v>
+        <v>89328</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14655,42 +14668,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594741</v>
+        <v>594735</v>
       </c>
       <c r="R139" t="n">
-        <v>6947668</v>
+        <v>6947729</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14722,7 +14727,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14732,12 +14737,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312297</v>
+        <v>133312226</v>
       </c>
       <c r="B140" t="n">
-        <v>91928</v>
+        <v>5201</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594737</v>
+        <v>594755</v>
       </c>
       <c r="R140" t="n">
-        <v>6947721</v>
+        <v>6947670</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14874,7 +14874,7 @@
         <v>133312272</v>
       </c>
       <c r="B141" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>133312320</v>
       </c>
       <c r="B142" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15085,32 +15085,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312226</v>
+        <v>133312297</v>
       </c>
       <c r="B143" t="n">
-        <v>5199</v>
+        <v>91947</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,13 +15120,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594755</v>
+        <v>594737</v>
       </c>
       <c r="R143" t="n">
-        <v>6947670</v>
+        <v>6947721</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15195,7 +15195,7 @@
         <v>133312195</v>
       </c>
       <c r="B144" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>133312222</v>
       </c>
       <c r="B145" t="n">
-        <v>91942</v>
+        <v>91961</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15406,10 +15406,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133312252</v>
+        <v>133312181</v>
       </c>
       <c r="B146" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>594811</v>
+        <v>594723</v>
       </c>
       <c r="R146" t="n">
-        <v>6947698</v>
+        <v>6947583</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15513,10 +15513,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133312181</v>
+        <v>133312288</v>
       </c>
       <c r="B147" t="n">
-        <v>91928</v>
+        <v>79967</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15524,21 +15524,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15548,10 +15548,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>594723</v>
+        <v>594771</v>
       </c>
       <c r="R147" t="n">
-        <v>6947583</v>
+        <v>6947766</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15620,10 +15620,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133312250</v>
+        <v>133312252</v>
       </c>
       <c r="B148" t="n">
-        <v>92227</v>
+        <v>91947</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15631,21 +15631,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>594805</v>
+        <v>594811</v>
       </c>
       <c r="R148" t="n">
-        <v>6947701</v>
+        <v>6947698</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15727,10 +15727,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133312304</v>
+        <v>133312250</v>
       </c>
       <c r="B149" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>594716</v>
+        <v>594805</v>
       </c>
       <c r="R149" t="n">
         <v>6947701</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15834,10 +15834,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133312288</v>
+        <v>133312304</v>
       </c>
       <c r="B150" t="n">
-        <v>79953</v>
+        <v>92218</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15845,21 +15845,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>594771</v>
+        <v>594716</v>
       </c>
       <c r="R150" t="n">
-        <v>6947766</v>
+        <v>6947701</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15944,7 +15944,7 @@
         <v>133312218</v>
       </c>
       <c r="B151" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16053,32 +16053,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312271</v>
+        <v>133312303</v>
       </c>
       <c r="B152" t="n">
-        <v>79334</v>
+        <v>80481</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16088,10 +16088,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594798</v>
+        <v>594701</v>
       </c>
       <c r="R152" t="n">
-        <v>6947776</v>
+        <v>6947707</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16160,32 +16160,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312189</v>
+        <v>133312186</v>
       </c>
       <c r="B153" t="n">
-        <v>83183</v>
+        <v>75444</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1312</v>
+        <v>6426</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594688</v>
+        <v>594705</v>
       </c>
       <c r="R153" t="n">
-        <v>6947584</v>
+        <v>6947589</v>
       </c>
       <c r="S153" t="n">
         <v>6</v>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16267,32 +16267,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133312303</v>
+        <v>133312271</v>
       </c>
       <c r="B154" t="n">
-        <v>80467</v>
+        <v>79348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16302,10 +16302,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>594701</v>
+        <v>594798</v>
       </c>
       <c r="R154" t="n">
-        <v>6947707</v>
+        <v>6947776</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16374,32 +16374,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133312186</v>
+        <v>133312189</v>
       </c>
       <c r="B155" t="n">
-        <v>75433</v>
+        <v>83197</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6426</v>
+        <v>1312</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16409,10 +16409,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>594705</v>
+        <v>594688</v>
       </c>
       <c r="R155" t="n">
-        <v>6947589</v>
+        <v>6947584</v>
       </c>
       <c r="S155" t="n">
         <v>6</v>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16481,10 +16481,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133312295</v>
+        <v>133312253</v>
       </c>
       <c r="B156" t="n">
-        <v>92227</v>
+        <v>79380</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16492,21 +16492,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>594733</v>
+        <v>594812</v>
       </c>
       <c r="R156" t="n">
-        <v>6947724</v>
+        <v>6947696</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16588,10 +16588,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133312253</v>
+        <v>133312182</v>
       </c>
       <c r="B157" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16623,10 +16623,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>594812</v>
+        <v>594709</v>
       </c>
       <c r="R157" t="n">
-        <v>6947696</v>
+        <v>6947587</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16695,10 +16695,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133312182</v>
+        <v>133312295</v>
       </c>
       <c r="B158" t="n">
-        <v>79366</v>
+        <v>92218</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16706,21 +16706,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16730,10 +16730,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>594709</v>
+        <v>594733</v>
       </c>
       <c r="R158" t="n">
-        <v>6947587</v>
+        <v>6947724</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16805,7 +16805,7 @@
         <v>133312269</v>
       </c>
       <c r="B159" t="n">
-        <v>5179</v>
+        <v>5181</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16909,32 +16909,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133312208</v>
+        <v>133312198</v>
       </c>
       <c r="B160" t="n">
-        <v>91928</v>
+        <v>75444</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16944,10 +16944,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>594728</v>
+        <v>594683</v>
       </c>
       <c r="R160" t="n">
-        <v>6947607</v>
+        <v>6947603</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17016,10 +17016,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133312198</v>
+        <v>133312306</v>
       </c>
       <c r="B161" t="n">
-        <v>75433</v>
+        <v>80357</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17027,21 +17027,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17051,13 +17051,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>594683</v>
+        <v>594711</v>
       </c>
       <c r="R161" t="n">
-        <v>6947603</v>
+        <v>6947680</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17123,10 +17123,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312306</v>
+        <v>133312206</v>
       </c>
       <c r="B162" t="n">
-        <v>80343</v>
+        <v>75444</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17134,21 +17134,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17158,13 +17158,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594711</v>
+        <v>594719</v>
       </c>
       <c r="R162" t="n">
-        <v>6947680</v>
+        <v>6947615</v>
       </c>
       <c r="S162" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17230,32 +17230,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133312206</v>
+        <v>133312208</v>
       </c>
       <c r="B163" t="n">
-        <v>75433</v>
+        <v>91947</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>594719</v>
+        <v>594728</v>
       </c>
       <c r="R163" t="n">
-        <v>6947615</v>
+        <v>6947607</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17337,10 +17337,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>133312279</v>
+        <v>133312203</v>
       </c>
       <c r="B164" t="n">
-        <v>92227</v>
+        <v>83197</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17348,21 +17348,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17372,10 +17372,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>594835</v>
+        <v>594694</v>
       </c>
       <c r="R164" t="n">
-        <v>6947822</v>
+        <v>6947611</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133312203</v>
+        <v>133312279</v>
       </c>
       <c r="B165" t="n">
-        <v>83183</v>
+        <v>92218</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17455,21 +17455,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>594694</v>
+        <v>594835</v>
       </c>
       <c r="R165" t="n">
-        <v>6947611</v>
+        <v>6947822</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17554,7 +17554,7 @@
         <v>133312300</v>
       </c>
       <c r="B166" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>133312234</v>
       </c>
       <c r="B167" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312259</v>
+        <v>133312312</v>
       </c>
       <c r="B168" t="n">
-        <v>79953</v>
+        <v>80413</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,13 +17800,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594814</v>
+        <v>594697</v>
       </c>
       <c r="R168" t="n">
-        <v>6947723</v>
+        <v>6947661</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312312</v>
+        <v>133312259</v>
       </c>
       <c r="B169" t="n">
-        <v>80399</v>
+        <v>79967</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,13 +17907,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594697</v>
+        <v>594814</v>
       </c>
       <c r="R169" t="n">
-        <v>6947661</v>
+        <v>6947723</v>
       </c>
       <c r="S169" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17982,7 +17982,7 @@
         <v>133312216</v>
       </c>
       <c r="B170" t="n">
-        <v>92651</v>
+        <v>92172</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>133312319</v>
       </c>
       <c r="B171" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>133312280</v>
       </c>
       <c r="B172" t="n">
-        <v>79091</v>
+        <v>79105</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>133312313</v>
       </c>
       <c r="B173" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>133312212</v>
       </c>
       <c r="B174" t="n">
-        <v>91942</v>
+        <v>91961</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>133312243</v>
       </c>
       <c r="B175" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>133312308</v>
       </c>
       <c r="B176" t="n">
-        <v>75433</v>
+        <v>75444</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>133312268</v>
       </c>
       <c r="B177" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18840,10 +18840,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>133312179</v>
+        <v>133312213</v>
       </c>
       <c r="B178" t="n">
-        <v>79366</v>
+        <v>91947</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18851,21 +18851,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18875,10 +18875,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>594731</v>
+        <v>594725</v>
       </c>
       <c r="R178" t="n">
-        <v>6947567</v>
+        <v>6947645</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18947,10 +18947,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>133312213</v>
+        <v>133312179</v>
       </c>
       <c r="B179" t="n">
-        <v>91928</v>
+        <v>79380</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18958,21 +18958,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18982,10 +18982,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>594725</v>
+        <v>594731</v>
       </c>
       <c r="R179" t="n">
-        <v>6947645</v>
+        <v>6947567</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19057,7 +19057,7 @@
         <v>133312286</v>
       </c>
       <c r="B180" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>133312192</v>
       </c>
       <c r="B181" t="n">
-        <v>75433</v>
+        <v>75444</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312240</v>
+        <v>133312194</v>
       </c>
       <c r="B182" t="n">
-        <v>92227</v>
+        <v>83333</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,10 +19303,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594782</v>
+        <v>594690</v>
       </c>
       <c r="R182" t="n">
-        <v>6947711</v>
+        <v>6947596</v>
       </c>
       <c r="S182" t="n">
         <v>6</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,10 +19375,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312298</v>
+        <v>133312240</v>
       </c>
       <c r="B183" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19410,13 +19410,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594740</v>
+        <v>594782</v>
       </c>
       <c r="R183" t="n">
-        <v>6947716</v>
+        <v>6947711</v>
       </c>
       <c r="S183" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19482,10 +19482,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133312194</v>
+        <v>133312298</v>
       </c>
       <c r="B184" t="n">
-        <v>83319</v>
+        <v>92218</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19493,21 +19493,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19517,13 +19517,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>594690</v>
+        <v>594740</v>
       </c>
       <c r="R184" t="n">
-        <v>6947596</v>
+        <v>6947716</v>
       </c>
       <c r="S184" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19592,7 +19592,7 @@
         <v>133312265</v>
       </c>
       <c r="B185" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>133312316</v>
       </c>
       <c r="B186" t="n">
-        <v>75433</v>
+        <v>75444</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19803,32 +19803,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312188</v>
+        <v>133312289</v>
       </c>
       <c r="B187" t="n">
-        <v>75433</v>
+        <v>92218</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,13 +19838,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594698</v>
+        <v>594777</v>
       </c>
       <c r="R187" t="n">
-        <v>6947587</v>
+        <v>6947757</v>
       </c>
       <c r="S187" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,10 +19910,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312236</v>
+        <v>133312188</v>
       </c>
       <c r="B188" t="n">
-        <v>79358</v>
+        <v>75444</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19921,21 +19921,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6434</v>
+        <v>6426</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,13 +19945,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594742</v>
+        <v>594698</v>
       </c>
       <c r="R188" t="n">
-        <v>6947701</v>
+        <v>6947587</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,10 +20017,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312197</v>
+        <v>133312276</v>
       </c>
       <c r="B189" t="n">
-        <v>75433</v>
+        <v>80413</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20028,21 +20028,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594687</v>
+        <v>594856</v>
       </c>
       <c r="R189" t="n">
-        <v>6947597</v>
+        <v>6947759</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,10 +20124,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312276</v>
+        <v>133312236</v>
       </c>
       <c r="B190" t="n">
-        <v>80399</v>
+        <v>79372</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20135,21 +20135,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229497</v>
+        <v>6434</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20159,10 +20159,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594856</v>
+        <v>594742</v>
       </c>
       <c r="R190" t="n">
-        <v>6947759</v>
+        <v>6947701</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,10 +20231,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312289</v>
+        <v>133312266</v>
       </c>
       <c r="B191" t="n">
-        <v>92227</v>
+        <v>91947</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20242,21 +20242,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20266,10 +20266,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594777</v>
+        <v>594820</v>
       </c>
       <c r="R191" t="n">
-        <v>6947757</v>
+        <v>6947773</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,32 +20338,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312266</v>
+        <v>133312197</v>
       </c>
       <c r="B192" t="n">
-        <v>91928</v>
+        <v>75444</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594820</v>
+        <v>594687</v>
       </c>
       <c r="R192" t="n">
-        <v>6947773</v>
+        <v>6947597</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312225</v>
+        <v>133312317</v>
       </c>
       <c r="B193" t="n">
-        <v>91928</v>
+        <v>75444</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,13 +20480,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594757</v>
+        <v>594682</v>
       </c>
       <c r="R193" t="n">
-        <v>6947666</v>
+        <v>6947610</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20555,7 +20555,7 @@
         <v>133312318</v>
       </c>
       <c r="B194" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20659,32 +20659,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133312317</v>
+        <v>133312225</v>
       </c>
       <c r="B195" t="n">
-        <v>75433</v>
+        <v>91947</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20694,13 +20694,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>594682</v>
+        <v>594757</v>
       </c>
       <c r="R195" t="n">
-        <v>6947610</v>
+        <v>6947666</v>
       </c>
       <c r="S195" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312239</v>
+        <v>133312215</v>
       </c>
       <c r="B196" t="n">
-        <v>79334</v>
+        <v>92218</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594784</v>
+        <v>594730</v>
       </c>
       <c r="R196" t="n">
-        <v>6947700</v>
+        <v>6947645</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312219</v>
+        <v>133312239</v>
       </c>
       <c r="B197" t="n">
-        <v>91942</v>
+        <v>79348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20884,21 +20884,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594728</v>
+        <v>594784</v>
       </c>
       <c r="R197" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,10 +20980,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312215</v>
+        <v>133312224</v>
       </c>
       <c r="B198" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594730</v>
+        <v>594755</v>
       </c>
       <c r="R198" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312224</v>
+        <v>133312219</v>
       </c>
       <c r="B199" t="n">
-        <v>92227</v>
+        <v>91961</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21122,7 +21122,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594755</v>
+        <v>594728</v>
       </c>
       <c r="R199" t="n">
         <v>6947667</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21194,32 +21194,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133312209</v>
+        <v>133312277</v>
       </c>
       <c r="B200" t="n">
-        <v>92227</v>
+        <v>92613</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21229,10 +21229,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>594725</v>
+        <v>594860</v>
       </c>
       <c r="R200" t="n">
-        <v>6947645</v>
+        <v>6947799</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21274,7 +21274,12 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21283,6 +21288,7 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -21301,32 +21307,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133312277</v>
+        <v>133312209</v>
       </c>
       <c r="B201" t="n">
-        <v>92576</v>
+        <v>92218</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21336,10 +21342,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>594860</v>
+        <v>594725</v>
       </c>
       <c r="R201" t="n">
-        <v>6947799</v>
+        <v>6947645</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -21371,7 +21377,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21381,12 +21387,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21395,7 +21396,6 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12387,10 +12387,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133312232</v>
+        <v>133312282</v>
       </c>
       <c r="B118" t="n">
-        <v>91961</v>
+        <v>79380</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>594755</v>
+        <v>594775</v>
       </c>
       <c r="R118" t="n">
-        <v>6947677</v>
+        <v>6947806</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133312282</v>
+        <v>133312232</v>
       </c>
       <c r="B119" t="n">
-        <v>79380</v>
+        <v>91961</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>594775</v>
+        <v>594755</v>
       </c>
       <c r="R119" t="n">
-        <v>6947806</v>
+        <v>6947677</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12708,10 +12708,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133312293</v>
+        <v>133312229</v>
       </c>
       <c r="B121" t="n">
-        <v>91947</v>
+        <v>79380</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12719,21 +12719,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>594745</v>
+        <v>594755</v>
       </c>
       <c r="R121" t="n">
-        <v>6947738</v>
+        <v>6947668</v>
       </c>
       <c r="S121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133312229</v>
+        <v>133312293</v>
       </c>
       <c r="B122" t="n">
-        <v>79380</v>
+        <v>91947</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12850,13 +12850,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>594755</v>
+        <v>594745</v>
       </c>
       <c r="R122" t="n">
-        <v>6947668</v>
+        <v>6947738</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13890,32 +13890,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133312244</v>
+        <v>133312305</v>
       </c>
       <c r="B132" t="n">
-        <v>57152</v>
+        <v>79348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,13 +13925,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>594797</v>
+        <v>594707</v>
       </c>
       <c r="R132" t="n">
-        <v>6947735</v>
+        <v>6947692</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,12 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Äldre spillning under betestall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14002,10 +13997,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133312305</v>
+        <v>133312247</v>
       </c>
       <c r="B133" t="n">
-        <v>79348</v>
+        <v>92218</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14013,21 +14008,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14037,13 +14032,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>594707</v>
+        <v>594801</v>
       </c>
       <c r="R133" t="n">
-        <v>6947692</v>
+        <v>6947716</v>
       </c>
       <c r="S133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14072,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14082,7 +14077,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14109,32 +14104,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133312247</v>
+        <v>133312244</v>
       </c>
       <c r="B134" t="n">
-        <v>92218</v>
+        <v>57152</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14144,10 +14139,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>594801</v>
+        <v>594797</v>
       </c>
       <c r="R134" t="n">
-        <v>6947716</v>
+        <v>6947735</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14179,7 +14174,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14189,7 +14184,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Äldre spillning under betestall</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312221</v>
+        <v>133312302</v>
       </c>
       <c r="B135" t="n">
-        <v>57965</v>
+        <v>79380</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,42 +14227,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594741</v>
+        <v>594703</v>
       </c>
       <c r="R135" t="n">
-        <v>6947668</v>
+        <v>6947719</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14294,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14304,12 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14336,10 +14323,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312262</v>
+        <v>133312299</v>
       </c>
       <c r="B136" t="n">
-        <v>79380</v>
+        <v>92218</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14347,21 +14334,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14371,10 +14358,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594845</v>
+        <v>594747</v>
       </c>
       <c r="R136" t="n">
-        <v>6947767</v>
+        <v>6947714</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14406,7 +14393,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14416,7 +14403,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14443,7 +14430,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133312302</v>
+        <v>133312262</v>
       </c>
       <c r="B137" t="n">
         <v>79380</v>
@@ -14478,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>594703</v>
+        <v>594845</v>
       </c>
       <c r="R137" t="n">
-        <v>6947719</v>
+        <v>6947767</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14513,7 +14500,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14523,7 +14510,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14550,10 +14537,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133312299</v>
+        <v>133312294</v>
       </c>
       <c r="B138" t="n">
-        <v>92218</v>
+        <v>89328</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14561,21 +14548,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14585,10 +14572,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>594747</v>
+        <v>594735</v>
       </c>
       <c r="R138" t="n">
-        <v>6947714</v>
+        <v>6947729</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14620,7 +14607,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14630,7 +14617,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14657,10 +14644,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133312294</v>
+        <v>133312221</v>
       </c>
       <c r="B139" t="n">
-        <v>89328</v>
+        <v>57965</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14668,34 +14655,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sundsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>594735</v>
+        <v>594741</v>
       </c>
       <c r="R139" t="n">
-        <v>6947729</v>
+        <v>6947668</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14727,7 +14722,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14737,7 +14732,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15406,10 +15406,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133312181</v>
+        <v>133312288</v>
       </c>
       <c r="B146" t="n">
-        <v>91947</v>
+        <v>79967</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15417,21 +15417,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>594723</v>
+        <v>594771</v>
       </c>
       <c r="R146" t="n">
-        <v>6947583</v>
+        <v>6947766</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15513,10 +15513,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133312288</v>
+        <v>133312252</v>
       </c>
       <c r="B147" t="n">
-        <v>79967</v>
+        <v>91947</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15524,21 +15524,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15548,10 +15548,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>594771</v>
+        <v>594811</v>
       </c>
       <c r="R147" t="n">
-        <v>6947766</v>
+        <v>6947698</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15620,7 +15620,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133312252</v>
+        <v>133312181</v>
       </c>
       <c r="B148" t="n">
         <v>91947</v>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>594811</v>
+        <v>594723</v>
       </c>
       <c r="R148" t="n">
-        <v>6947698</v>
+        <v>6947583</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15941,32 +15941,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133312218</v>
+        <v>133312303</v>
       </c>
       <c r="B151" t="n">
-        <v>92218</v>
+        <v>80481</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15976,10 +15976,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>594717</v>
+        <v>594701</v>
       </c>
       <c r="R151" t="n">
-        <v>6947668</v>
+        <v>6947707</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16021,12 +16021,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16053,10 +16048,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312303</v>
+        <v>133312186</v>
       </c>
       <c r="B152" t="n">
-        <v>80481</v>
+        <v>75444</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16064,21 +16059,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6461</v>
+        <v>6426</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16088,13 +16083,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594701</v>
+        <v>594705</v>
       </c>
       <c r="R152" t="n">
-        <v>6947707</v>
+        <v>6947589</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16123,7 +16118,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16133,7 +16128,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16160,32 +16155,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312186</v>
+        <v>133312218</v>
       </c>
       <c r="B153" t="n">
-        <v>75444</v>
+        <v>92218</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16195,13 +16190,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594705</v>
+        <v>594717</v>
       </c>
       <c r="R153" t="n">
-        <v>6947589</v>
+        <v>6947668</v>
       </c>
       <c r="S153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16230,7 +16225,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16240,7 +16235,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17337,10 +17337,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>133312203</v>
+        <v>133312279</v>
       </c>
       <c r="B164" t="n">
-        <v>83197</v>
+        <v>92218</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17348,21 +17348,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17372,10 +17372,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>594694</v>
+        <v>594835</v>
       </c>
       <c r="R164" t="n">
-        <v>6947611</v>
+        <v>6947822</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133312279</v>
+        <v>133312203</v>
       </c>
       <c r="B165" t="n">
-        <v>92218</v>
+        <v>83197</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17455,21 +17455,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>594835</v>
+        <v>594694</v>
       </c>
       <c r="R165" t="n">
-        <v>6947822</v>
+        <v>6947611</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17765,10 +17765,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312312</v>
+        <v>133312216</v>
       </c>
       <c r="B168" t="n">
-        <v>80413</v>
+        <v>92172</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17776,21 +17776,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,13 +17800,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594697</v>
+        <v>594730</v>
       </c>
       <c r="R168" t="n">
-        <v>6947661</v>
+        <v>6947646</v>
       </c>
       <c r="S168" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,10 +17872,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312259</v>
+        <v>133312280</v>
       </c>
       <c r="B169" t="n">
-        <v>79967</v>
+        <v>79105</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17883,21 +17883,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594814</v>
+        <v>594788</v>
       </c>
       <c r="R169" t="n">
-        <v>6947723</v>
+        <v>6947813</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,10 +17979,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312216</v>
+        <v>133312312</v>
       </c>
       <c r="B170" t="n">
-        <v>92172</v>
+        <v>80413</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17990,21 +17990,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,13 +18014,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594730</v>
+        <v>594697</v>
       </c>
       <c r="R170" t="n">
-        <v>6947646</v>
+        <v>6947661</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,10 +18086,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312319</v>
+        <v>133312259</v>
       </c>
       <c r="B171" t="n">
-        <v>91947</v>
+        <v>79967</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18097,21 +18097,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594662</v>
+        <v>594814</v>
       </c>
       <c r="R171" t="n">
-        <v>6947577</v>
+        <v>6947723</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,10 +18193,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312280</v>
+        <v>133312319</v>
       </c>
       <c r="B172" t="n">
-        <v>79105</v>
+        <v>91947</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18204,21 +18204,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594788</v>
+        <v>594662</v>
       </c>
       <c r="R172" t="n">
-        <v>6947813</v>
+        <v>6947577</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18514,32 +18514,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312243</v>
+        <v>133312308</v>
       </c>
       <c r="B175" t="n">
-        <v>91947</v>
+        <v>75444</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594794</v>
+        <v>594707</v>
       </c>
       <c r="R175" t="n">
-        <v>6947729</v>
+        <v>6947669</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18621,32 +18621,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312308</v>
+        <v>133312268</v>
       </c>
       <c r="B176" t="n">
-        <v>75444</v>
+        <v>57962</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18656,10 +18656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594707</v>
+        <v>594805</v>
       </c>
       <c r="R176" t="n">
-        <v>6947669</v>
+        <v>6947762</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18701,7 +18701,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18728,10 +18733,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312268</v>
+        <v>133312243</v>
       </c>
       <c r="B177" t="n">
-        <v>57962</v>
+        <v>91947</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18739,21 +18744,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18763,10 +18768,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594805</v>
+        <v>594794</v>
       </c>
       <c r="R177" t="n">
-        <v>6947762</v>
+        <v>6947729</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18798,7 +18803,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18808,12 +18813,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312317</v>
+        <v>133312318</v>
       </c>
       <c r="B193" t="n">
-        <v>75444</v>
+        <v>79348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,13 +20480,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594682</v>
+        <v>594678</v>
       </c>
       <c r="R193" t="n">
-        <v>6947610</v>
+        <v>6947597</v>
       </c>
       <c r="S193" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20552,32 +20552,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133312318</v>
+        <v>133312317</v>
       </c>
       <c r="B194" t="n">
-        <v>79348</v>
+        <v>75444</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20587,13 +20587,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>594678</v>
+        <v>594682</v>
       </c>
       <c r="R194" t="n">
-        <v>6947597</v>
+        <v>6947610</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312215</v>
+        <v>133312219</v>
       </c>
       <c r="B196" t="n">
-        <v>92218</v>
+        <v>91961</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594730</v>
+        <v>594728</v>
       </c>
       <c r="R196" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312239</v>
+        <v>133312215</v>
       </c>
       <c r="B197" t="n">
-        <v>79348</v>
+        <v>92218</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20884,21 +20884,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594784</v>
+        <v>594730</v>
       </c>
       <c r="R197" t="n">
-        <v>6947700</v>
+        <v>6947645</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,10 +20980,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312224</v>
+        <v>133312239</v>
       </c>
       <c r="B198" t="n">
-        <v>92218</v>
+        <v>79348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20991,21 +20991,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594755</v>
+        <v>594784</v>
       </c>
       <c r="R198" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312219</v>
+        <v>133312224</v>
       </c>
       <c r="B199" t="n">
-        <v>91961</v>
+        <v>92218</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21122,7 +21122,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594728</v>
+        <v>594755</v>
       </c>
       <c r="R199" t="n">
         <v>6947667</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD199" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12387,10 +12387,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133312282</v>
+        <v>133312232</v>
       </c>
       <c r="B118" t="n">
-        <v>79380</v>
+        <v>91971</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>594775</v>
+        <v>594755</v>
       </c>
       <c r="R118" t="n">
-        <v>6947806</v>
+        <v>6947677</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133312232</v>
+        <v>133312282</v>
       </c>
       <c r="B119" t="n">
-        <v>91961</v>
+        <v>79390</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>594755</v>
+        <v>594775</v>
       </c>
       <c r="R119" t="n">
-        <v>6947677</v>
+        <v>6947806</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12604,7 +12604,7 @@
         <v>133312291</v>
       </c>
       <c r="B120" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>133312229</v>
       </c>
       <c r="B121" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>133312293</v>
       </c>
       <c r="B122" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12922,32 +12922,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312200</v>
+        <v>133312274</v>
       </c>
       <c r="B123" t="n">
-        <v>75444</v>
+        <v>92228</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594692</v>
+        <v>594857</v>
       </c>
       <c r="R123" t="n">
-        <v>6947605</v>
+        <v>6947775</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312274</v>
+        <v>133312241</v>
       </c>
       <c r="B124" t="n">
-        <v>92218</v>
+        <v>79977</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594857</v>
+        <v>594784</v>
       </c>
       <c r="R124" t="n">
-        <v>6947775</v>
+        <v>6947732</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312241</v>
+        <v>133312200</v>
       </c>
       <c r="B125" t="n">
-        <v>79967</v>
+        <v>75454</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594784</v>
+        <v>594692</v>
       </c>
       <c r="R125" t="n">
-        <v>6947732</v>
+        <v>6947605</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13246,7 +13246,7 @@
         <v>133312205</v>
       </c>
       <c r="B126" t="n">
-        <v>75444</v>
+        <v>75454</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>133312284</v>
       </c>
       <c r="B127" t="n">
-        <v>91897</v>
+        <v>91907</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>133312184</v>
       </c>
       <c r="B128" t="n">
-        <v>75444</v>
+        <v>75454</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13564,10 +13564,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312246</v>
+        <v>133312263</v>
       </c>
       <c r="B129" t="n">
-        <v>79967</v>
+        <v>57972</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13575,21 +13575,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,13 +13599,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594810</v>
+        <v>594826</v>
       </c>
       <c r="R129" t="n">
-        <v>6947725</v>
+        <v>6947773</v>
       </c>
       <c r="S129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,7 +13644,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13671,10 +13676,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312263</v>
+        <v>133312257</v>
       </c>
       <c r="B130" t="n">
-        <v>57962</v>
+        <v>79390</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13682,21 +13687,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13706,10 +13711,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594826</v>
+        <v>594820</v>
       </c>
       <c r="R130" t="n">
-        <v>6947773</v>
+        <v>6947705</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13741,7 +13746,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13751,12 +13756,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13783,10 +13783,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312257</v>
+        <v>133312246</v>
       </c>
       <c r="B131" t="n">
-        <v>79380</v>
+        <v>79977</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13794,21 +13794,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13818,13 +13818,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594820</v>
+        <v>594810</v>
       </c>
       <c r="R131" t="n">
-        <v>6947705</v>
+        <v>6947725</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13893,7 +13893,7 @@
         <v>133312305</v>
       </c>
       <c r="B132" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>133312247</v>
       </c>
       <c r="B133" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>133312244</v>
       </c>
       <c r="B134" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312302</v>
+        <v>133312299</v>
       </c>
       <c r="B135" t="n">
-        <v>79380</v>
+        <v>92228</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,21 +14227,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594703</v>
+        <v>594747</v>
       </c>
       <c r="R135" t="n">
-        <v>6947719</v>
+        <v>6947714</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14323,10 +14323,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312299</v>
+        <v>133312302</v>
       </c>
       <c r="B136" t="n">
-        <v>92218</v>
+        <v>79390</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14334,21 +14334,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594747</v>
+        <v>594703</v>
       </c>
       <c r="R136" t="n">
-        <v>6947714</v>
+        <v>6947719</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14433,7 +14433,7 @@
         <v>133312262</v>
       </c>
       <c r="B137" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>133312294</v>
       </c>
       <c r="B138" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>133312221</v>
       </c>
       <c r="B139" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312226</v>
+        <v>133312297</v>
       </c>
       <c r="B140" t="n">
-        <v>5201</v>
+        <v>91957</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594755</v>
+        <v>594737</v>
       </c>
       <c r="R140" t="n">
-        <v>6947670</v>
+        <v>6947721</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14874,7 +14874,7 @@
         <v>133312272</v>
       </c>
       <c r="B141" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14978,32 +14978,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133312320</v>
+        <v>133312226</v>
       </c>
       <c r="B142" t="n">
-        <v>79380</v>
+        <v>5201</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>594653</v>
+        <v>594755</v>
       </c>
       <c r="R142" t="n">
-        <v>6947566</v>
+        <v>6947670</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15085,10 +15085,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312297</v>
+        <v>133312320</v>
       </c>
       <c r="B143" t="n">
-        <v>91947</v>
+        <v>79390</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15096,21 +15096,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,13 +15120,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594737</v>
+        <v>594653</v>
       </c>
       <c r="R143" t="n">
-        <v>6947721</v>
+        <v>6947566</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15192,10 +15192,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133312195</v>
+        <v>133312222</v>
       </c>
       <c r="B144" t="n">
-        <v>83197</v>
+        <v>91971</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15203,21 +15203,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15227,13 +15227,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>594690</v>
+        <v>594755</v>
       </c>
       <c r="R144" t="n">
-        <v>6947596</v>
+        <v>6947667</v>
       </c>
       <c r="S144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15299,10 +15299,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133312222</v>
+        <v>133312195</v>
       </c>
       <c r="B145" t="n">
-        <v>91961</v>
+        <v>83207</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15310,21 +15310,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>594755</v>
+        <v>594690</v>
       </c>
       <c r="R145" t="n">
-        <v>6947667</v>
+        <v>6947596</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15409,7 +15409,7 @@
         <v>133312288</v>
       </c>
       <c r="B146" t="n">
-        <v>79967</v>
+        <v>79977</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>133312252</v>
       </c>
       <c r="B147" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15620,10 +15620,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133312181</v>
+        <v>133312250</v>
       </c>
       <c r="B148" t="n">
-        <v>91947</v>
+        <v>92228</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15631,21 +15631,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>594723</v>
+        <v>594805</v>
       </c>
       <c r="R148" t="n">
-        <v>6947583</v>
+        <v>6947701</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15727,10 +15727,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133312250</v>
+        <v>133312181</v>
       </c>
       <c r="B149" t="n">
-        <v>92218</v>
+        <v>91957</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15738,21 +15738,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>594805</v>
+        <v>594723</v>
       </c>
       <c r="R149" t="n">
-        <v>6947701</v>
+        <v>6947583</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15837,7 +15837,7 @@
         <v>133312304</v>
       </c>
       <c r="B150" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>133312303</v>
       </c>
       <c r="B151" t="n">
-        <v>80481</v>
+        <v>80477</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16048,32 +16048,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312186</v>
+        <v>133312271</v>
       </c>
       <c r="B152" t="n">
-        <v>75444</v>
+        <v>79358</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16083,13 +16083,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594705</v>
+        <v>594798</v>
       </c>
       <c r="R152" t="n">
-        <v>6947589</v>
+        <v>6947776</v>
       </c>
       <c r="S152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16155,32 +16155,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312218</v>
+        <v>133312186</v>
       </c>
       <c r="B153" t="n">
-        <v>92218</v>
+        <v>75454</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16190,13 +16190,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594717</v>
+        <v>594705</v>
       </c>
       <c r="R153" t="n">
-        <v>6947668</v>
+        <v>6947589</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16235,12 +16235,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16267,10 +16262,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133312271</v>
+        <v>133312218</v>
       </c>
       <c r="B154" t="n">
-        <v>79348</v>
+        <v>92228</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16278,21 +16273,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16302,10 +16297,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>594798</v>
+        <v>594717</v>
       </c>
       <c r="R154" t="n">
-        <v>6947776</v>
+        <v>6947668</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -16337,7 +16332,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16347,7 +16342,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16377,7 +16377,7 @@
         <v>133312189</v>
       </c>
       <c r="B155" t="n">
-        <v>83197</v>
+        <v>83207</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16481,32 +16481,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133312253</v>
+        <v>133312269</v>
       </c>
       <c r="B156" t="n">
-        <v>79380</v>
+        <v>5181</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>594812</v>
+        <v>594804</v>
       </c>
       <c r="R156" t="n">
-        <v>6947696</v>
+        <v>6947763</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16588,10 +16588,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133312182</v>
+        <v>133312253</v>
       </c>
       <c r="B157" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16623,10 +16623,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>594709</v>
+        <v>594812</v>
       </c>
       <c r="R157" t="n">
-        <v>6947587</v>
+        <v>6947696</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16698,7 +16698,7 @@
         <v>133312295</v>
       </c>
       <c r="B158" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16802,32 +16802,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133312269</v>
+        <v>133312182</v>
       </c>
       <c r="B159" t="n">
-        <v>5181</v>
+        <v>79390</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16837,10 +16837,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>594804</v>
+        <v>594709</v>
       </c>
       <c r="R159" t="n">
-        <v>6947763</v>
+        <v>6947587</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16912,7 +16912,7 @@
         <v>133312198</v>
       </c>
       <c r="B160" t="n">
-        <v>75444</v>
+        <v>75454</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>133312306</v>
       </c>
       <c r="B161" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17123,32 +17123,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312206</v>
+        <v>133312208</v>
       </c>
       <c r="B162" t="n">
-        <v>75444</v>
+        <v>91957</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17158,10 +17158,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594719</v>
+        <v>594728</v>
       </c>
       <c r="R162" t="n">
-        <v>6947615</v>
+        <v>6947607</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17230,32 +17230,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133312208</v>
+        <v>133312206</v>
       </c>
       <c r="B163" t="n">
-        <v>91947</v>
+        <v>75454</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>594728</v>
+        <v>594719</v>
       </c>
       <c r="R163" t="n">
-        <v>6947607</v>
+        <v>6947615</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17340,7 +17340,7 @@
         <v>133312279</v>
       </c>
       <c r="B164" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17444,10 +17444,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133312203</v>
+        <v>133312300</v>
       </c>
       <c r="B165" t="n">
-        <v>83197</v>
+        <v>91957</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17455,21 +17455,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>594694</v>
+        <v>594724</v>
       </c>
       <c r="R165" t="n">
-        <v>6947611</v>
+        <v>6947715</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17551,10 +17551,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133312300</v>
+        <v>133312203</v>
       </c>
       <c r="B166" t="n">
-        <v>91947</v>
+        <v>83207</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>594724</v>
+        <v>594694</v>
       </c>
       <c r="R166" t="n">
-        <v>6947715</v>
+        <v>6947611</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17661,7 +17661,7 @@
         <v>133312234</v>
       </c>
       <c r="B167" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17765,10 +17765,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312216</v>
+        <v>133312312</v>
       </c>
       <c r="B168" t="n">
-        <v>92172</v>
+        <v>80423</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17776,21 +17776,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,13 +17800,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594730</v>
+        <v>594697</v>
       </c>
       <c r="R168" t="n">
-        <v>6947646</v>
+        <v>6947661</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,10 +17872,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312280</v>
+        <v>133312259</v>
       </c>
       <c r="B169" t="n">
-        <v>79105</v>
+        <v>79977</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17883,21 +17883,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594788</v>
+        <v>594814</v>
       </c>
       <c r="R169" t="n">
-        <v>6947813</v>
+        <v>6947723</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,10 +17979,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312312</v>
+        <v>133312216</v>
       </c>
       <c r="B170" t="n">
-        <v>80413</v>
+        <v>92182</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17990,21 +17990,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,13 +18014,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594697</v>
+        <v>594730</v>
       </c>
       <c r="R170" t="n">
-        <v>6947661</v>
+        <v>6947646</v>
       </c>
       <c r="S170" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,10 +18086,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312259</v>
+        <v>133312280</v>
       </c>
       <c r="B171" t="n">
-        <v>79967</v>
+        <v>79115</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18097,21 +18097,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594814</v>
+        <v>594788</v>
       </c>
       <c r="R171" t="n">
-        <v>6947723</v>
+        <v>6947813</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,32 +18193,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312319</v>
+        <v>133312313</v>
       </c>
       <c r="B172" t="n">
-        <v>91947</v>
+        <v>80485</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594662</v>
+        <v>594697</v>
       </c>
       <c r="R172" t="n">
-        <v>6947577</v>
+        <v>6947661</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18300,32 +18300,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312313</v>
+        <v>133312319</v>
       </c>
       <c r="B173" t="n">
-        <v>80489</v>
+        <v>91957</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18335,10 +18335,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>594697</v>
+        <v>594662</v>
       </c>
       <c r="R173" t="n">
-        <v>6947661</v>
+        <v>6947577</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18410,7 +18410,7 @@
         <v>133312212</v>
       </c>
       <c r="B174" t="n">
-        <v>91961</v>
+        <v>91971</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18514,32 +18514,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133312308</v>
+        <v>133312243</v>
       </c>
       <c r="B175" t="n">
-        <v>75444</v>
+        <v>91957</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>594707</v>
+        <v>594794</v>
       </c>
       <c r="R175" t="n">
-        <v>6947669</v>
+        <v>6947729</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18621,32 +18621,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133312268</v>
+        <v>133312308</v>
       </c>
       <c r="B176" t="n">
-        <v>57962</v>
+        <v>75454</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18656,10 +18656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>594805</v>
+        <v>594707</v>
       </c>
       <c r="R176" t="n">
-        <v>6947762</v>
+        <v>6947669</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18701,12 +18701,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18733,10 +18728,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133312243</v>
+        <v>133312268</v>
       </c>
       <c r="B177" t="n">
-        <v>91947</v>
+        <v>57972</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18744,21 +18739,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18768,10 +18763,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>594794</v>
+        <v>594805</v>
       </c>
       <c r="R177" t="n">
-        <v>6947729</v>
+        <v>6947762</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -18803,7 +18798,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18813,7 +18808,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18843,7 +18843,7 @@
         <v>133312213</v>
       </c>
       <c r="B178" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>133312179</v>
       </c>
       <c r="B179" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>133312286</v>
       </c>
       <c r="B180" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>133312192</v>
       </c>
       <c r="B181" t="n">
-        <v>75444</v>
+        <v>75454</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312194</v>
+        <v>133312240</v>
       </c>
       <c r="B182" t="n">
-        <v>83333</v>
+        <v>92228</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,10 +19303,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594690</v>
+        <v>594782</v>
       </c>
       <c r="R182" t="n">
-        <v>6947596</v>
+        <v>6947711</v>
       </c>
       <c r="S182" t="n">
         <v>6</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,10 +19375,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312240</v>
+        <v>133312194</v>
       </c>
       <c r="B183" t="n">
-        <v>92218</v>
+        <v>83343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19386,21 +19386,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19410,10 +19410,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594782</v>
+        <v>594690</v>
       </c>
       <c r="R183" t="n">
-        <v>6947711</v>
+        <v>6947596</v>
       </c>
       <c r="S183" t="n">
         <v>6</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19485,7 +19485,7 @@
         <v>133312298</v>
       </c>
       <c r="B184" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>133312265</v>
       </c>
       <c r="B185" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19696,32 +19696,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312316</v>
+        <v>133312289</v>
       </c>
       <c r="B186" t="n">
-        <v>75444</v>
+        <v>92228</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594666</v>
+        <v>594777</v>
       </c>
       <c r="R186" t="n">
-        <v>6947640</v>
+        <v>6947757</v>
       </c>
       <c r="S186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19803,32 +19803,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312289</v>
+        <v>133312276</v>
       </c>
       <c r="B187" t="n">
-        <v>92218</v>
+        <v>80423</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,10 +19838,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594777</v>
+        <v>594856</v>
       </c>
       <c r="R187" t="n">
-        <v>6947757</v>
+        <v>6947759</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,10 +19910,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312188</v>
+        <v>133312236</v>
       </c>
       <c r="B188" t="n">
-        <v>75444</v>
+        <v>79382</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19921,21 +19921,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6426</v>
+        <v>6434</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,13 +19945,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594698</v>
+        <v>594742</v>
       </c>
       <c r="R188" t="n">
-        <v>6947587</v>
+        <v>6947701</v>
       </c>
       <c r="S188" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,32 +20017,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312276</v>
+        <v>133312266</v>
       </c>
       <c r="B189" t="n">
-        <v>80413</v>
+        <v>91957</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594856</v>
+        <v>594820</v>
       </c>
       <c r="R189" t="n">
-        <v>6947759</v>
+        <v>6947773</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,32 +20124,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312236</v>
+        <v>133312318</v>
       </c>
       <c r="B190" t="n">
-        <v>79372</v>
+        <v>79358</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20159,10 +20159,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594742</v>
+        <v>594678</v>
       </c>
       <c r="R190" t="n">
-        <v>6947701</v>
+        <v>6947597</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,32 +20231,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312266</v>
+        <v>133312317</v>
       </c>
       <c r="B191" t="n">
-        <v>91947</v>
+        <v>75454</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594820</v>
+        <v>594682</v>
       </c>
       <c r="R191" t="n">
-        <v>6947773</v>
+        <v>6947610</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20341,7 +20341,7 @@
         <v>133312197</v>
       </c>
       <c r="B192" t="n">
-        <v>75444</v>
+        <v>75454</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312318</v>
+        <v>133312316</v>
       </c>
       <c r="B193" t="n">
-        <v>79348</v>
+        <v>75454</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,13 +20480,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594678</v>
+        <v>594666</v>
       </c>
       <c r="R193" t="n">
-        <v>6947597</v>
+        <v>6947640</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20552,10 +20552,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133312317</v>
+        <v>133312188</v>
       </c>
       <c r="B194" t="n">
-        <v>75444</v>
+        <v>75454</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20587,13 +20587,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>594682</v>
+        <v>594698</v>
       </c>
       <c r="R194" t="n">
-        <v>6947610</v>
+        <v>6947587</v>
       </c>
       <c r="S194" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20662,7 +20662,7 @@
         <v>133312225</v>
       </c>
       <c r="B195" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312219</v>
+        <v>133312239</v>
       </c>
       <c r="B196" t="n">
-        <v>91961</v>
+        <v>79358</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594728</v>
+        <v>594784</v>
       </c>
       <c r="R196" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312215</v>
+        <v>133312224</v>
       </c>
       <c r="B197" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594730</v>
+        <v>594755</v>
       </c>
       <c r="R197" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,10 +20980,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312239</v>
+        <v>133312219</v>
       </c>
       <c r="B198" t="n">
-        <v>79348</v>
+        <v>91971</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20991,21 +20991,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594784</v>
+        <v>594728</v>
       </c>
       <c r="R198" t="n">
-        <v>6947700</v>
+        <v>6947667</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312224</v>
+        <v>133312215</v>
       </c>
       <c r="B199" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594755</v>
+        <v>594730</v>
       </c>
       <c r="R199" t="n">
-        <v>6947667</v>
+        <v>6947645</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21197,7 +21197,7 @@
         <v>133312277</v>
       </c>
       <c r="B200" t="n">
-        <v>92613</v>
+        <v>92623</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>133312209</v>
       </c>
       <c r="B201" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -12387,10 +12387,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133312232</v>
+        <v>133312282</v>
       </c>
       <c r="B118" t="n">
-        <v>91971</v>
+        <v>79390</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>594755</v>
+        <v>594775</v>
       </c>
       <c r="R118" t="n">
-        <v>6947677</v>
+        <v>6947806</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133312282</v>
+        <v>133312232</v>
       </c>
       <c r="B119" t="n">
-        <v>79390</v>
+        <v>91971</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>594775</v>
+        <v>594755</v>
       </c>
       <c r="R119" t="n">
-        <v>6947806</v>
+        <v>6947677</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12922,32 +12922,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133312274</v>
+        <v>133312200</v>
       </c>
       <c r="B123" t="n">
-        <v>92228</v>
+        <v>75454</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>594857</v>
+        <v>594692</v>
       </c>
       <c r="R123" t="n">
-        <v>6947775</v>
+        <v>6947605</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133312241</v>
+        <v>133312274</v>
       </c>
       <c r="B124" t="n">
-        <v>79977</v>
+        <v>92228</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>594784</v>
+        <v>594857</v>
       </c>
       <c r="R124" t="n">
-        <v>6947732</v>
+        <v>6947775</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13136,32 +13136,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133312200</v>
+        <v>133312241</v>
       </c>
       <c r="B125" t="n">
-        <v>75454</v>
+        <v>79977</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>594692</v>
+        <v>594784</v>
       </c>
       <c r="R125" t="n">
-        <v>6947605</v>
+        <v>6947732</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13564,10 +13564,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133312263</v>
+        <v>133312246</v>
       </c>
       <c r="B129" t="n">
-        <v>57972</v>
+        <v>79977</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13575,21 +13575,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13599,13 +13599,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>594826</v>
+        <v>594810</v>
       </c>
       <c r="R129" t="n">
-        <v>6947773</v>
+        <v>6947725</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13644,12 +13644,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13676,10 +13671,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133312257</v>
+        <v>133312263</v>
       </c>
       <c r="B130" t="n">
-        <v>79390</v>
+        <v>57972</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13687,21 +13682,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13711,10 +13706,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>594820</v>
+        <v>594826</v>
       </c>
       <c r="R130" t="n">
-        <v>6947705</v>
+        <v>6947773</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13746,7 +13741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13756,7 +13751,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13783,10 +13783,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133312246</v>
+        <v>133312257</v>
       </c>
       <c r="B131" t="n">
-        <v>79977</v>
+        <v>79390</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13794,21 +13794,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13818,13 +13818,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>594810</v>
+        <v>594820</v>
       </c>
       <c r="R131" t="n">
-        <v>6947725</v>
+        <v>6947705</v>
       </c>
       <c r="S131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14216,10 +14216,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133312299</v>
+        <v>133312302</v>
       </c>
       <c r="B135" t="n">
-        <v>92228</v>
+        <v>79390</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14227,21 +14227,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>594747</v>
+        <v>594703</v>
       </c>
       <c r="R135" t="n">
-        <v>6947714</v>
+        <v>6947719</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14323,10 +14323,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133312302</v>
+        <v>133312299</v>
       </c>
       <c r="B136" t="n">
-        <v>79390</v>
+        <v>92228</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14334,21 +14334,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>594703</v>
+        <v>594747</v>
       </c>
       <c r="R136" t="n">
-        <v>6947719</v>
+        <v>6947714</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14764,32 +14764,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133312297</v>
+        <v>133312226</v>
       </c>
       <c r="B140" t="n">
-        <v>91957</v>
+        <v>5201</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14799,13 +14799,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>594737</v>
+        <v>594755</v>
       </c>
       <c r="R140" t="n">
-        <v>6947721</v>
+        <v>6947670</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14978,32 +14978,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133312226</v>
+        <v>133312320</v>
       </c>
       <c r="B142" t="n">
-        <v>5201</v>
+        <v>79390</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>594755</v>
+        <v>594653</v>
       </c>
       <c r="R142" t="n">
-        <v>6947670</v>
+        <v>6947566</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15085,10 +15085,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133312320</v>
+        <v>133312297</v>
       </c>
       <c r="B143" t="n">
-        <v>79390</v>
+        <v>91957</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15096,21 +15096,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15120,13 +15120,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>594653</v>
+        <v>594737</v>
       </c>
       <c r="R143" t="n">
-        <v>6947566</v>
+        <v>6947721</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15192,10 +15192,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133312222</v>
+        <v>133312195</v>
       </c>
       <c r="B144" t="n">
-        <v>91971</v>
+        <v>83207</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15203,21 +15203,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15227,13 +15227,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>594755</v>
+        <v>594690</v>
       </c>
       <c r="R144" t="n">
-        <v>6947667</v>
+        <v>6947596</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15299,10 +15299,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133312195</v>
+        <v>133312222</v>
       </c>
       <c r="B145" t="n">
-        <v>83207</v>
+        <v>91971</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15310,21 +15310,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>594690</v>
+        <v>594755</v>
       </c>
       <c r="R145" t="n">
-        <v>6947596</v>
+        <v>6947667</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15620,10 +15620,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133312250</v>
+        <v>133312181</v>
       </c>
       <c r="B148" t="n">
-        <v>92228</v>
+        <v>91957</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15631,21 +15631,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>594805</v>
+        <v>594723</v>
       </c>
       <c r="R148" t="n">
-        <v>6947701</v>
+        <v>6947583</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15727,10 +15727,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133312181</v>
+        <v>133312250</v>
       </c>
       <c r="B149" t="n">
-        <v>91957</v>
+        <v>92228</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15738,21 +15738,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>594723</v>
+        <v>594805</v>
       </c>
       <c r="R149" t="n">
-        <v>6947583</v>
+        <v>6947701</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16048,32 +16048,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133312271</v>
+        <v>133312186</v>
       </c>
       <c r="B152" t="n">
-        <v>79358</v>
+        <v>75454</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16083,13 +16083,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>594798</v>
+        <v>594705</v>
       </c>
       <c r="R152" t="n">
-        <v>6947776</v>
+        <v>6947589</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16155,32 +16155,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133312186</v>
+        <v>133312218</v>
       </c>
       <c r="B153" t="n">
-        <v>75454</v>
+        <v>92228</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16190,13 +16190,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>594705</v>
+        <v>594717</v>
       </c>
       <c r="R153" t="n">
-        <v>6947589</v>
+        <v>6947668</v>
       </c>
       <c r="S153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16235,7 +16235,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Död fruktkropp</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16262,10 +16267,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133312218</v>
+        <v>133312271</v>
       </c>
       <c r="B154" t="n">
-        <v>92228</v>
+        <v>79358</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16273,21 +16278,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16297,10 +16302,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>594717</v>
+        <v>594798</v>
       </c>
       <c r="R154" t="n">
-        <v>6947668</v>
+        <v>6947776</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -16332,7 +16337,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16342,12 +16347,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16481,32 +16481,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133312269</v>
+        <v>133312253</v>
       </c>
       <c r="B156" t="n">
-        <v>5181</v>
+        <v>79390</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>594804</v>
+        <v>594812</v>
       </c>
       <c r="R156" t="n">
-        <v>6947763</v>
+        <v>6947696</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16588,7 +16588,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133312253</v>
+        <v>133312182</v>
       </c>
       <c r="B157" t="n">
         <v>79390</v>
@@ -16623,10 +16623,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>594812</v>
+        <v>594709</v>
       </c>
       <c r="R157" t="n">
-        <v>6947696</v>
+        <v>6947587</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16802,32 +16802,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133312182</v>
+        <v>133312269</v>
       </c>
       <c r="B159" t="n">
-        <v>79390</v>
+        <v>5181</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16837,10 +16837,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>594709</v>
+        <v>594804</v>
       </c>
       <c r="R159" t="n">
-        <v>6947587</v>
+        <v>6947763</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17123,32 +17123,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133312208</v>
+        <v>133312206</v>
       </c>
       <c r="B162" t="n">
-        <v>91957</v>
+        <v>75454</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17158,10 +17158,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>594728</v>
+        <v>594719</v>
       </c>
       <c r="R162" t="n">
-        <v>6947607</v>
+        <v>6947615</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17230,32 +17230,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133312206</v>
+        <v>133312208</v>
       </c>
       <c r="B163" t="n">
-        <v>75454</v>
+        <v>91957</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17265,10 +17265,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>594719</v>
+        <v>594728</v>
       </c>
       <c r="R163" t="n">
-        <v>6947615</v>
+        <v>6947607</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133312300</v>
+        <v>133312203</v>
       </c>
       <c r="B165" t="n">
-        <v>91957</v>
+        <v>83207</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17455,21 +17455,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>594724</v>
+        <v>594694</v>
       </c>
       <c r="R165" t="n">
-        <v>6947715</v>
+        <v>6947611</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17551,10 +17551,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133312203</v>
+        <v>133312300</v>
       </c>
       <c r="B166" t="n">
-        <v>83207</v>
+        <v>91957</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>594694</v>
+        <v>594724</v>
       </c>
       <c r="R166" t="n">
-        <v>6947611</v>
+        <v>6947715</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17765,32 +17765,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312312</v>
+        <v>133312259</v>
       </c>
       <c r="B168" t="n">
-        <v>80423</v>
+        <v>79977</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,13 +17800,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594697</v>
+        <v>594814</v>
       </c>
       <c r="R168" t="n">
-        <v>6947661</v>
+        <v>6947723</v>
       </c>
       <c r="S168" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312259</v>
+        <v>133312216</v>
       </c>
       <c r="B169" t="n">
-        <v>79977</v>
+        <v>92182</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>3298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594814</v>
+        <v>594730</v>
       </c>
       <c r="R169" t="n">
-        <v>6947723</v>
+        <v>6947646</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,32 +17979,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312216</v>
+        <v>133312319</v>
       </c>
       <c r="B170" t="n">
-        <v>92182</v>
+        <v>91957</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594730</v>
+        <v>594662</v>
       </c>
       <c r="R170" t="n">
-        <v>6947646</v>
+        <v>6947577</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18300,32 +18300,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312319</v>
+        <v>133312312</v>
       </c>
       <c r="B173" t="n">
-        <v>91957</v>
+        <v>80423</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>594662</v>
+        <v>594697</v>
       </c>
       <c r="R173" t="n">
-        <v>6947577</v>
+        <v>6947661</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19268,10 +19268,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133312240</v>
+        <v>133312194</v>
       </c>
       <c r="B182" t="n">
-        <v>92228</v>
+        <v>83343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19279,21 +19279,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19303,10 +19303,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>594782</v>
+        <v>594690</v>
       </c>
       <c r="R182" t="n">
-        <v>6947711</v>
+        <v>6947596</v>
       </c>
       <c r="S182" t="n">
         <v>6</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19375,10 +19375,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133312194</v>
+        <v>133312240</v>
       </c>
       <c r="B183" t="n">
-        <v>83343</v>
+        <v>92228</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19386,21 +19386,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19410,10 +19410,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>594690</v>
+        <v>594782</v>
       </c>
       <c r="R183" t="n">
-        <v>6947596</v>
+        <v>6947711</v>
       </c>
       <c r="S183" t="n">
         <v>6</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19696,32 +19696,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133312289</v>
+        <v>133312316</v>
       </c>
       <c r="B186" t="n">
-        <v>92228</v>
+        <v>75454</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>594777</v>
+        <v>594666</v>
       </c>
       <c r="R186" t="n">
-        <v>6947757</v>
+        <v>6947640</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19910,32 +19910,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312236</v>
+        <v>133312266</v>
       </c>
       <c r="B188" t="n">
-        <v>79382</v>
+        <v>91957</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,10 +19945,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594742</v>
+        <v>594820</v>
       </c>
       <c r="R188" t="n">
-        <v>6947701</v>
+        <v>6947773</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,32 +20017,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312266</v>
+        <v>133312197</v>
       </c>
       <c r="B189" t="n">
-        <v>91957</v>
+        <v>75454</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594820</v>
+        <v>594687</v>
       </c>
       <c r="R189" t="n">
-        <v>6947773</v>
+        <v>6947597</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20338,32 +20338,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312197</v>
+        <v>133312225</v>
       </c>
       <c r="B192" t="n">
-        <v>75454</v>
+        <v>91957</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594687</v>
+        <v>594757</v>
       </c>
       <c r="R192" t="n">
-        <v>6947597</v>
+        <v>6947666</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,32 +20445,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312316</v>
+        <v>133312289</v>
       </c>
       <c r="B193" t="n">
-        <v>75454</v>
+        <v>92228</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20480,13 +20480,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>594666</v>
+        <v>594777</v>
       </c>
       <c r="R193" t="n">
-        <v>6947640</v>
+        <v>6947757</v>
       </c>
       <c r="S193" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20659,32 +20659,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133312225</v>
+        <v>133312236</v>
       </c>
       <c r="B195" t="n">
-        <v>91957</v>
+        <v>79382</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20694,10 +20694,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>594757</v>
+        <v>594742</v>
       </c>
       <c r="R195" t="n">
-        <v>6947666</v>
+        <v>6947701</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20766,10 +20766,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133312239</v>
+        <v>133312219</v>
       </c>
       <c r="B196" t="n">
-        <v>79358</v>
+        <v>91971</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20777,21 +20777,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>594784</v>
+        <v>594728</v>
       </c>
       <c r="R196" t="n">
-        <v>6947700</v>
+        <v>6947667</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20873,7 +20873,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133312224</v>
+        <v>133312215</v>
       </c>
       <c r="B197" t="n">
         <v>92228</v>
@@ -20908,10 +20908,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>594755</v>
+        <v>594730</v>
       </c>
       <c r="R197" t="n">
-        <v>6947667</v>
+        <v>6947645</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20980,10 +20980,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133312219</v>
+        <v>133312239</v>
       </c>
       <c r="B198" t="n">
-        <v>91971</v>
+        <v>79358</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20991,21 +20991,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>594728</v>
+        <v>594784</v>
       </c>
       <c r="R198" t="n">
-        <v>6947667</v>
+        <v>6947700</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21087,7 +21087,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133312215</v>
+        <v>133312224</v>
       </c>
       <c r="B199" t="n">
         <v>92228</v>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>594730</v>
+        <v>594755</v>
       </c>
       <c r="R199" t="n">
-        <v>6947645</v>
+        <v>6947667</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD199" t="b">

--- a/artfynd/A 24987-2024 artfynd.xlsx
+++ b/artfynd/A 24987-2024 artfynd.xlsx
@@ -15192,10 +15192,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133312195</v>
+        <v>133312222</v>
       </c>
       <c r="B144" t="n">
-        <v>83207</v>
+        <v>91971</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15203,21 +15203,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15227,13 +15227,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>594690</v>
+        <v>594755</v>
       </c>
       <c r="R144" t="n">
-        <v>6947596</v>
+        <v>6947667</v>
       </c>
       <c r="S144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15299,10 +15299,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133312222</v>
+        <v>133312195</v>
       </c>
       <c r="B145" t="n">
-        <v>91971</v>
+        <v>83207</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15310,21 +15310,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>594755</v>
+        <v>594690</v>
       </c>
       <c r="R145" t="n">
-        <v>6947667</v>
+        <v>6947596</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17765,32 +17765,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133312259</v>
+        <v>133312312</v>
       </c>
       <c r="B168" t="n">
-        <v>79977</v>
+        <v>80423</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17800,13 +17800,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>594814</v>
+        <v>594697</v>
       </c>
       <c r="R168" t="n">
-        <v>6947723</v>
+        <v>6947661</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17872,32 +17872,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133312216</v>
+        <v>133312259</v>
       </c>
       <c r="B169" t="n">
-        <v>92182</v>
+        <v>79977</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3298</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>594730</v>
+        <v>594814</v>
       </c>
       <c r="R169" t="n">
-        <v>6947646</v>
+        <v>6947723</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17979,32 +17979,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133312319</v>
+        <v>133312216</v>
       </c>
       <c r="B170" t="n">
-        <v>91957</v>
+        <v>92182</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18014,10 +18014,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>594662</v>
+        <v>594730</v>
       </c>
       <c r="R170" t="n">
-        <v>6947577</v>
+        <v>6947646</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18086,10 +18086,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133312280</v>
+        <v>133312319</v>
       </c>
       <c r="B171" t="n">
-        <v>79115</v>
+        <v>91957</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18097,21 +18097,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>594788</v>
+        <v>594662</v>
       </c>
       <c r="R171" t="n">
-        <v>6947813</v>
+        <v>6947577</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18193,32 +18193,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133312313</v>
+        <v>133312280</v>
       </c>
       <c r="B172" t="n">
-        <v>80485</v>
+        <v>79115</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>594697</v>
+        <v>594788</v>
       </c>
       <c r="R172" t="n">
-        <v>6947661</v>
+        <v>6947813</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18300,10 +18300,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133312312</v>
+        <v>133312313</v>
       </c>
       <c r="B173" t="n">
-        <v>80423</v>
+        <v>80485</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18311,21 +18311,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18341,7 +18341,7 @@
         <v>6947661</v>
       </c>
       <c r="S173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19803,32 +19803,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133312276</v>
+        <v>133312289</v>
       </c>
       <c r="B187" t="n">
-        <v>80423</v>
+        <v>92228</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19838,10 +19838,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>594856</v>
+        <v>594777</v>
       </c>
       <c r="R187" t="n">
-        <v>6947759</v>
+        <v>6947757</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19910,32 +19910,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133312266</v>
+        <v>133312188</v>
       </c>
       <c r="B188" t="n">
-        <v>91957</v>
+        <v>75454</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19945,13 +19945,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>594820</v>
+        <v>594698</v>
       </c>
       <c r="R188" t="n">
-        <v>6947773</v>
+        <v>6947587</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,10 +20017,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133312197</v>
+        <v>133312276</v>
       </c>
       <c r="B189" t="n">
-        <v>75454</v>
+        <v>80423</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20028,21 +20028,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>594687</v>
+        <v>594856</v>
       </c>
       <c r="R189" t="n">
-        <v>6947597</v>
+        <v>6947759</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20124,32 +20124,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133312318</v>
+        <v>133312236</v>
       </c>
       <c r="B190" t="n">
-        <v>79358</v>
+        <v>79382</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20159,10 +20159,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>594678</v>
+        <v>594742</v>
       </c>
       <c r="R190" t="n">
-        <v>6947597</v>
+        <v>6947701</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20231,32 +20231,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133312317</v>
+        <v>133312266</v>
       </c>
       <c r="B191" t="n">
-        <v>75454</v>
+        <v>91957</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20266,13 +20266,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>594682</v>
+        <v>594820</v>
       </c>
       <c r="R191" t="n">
-        <v>6947610</v>
+        <v>6947773</v>
       </c>
       <c r="S191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20338,32 +20338,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133312225</v>
+        <v>133312197</v>
       </c>
       <c r="B192" t="n">
-        <v>91957</v>
+        <v>75454</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20373,10 +20373,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>594757</v>
+        <v>594687</v>
       </c>
       <c r="R192" t="n">
-        <v>6947666</v>
+        <v>6947597</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20445,10 +20445,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133312289</v>
+        <v>133312318</v>
       </c>
       <c r="B193" t="n">
-        <v>92228</v>
+        <v>79358</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20456,21 +20456,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
   